--- a/artfynd/A 49064-2025 artfynd.xlsx
+++ b/artfynd/A 49064-2025 artfynd.xlsx
@@ -2683,10 +2683,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129082549</v>
+        <v>129082537</v>
       </c>
       <c r="B22" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2694,34 +2694,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436322</v>
+        <v>436399</v>
       </c>
       <c r="R22" t="n">
-        <v>6786798</v>
+        <v>6786867</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2974,10 +2982,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129082537</v>
+        <v>129082549</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2985,42 +2993,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436399</v>
+        <v>436322</v>
       </c>
       <c r="R25" t="n">
-        <v>6786867</v>
+        <v>6786798</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4168,27 +4168,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129082588</v>
+        <v>129082538</v>
       </c>
       <c r="B37" t="n">
-        <v>58093</v>
+        <v>57720</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4201,7 +4201,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435979</v>
+        <v>436141</v>
       </c>
       <c r="R37" t="n">
-        <v>6786531</v>
+        <v>6786882</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4273,41 +4273,40 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129082573</v>
+        <v>129082533</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4317,10 +4316,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436525</v>
+        <v>436445</v>
       </c>
       <c r="R38" t="n">
-        <v>6786729</v>
+        <v>6786610</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4361,7 +4360,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4574,27 +4572,27 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129082538</v>
+        <v>129082588</v>
       </c>
       <c r="B41" t="n">
-        <v>57720</v>
+        <v>58093</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4607,7 +4605,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4617,10 +4615,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436141</v>
+        <v>435979</v>
       </c>
       <c r="R41" t="n">
-        <v>6786882</v>
+        <v>6786531</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4679,40 +4677,41 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129082533</v>
+        <v>129082573</v>
       </c>
       <c r="B42" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -4722,10 +4721,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436445</v>
+        <v>436525</v>
       </c>
       <c r="R42" t="n">
-        <v>6786610</v>
+        <v>6786729</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4766,6 +4765,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5279,37 +5279,43 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129082648</v>
+        <v>129082567</v>
       </c>
       <c r="B48" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5317,10 +5323,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436353</v>
+        <v>436312</v>
       </c>
       <c r="R48" t="n">
-        <v>6786940</v>
+        <v>6786810</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5380,45 +5386,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129082611</v>
+        <v>129082585</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435898</v>
+        <v>435948</v>
       </c>
       <c r="R49" t="n">
-        <v>6786619</v>
+        <v>6786565</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5459,6 +5474,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5477,7 +5493,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129082624</v>
+        <v>129082648</v>
       </c>
       <c r="B50" t="n">
         <v>79034</v>
@@ -5506,16 +5522,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436138</v>
+        <v>436353</v>
       </c>
       <c r="R50" t="n">
-        <v>6786811</v>
+        <v>6786940</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5556,6 +5575,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5574,7 +5594,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129082655</v>
+        <v>129082611</v>
       </c>
       <c r="B51" t="n">
         <v>79034</v>
@@ -5609,10 +5629,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436020</v>
+        <v>435898</v>
       </c>
       <c r="R51" t="n">
-        <v>6786856</v>
+        <v>6786619</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5671,10 +5691,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129082529</v>
+        <v>129082624</v>
       </c>
       <c r="B52" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5682,42 +5702,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436057</v>
+        <v>436138</v>
       </c>
       <c r="R52" t="n">
-        <v>6786761</v>
+        <v>6786811</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5776,54 +5788,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129082567</v>
+        <v>129082655</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436312</v>
+        <v>436020</v>
       </c>
       <c r="R53" t="n">
-        <v>6786810</v>
+        <v>6786856</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5864,7 +5867,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5883,41 +5885,40 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129082585</v>
+        <v>129082529</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -5927,10 +5928,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435948</v>
+        <v>436057</v>
       </c>
       <c r="R54" t="n">
-        <v>6786565</v>
+        <v>6786761</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5971,7 +5972,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7291,10 +7291,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129082507</v>
+        <v>129082528</v>
       </c>
       <c r="B68" t="n">
-        <v>79653</v>
+        <v>57720</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7302,34 +7302,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436265</v>
+        <v>436042</v>
       </c>
       <c r="R68" t="n">
-        <v>6786874</v>
+        <v>6786785</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7388,45 +7396,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129082610</v>
+        <v>129082572</v>
       </c>
       <c r="B69" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435906</v>
+        <v>436553</v>
       </c>
       <c r="R69" t="n">
-        <v>6786603</v>
+        <v>6786640</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7467,6 +7484,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7485,10 +7503,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129082528</v>
+        <v>129082552</v>
       </c>
       <c r="B70" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7496,42 +7514,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436042</v>
+        <v>436206</v>
       </c>
       <c r="R70" t="n">
-        <v>6786785</v>
+        <v>6786892</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7590,54 +7600,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129082572</v>
+        <v>129082550</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436553</v>
+        <v>436361</v>
       </c>
       <c r="R71" t="n">
-        <v>6786640</v>
+        <v>6786687</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7678,7 +7679,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129082552</v>
+        <v>129082507</v>
       </c>
       <c r="B72" t="n">
-        <v>78792</v>
+        <v>79653</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7708,21 +7708,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436206</v>
+        <v>436265</v>
       </c>
       <c r="R72" t="n">
-        <v>6786892</v>
+        <v>6786874</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7794,10 +7794,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129082550</v>
+        <v>129082610</v>
       </c>
       <c r="B73" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7805,21 +7805,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7829,10 +7829,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436361</v>
+        <v>435906</v>
       </c>
       <c r="R73" t="n">
-        <v>6786687</v>
+        <v>6786603</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7891,10 +7891,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129082534</v>
+        <v>129082639</v>
       </c>
       <c r="B74" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7902,42 +7902,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436565</v>
+        <v>436568</v>
       </c>
       <c r="R74" t="n">
-        <v>6786624</v>
+        <v>6786650</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7996,10 +7988,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129082539</v>
+        <v>129082503</v>
       </c>
       <c r="B75" t="n">
-        <v>57720</v>
+        <v>79653</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8007,42 +7999,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436069</v>
+        <v>436052</v>
       </c>
       <c r="R75" t="n">
-        <v>6786886</v>
+        <v>6786720</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8101,10 +8085,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129082540</v>
+        <v>129082634</v>
       </c>
       <c r="B76" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8112,42 +8096,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436188</v>
+        <v>436338</v>
       </c>
       <c r="R76" t="n">
-        <v>6786921</v>
+        <v>6786664</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8206,41 +8182,40 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129082579</v>
+        <v>129082534</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -8250,10 +8225,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436306</v>
+        <v>436565</v>
       </c>
       <c r="R77" t="n">
-        <v>6786960</v>
+        <v>6786624</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8294,7 +8269,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8313,10 +8287,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129082639</v>
+        <v>129082539</v>
       </c>
       <c r="B78" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8324,34 +8298,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436568</v>
+        <v>436069</v>
       </c>
       <c r="R78" t="n">
-        <v>6786650</v>
+        <v>6786886</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8410,10 +8392,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129082503</v>
+        <v>129082540</v>
       </c>
       <c r="B79" t="n">
-        <v>79653</v>
+        <v>57720</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8421,34 +8403,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436052</v>
+        <v>436188</v>
       </c>
       <c r="R79" t="n">
-        <v>6786720</v>
+        <v>6786921</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8507,45 +8497,54 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129082634</v>
+        <v>129082579</v>
       </c>
       <c r="B80" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436338</v>
+        <v>436306</v>
       </c>
       <c r="R80" t="n">
-        <v>6786664</v>
+        <v>6786960</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8586,6 +8585,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -10679,54 +10679,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129082578</v>
+        <v>129082621</v>
       </c>
       <c r="B102" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>436368</v>
+        <v>436086</v>
       </c>
       <c r="R102" t="n">
-        <v>6786971</v>
+        <v>6786788</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10767,7 +10758,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10786,7 +10776,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129082621</v>
+        <v>129082642</v>
       </c>
       <c r="B103" t="n">
         <v>79034</v>
@@ -10821,10 +10811,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>436086</v>
+        <v>436506</v>
       </c>
       <c r="R103" t="n">
-        <v>6786788</v>
+        <v>6786683</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10883,10 +10873,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129082642</v>
+        <v>129082591</v>
       </c>
       <c r="B104" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10894,21 +10884,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10918,10 +10908,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>436506</v>
+        <v>436044</v>
       </c>
       <c r="R104" t="n">
-        <v>6786683</v>
+        <v>6786741</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10980,10 +10970,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129082591</v>
+        <v>129082650</v>
       </c>
       <c r="B105" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10991,21 +10981,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11015,10 +11005,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>436044</v>
+        <v>436235</v>
       </c>
       <c r="R105" t="n">
-        <v>6786741</v>
+        <v>6786944</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11077,10 +11067,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129082650</v>
+        <v>129082532</v>
       </c>
       <c r="B106" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11088,34 +11078,42 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>436235</v>
+        <v>436295</v>
       </c>
       <c r="R106" t="n">
-        <v>6786944</v>
+        <v>6786848</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11174,7 +11172,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129082532</v>
+        <v>129082531</v>
       </c>
       <c r="B107" t="n">
         <v>57720</v>
@@ -11217,10 +11215,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436295</v>
+        <v>436246</v>
       </c>
       <c r="R107" t="n">
-        <v>6786848</v>
+        <v>6786863</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11279,40 +11277,41 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129082531</v>
+        <v>129082578</v>
       </c>
       <c r="B108" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
@@ -11322,10 +11321,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>436246</v>
+        <v>436368</v>
       </c>
       <c r="R108" t="n">
-        <v>6786863</v>
+        <v>6786971</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11366,6 +11365,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -12160,10 +12160,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129082633</v>
+        <v>129082554</v>
       </c>
       <c r="B117" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12171,21 +12171,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12195,10 +12195,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>436347</v>
+        <v>436096</v>
       </c>
       <c r="R117" t="n">
-        <v>6786689</v>
+        <v>6786876</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12471,54 +12471,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129082586</v>
+        <v>129082633</v>
       </c>
       <c r="B120" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>435931</v>
+        <v>436347</v>
       </c>
       <c r="R120" t="n">
-        <v>6786572</v>
+        <v>6786689</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12559,7 +12550,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12578,7 +12568,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129082580</v>
+        <v>129082586</v>
       </c>
       <c r="B121" t="n">
         <v>8450</v>
@@ -12622,10 +12612,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>436280</v>
+        <v>435931</v>
       </c>
       <c r="R121" t="n">
-        <v>6786936</v>
+        <v>6786572</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12685,45 +12675,54 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129082554</v>
+        <v>129082580</v>
       </c>
       <c r="B122" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>436096</v>
+        <v>436280</v>
       </c>
       <c r="R122" t="n">
-        <v>6786876</v>
+        <v>6786936</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12764,6 +12763,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12782,45 +12782,54 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129082618</v>
+        <v>129082563</v>
       </c>
       <c r="B123" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>436027</v>
+        <v>436055</v>
       </c>
       <c r="R123" t="n">
-        <v>6786735</v>
+        <v>6786776</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12861,6 +12870,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12879,45 +12889,54 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129082598</v>
+        <v>129082565</v>
       </c>
       <c r="B124" t="n">
-        <v>78791</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>436107</v>
+        <v>436230</v>
       </c>
       <c r="R124" t="n">
-        <v>6786875</v>
+        <v>6786855</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12958,6 +12977,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -12976,7 +12996,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129082613</v>
+        <v>129082618</v>
       </c>
       <c r="B125" t="n">
         <v>79034</v>
@@ -13011,10 +13031,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>435886</v>
+        <v>436027</v>
       </c>
       <c r="R125" t="n">
-        <v>6786666</v>
+        <v>6786735</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13073,54 +13093,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129082563</v>
+        <v>129082598</v>
       </c>
       <c r="B126" t="n">
-        <v>8450</v>
+        <v>78791</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436055</v>
+        <v>436107</v>
       </c>
       <c r="R126" t="n">
-        <v>6786776</v>
+        <v>6786875</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13161,7 +13172,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13180,54 +13190,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129082565</v>
+        <v>129082613</v>
       </c>
       <c r="B127" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>436230</v>
+        <v>435886</v>
       </c>
       <c r="R127" t="n">
-        <v>6786855</v>
+        <v>6786666</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13268,7 +13269,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49064-2025 artfynd.xlsx
+++ b/artfynd/A 49064-2025 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129082641</v>
+        <v>129082570</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436537</v>
+        <v>436428</v>
       </c>
       <c r="R2" t="n">
-        <v>6786684</v>
+        <v>6786577</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129082659</v>
+        <v>129082641</v>
       </c>
       <c r="B3" t="n">
         <v>79034</v>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435974</v>
+        <v>436537</v>
       </c>
       <c r="R3" t="n">
-        <v>6786534</v>
+        <v>6786684</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129082637</v>
+        <v>129082659</v>
       </c>
       <c r="B4" t="n">
         <v>79034</v>
@@ -904,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436410</v>
+        <v>435974</v>
       </c>
       <c r="R4" t="n">
-        <v>6786560</v>
+        <v>6786534</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,54 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129082570</v>
+        <v>129082637</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436428</v>
+        <v>436410</v>
       </c>
       <c r="R5" t="n">
-        <v>6786577</v>
+        <v>6786560</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,7 +1055,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129082537</v>
+        <v>129082614</v>
       </c>
       <c r="B22" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2694,42 +2694,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436399</v>
+        <v>435889</v>
       </c>
       <c r="R22" t="n">
-        <v>6786867</v>
+        <v>6786670</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2788,7 +2780,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129082614</v>
+        <v>129082640</v>
       </c>
       <c r="B23" t="n">
         <v>79034</v>
@@ -2823,10 +2815,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435889</v>
+        <v>436530</v>
       </c>
       <c r="R23" t="n">
-        <v>6786670</v>
+        <v>6786657</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2885,10 +2877,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129082640</v>
+        <v>129082537</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2896,34 +2888,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436530</v>
+        <v>436399</v>
       </c>
       <c r="R24" t="n">
-        <v>6786657</v>
+        <v>6786867</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129082504</v>
+        <v>129082524</v>
       </c>
       <c r="B26" t="n">
-        <v>79653</v>
+        <v>57883</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3090,34 +3090,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436031</v>
+        <v>436189</v>
       </c>
       <c r="R26" t="n">
-        <v>6786744</v>
+        <v>6786920</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3176,45 +3184,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129082636</v>
+        <v>129082562</v>
       </c>
       <c r="B27" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436431</v>
+        <v>436015</v>
       </c>
       <c r="R27" t="n">
-        <v>6786583</v>
+        <v>6786713</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3255,6 +3272,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3273,7 +3291,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129082505</v>
+        <v>129082504</v>
       </c>
       <c r="B28" t="n">
         <v>79653</v>
@@ -3308,10 +3326,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436095</v>
+        <v>436031</v>
       </c>
       <c r="R28" t="n">
-        <v>6786747</v>
+        <v>6786744</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3370,7 +3388,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129082653</v>
+        <v>129082636</v>
       </c>
       <c r="B29" t="n">
         <v>79034</v>
@@ -3399,19 +3417,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436092</v>
+        <v>436431</v>
       </c>
       <c r="R29" t="n">
-        <v>6786889</v>
+        <v>6786583</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3452,7 +3467,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3471,7 +3485,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129082512</v>
+        <v>129082505</v>
       </c>
       <c r="B30" t="n">
         <v>79653</v>
@@ -3506,10 +3520,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436428</v>
+        <v>436095</v>
       </c>
       <c r="R30" t="n">
-        <v>6786809</v>
+        <v>6786747</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3568,10 +3582,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129082589</v>
+        <v>129082653</v>
       </c>
       <c r="B31" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3579,34 +3593,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436033</v>
+        <v>436092</v>
       </c>
       <c r="R31" t="n">
-        <v>6786758</v>
+        <v>6786889</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3647,6 +3664,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3665,10 +3683,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129082524</v>
+        <v>129082512</v>
       </c>
       <c r="B32" t="n">
-        <v>57883</v>
+        <v>79653</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3676,42 +3694,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436189</v>
+        <v>436428</v>
       </c>
       <c r="R32" t="n">
-        <v>6786920</v>
+        <v>6786809</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3770,54 +3780,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129082562</v>
+        <v>129082589</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>78791</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436015</v>
+        <v>436033</v>
       </c>
       <c r="R33" t="n">
-        <v>6786713</v>
+        <v>6786758</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3858,7 +3859,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3877,10 +3877,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129082662</v>
+        <v>129082538</v>
       </c>
       <c r="B34" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3888,34 +3888,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435932</v>
+        <v>436141</v>
       </c>
       <c r="R34" t="n">
-        <v>6786581</v>
+        <v>6786882</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3974,10 +3982,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129082612</v>
+        <v>129082533</v>
       </c>
       <c r="B35" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3985,34 +3993,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435883</v>
+        <v>436445</v>
       </c>
       <c r="R35" t="n">
-        <v>6786641</v>
+        <v>6786610</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4071,45 +4087,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129082646</v>
+        <v>129082588</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>58093</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436400</v>
+        <v>435979</v>
       </c>
       <c r="R36" t="n">
-        <v>6786855</v>
+        <v>6786531</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4168,10 +4192,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129082538</v>
+        <v>129082543</v>
       </c>
       <c r="B37" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4179,42 +4203,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436141</v>
+        <v>436027</v>
       </c>
       <c r="R37" t="n">
-        <v>6786882</v>
+        <v>6786747</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4273,10 +4289,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129082533</v>
+        <v>129082551</v>
       </c>
       <c r="B38" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4284,42 +4300,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436445</v>
+        <v>436436</v>
       </c>
       <c r="R38" t="n">
-        <v>6786610</v>
+        <v>6786563</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4378,10 +4386,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129082543</v>
+        <v>129082662</v>
       </c>
       <c r="B39" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4389,21 +4397,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4413,10 +4421,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436027</v>
+        <v>435932</v>
       </c>
       <c r="R39" t="n">
-        <v>6786747</v>
+        <v>6786581</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4475,10 +4483,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129082551</v>
+        <v>129082612</v>
       </c>
       <c r="B40" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4486,21 +4494,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4510,10 +4518,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436436</v>
+        <v>435883</v>
       </c>
       <c r="R40" t="n">
-        <v>6786563</v>
+        <v>6786641</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4572,53 +4580,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129082588</v>
+        <v>129082646</v>
       </c>
       <c r="B41" t="n">
-        <v>58093</v>
+        <v>79034</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435979</v>
+        <v>436400</v>
       </c>
       <c r="R41" t="n">
-        <v>6786531</v>
+        <v>6786855</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5279,41 +5279,40 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129082567</v>
+        <v>129082529</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5323,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436312</v>
+        <v>436057</v>
       </c>
       <c r="R48" t="n">
-        <v>6786810</v>
+        <v>6786761</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5367,7 +5366,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5386,43 +5384,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129082585</v>
+        <v>129082648</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5430,10 +5422,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435948</v>
+        <v>436353</v>
       </c>
       <c r="R49" t="n">
-        <v>6786565</v>
+        <v>6786940</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5493,7 +5485,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129082648</v>
+        <v>129082611</v>
       </c>
       <c r="B50" t="n">
         <v>79034</v>
@@ -5522,19 +5514,16 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436353</v>
+        <v>435898</v>
       </c>
       <c r="R50" t="n">
-        <v>6786940</v>
+        <v>6786619</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5575,7 +5564,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5594,7 +5582,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129082611</v>
+        <v>129082624</v>
       </c>
       <c r="B51" t="n">
         <v>79034</v>
@@ -5629,10 +5617,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435898</v>
+        <v>436138</v>
       </c>
       <c r="R51" t="n">
-        <v>6786619</v>
+        <v>6786811</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5691,7 +5679,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129082624</v>
+        <v>129082655</v>
       </c>
       <c r="B52" t="n">
         <v>79034</v>
@@ -5726,10 +5714,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436138</v>
+        <v>436020</v>
       </c>
       <c r="R52" t="n">
-        <v>6786811</v>
+        <v>6786856</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5788,45 +5776,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129082655</v>
+        <v>129082567</v>
       </c>
       <c r="B53" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436020</v>
+        <v>436312</v>
       </c>
       <c r="R53" t="n">
-        <v>6786856</v>
+        <v>6786810</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5867,6 +5864,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5885,40 +5883,41 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129082529</v>
+        <v>129082585</v>
       </c>
       <c r="B54" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -5928,10 +5927,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>436057</v>
+        <v>435948</v>
       </c>
       <c r="R54" t="n">
-        <v>6786761</v>
+        <v>6786565</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5972,6 +5971,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5990,10 +5990,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129082647</v>
+        <v>129082555</v>
       </c>
       <c r="B55" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6001,34 +6001,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436372</v>
+        <v>436072</v>
       </c>
       <c r="R55" t="n">
-        <v>6786946</v>
+        <v>6786886</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6069,6 +6072,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6087,7 +6091,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129082656</v>
+        <v>129082647</v>
       </c>
       <c r="B56" t="n">
         <v>79034</v>
@@ -6122,10 +6126,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435996</v>
+        <v>436372</v>
       </c>
       <c r="R56" t="n">
-        <v>6786755</v>
+        <v>6786946</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6184,54 +6188,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129082577</v>
+        <v>129082656</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>436381</v>
+        <v>435996</v>
       </c>
       <c r="R57" t="n">
-        <v>6786936</v>
+        <v>6786755</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6272,7 +6267,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6291,7 +6285,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129082564</v>
+        <v>129082577</v>
       </c>
       <c r="B58" t="n">
         <v>8450</v>
@@ -6325,7 +6319,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6335,10 +6329,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>436166</v>
+        <v>436381</v>
       </c>
       <c r="R58" t="n">
-        <v>6786846</v>
+        <v>6786936</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6398,37 +6392,43 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129082555</v>
+        <v>129082564</v>
       </c>
       <c r="B59" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>436072</v>
+        <v>436166</v>
       </c>
       <c r="R59" t="n">
-        <v>6786886</v>
+        <v>6786846</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7291,40 +7291,41 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129082528</v>
+        <v>129082572</v>
       </c>
       <c r="B68" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -7334,10 +7335,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436042</v>
+        <v>436553</v>
       </c>
       <c r="R68" t="n">
-        <v>6786785</v>
+        <v>6786640</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7378,6 +7379,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7396,54 +7398,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129082572</v>
+        <v>129082507</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>79653</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>436553</v>
+        <v>436265</v>
       </c>
       <c r="R69" t="n">
-        <v>6786640</v>
+        <v>6786874</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7484,7 +7477,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7503,10 +7495,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129082552</v>
+        <v>129082610</v>
       </c>
       <c r="B70" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7514,21 +7506,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7538,10 +7530,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436206</v>
+        <v>435906</v>
       </c>
       <c r="R70" t="n">
-        <v>6786892</v>
+        <v>6786603</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7600,10 +7592,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129082550</v>
+        <v>129082528</v>
       </c>
       <c r="B71" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7611,34 +7603,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436361</v>
+        <v>436042</v>
       </c>
       <c r="R71" t="n">
-        <v>6786687</v>
+        <v>6786785</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129082507</v>
+        <v>129082552</v>
       </c>
       <c r="B72" t="n">
-        <v>79653</v>
+        <v>78792</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7708,21 +7708,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436265</v>
+        <v>436206</v>
       </c>
       <c r="R72" t="n">
-        <v>6786874</v>
+        <v>6786892</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7794,10 +7794,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129082610</v>
+        <v>129082550</v>
       </c>
       <c r="B73" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7805,21 +7805,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7829,10 +7829,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>435906</v>
+        <v>436361</v>
       </c>
       <c r="R73" t="n">
-        <v>6786603</v>
+        <v>6786687</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7891,45 +7891,54 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129082639</v>
+        <v>129082579</v>
       </c>
       <c r="B74" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436568</v>
+        <v>436306</v>
       </c>
       <c r="R74" t="n">
-        <v>6786650</v>
+        <v>6786960</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7970,6 +7979,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7988,10 +7998,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129082503</v>
+        <v>129082639</v>
       </c>
       <c r="B75" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7999,21 +8009,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8023,10 +8033,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436052</v>
+        <v>436568</v>
       </c>
       <c r="R75" t="n">
-        <v>6786720</v>
+        <v>6786650</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8085,10 +8095,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129082634</v>
+        <v>129082503</v>
       </c>
       <c r="B76" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8096,21 +8106,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8120,10 +8130,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436338</v>
+        <v>436052</v>
       </c>
       <c r="R76" t="n">
-        <v>6786664</v>
+        <v>6786720</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8182,10 +8192,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129082534</v>
+        <v>129082634</v>
       </c>
       <c r="B77" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8193,42 +8203,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436565</v>
+        <v>436338</v>
       </c>
       <c r="R77" t="n">
-        <v>6786624</v>
+        <v>6786664</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8287,7 +8289,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129082539</v>
+        <v>129082534</v>
       </c>
       <c r="B78" t="n">
         <v>57720</v>
@@ -8320,7 +8322,7 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -8330,10 +8332,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436069</v>
+        <v>436565</v>
       </c>
       <c r="R78" t="n">
-        <v>6786886</v>
+        <v>6786624</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8392,7 +8394,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129082540</v>
+        <v>129082539</v>
       </c>
       <c r="B79" t="n">
         <v>57720</v>
@@ -8425,7 +8427,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -8435,10 +8437,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436188</v>
+        <v>436069</v>
       </c>
       <c r="R79" t="n">
-        <v>6786921</v>
+        <v>6786886</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8497,41 +8499,40 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129082579</v>
+        <v>129082540</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8541,10 +8542,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436306</v>
+        <v>436188</v>
       </c>
       <c r="R80" t="n">
-        <v>6786960</v>
+        <v>6786921</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8585,7 +8586,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8992,7 +8992,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129082617</v>
+        <v>129082667</v>
       </c>
       <c r="B85" t="n">
         <v>79034</v>
@@ -9027,10 +9027,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>436010</v>
+        <v>435965</v>
       </c>
       <c r="R85" t="n">
-        <v>6786752</v>
+        <v>6786476</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9089,45 +9089,53 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129082667</v>
+        <v>129082521</v>
       </c>
       <c r="B86" t="n">
-        <v>79034</v>
+        <v>56913</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>435965</v>
+        <v>436093</v>
       </c>
       <c r="R86" t="n">
-        <v>6786476</v>
+        <v>6786769</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9186,53 +9194,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129082521</v>
+        <v>129082617</v>
       </c>
       <c r="B87" t="n">
-        <v>56913</v>
+        <v>79034</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>436093</v>
+        <v>436010</v>
       </c>
       <c r="R87" t="n">
-        <v>6786769</v>
+        <v>6786752</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9291,45 +9291,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129082654</v>
+        <v>129082671</v>
       </c>
       <c r="B88" t="n">
-        <v>79034</v>
+        <v>92816</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>436054</v>
+        <v>436349</v>
       </c>
       <c r="R88" t="n">
-        <v>6786881</v>
+        <v>6786689</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9370,6 +9373,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9388,7 +9392,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129082625</v>
+        <v>129082654</v>
       </c>
       <c r="B89" t="n">
         <v>79034</v>
@@ -9423,10 +9427,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>436202</v>
+        <v>436054</v>
       </c>
       <c r="R89" t="n">
-        <v>6786849</v>
+        <v>6786881</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9485,7 +9489,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129082665</v>
+        <v>129082625</v>
       </c>
       <c r="B90" t="n">
         <v>79034</v>
@@ -9520,10 +9524,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436330</v>
+        <v>436202</v>
       </c>
       <c r="R90" t="n">
-        <v>6786736</v>
+        <v>6786849</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9582,7 +9586,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129082606</v>
+        <v>129082665</v>
       </c>
       <c r="B91" t="n">
         <v>79034</v>
@@ -9617,10 +9621,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>435970</v>
+        <v>436330</v>
       </c>
       <c r="R91" t="n">
-        <v>6786458</v>
+        <v>6786736</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9679,7 +9683,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129082619</v>
+        <v>129082606</v>
       </c>
       <c r="B92" t="n">
         <v>79034</v>
@@ -9714,10 +9718,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>436034</v>
+        <v>435970</v>
       </c>
       <c r="R92" t="n">
-        <v>6786743</v>
+        <v>6786458</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9776,7 +9780,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129082616</v>
+        <v>129082619</v>
       </c>
       <c r="B93" t="n">
         <v>79034</v>
@@ -9811,10 +9815,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436012</v>
+        <v>436034</v>
       </c>
       <c r="R93" t="n">
-        <v>6786734</v>
+        <v>6786743</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9873,10 +9877,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129082595</v>
+        <v>129082616</v>
       </c>
       <c r="B94" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9884,21 +9888,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9908,10 +9912,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436361</v>
+        <v>436012</v>
       </c>
       <c r="R94" t="n">
-        <v>6786688</v>
+        <v>6786734</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9970,7 +9974,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129082594</v>
+        <v>129082595</v>
       </c>
       <c r="B95" t="n">
         <v>78791</v>
@@ -10005,10 +10009,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436339</v>
+        <v>436361</v>
       </c>
       <c r="R95" t="n">
-        <v>6786747</v>
+        <v>6786688</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10067,48 +10071,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129082671</v>
+        <v>129082594</v>
       </c>
       <c r="B96" t="n">
-        <v>92811</v>
+        <v>78791</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436349</v>
+        <v>436339</v>
       </c>
       <c r="R96" t="n">
-        <v>6786689</v>
+        <v>6786747</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10149,7 +10150,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10273,40 +10273,41 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129082525</v>
+        <v>129082582</v>
       </c>
       <c r="B98" t="n">
-        <v>57883</v>
+        <v>8450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -10316,10 +10317,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>435948</v>
+        <v>436138</v>
       </c>
       <c r="R98" t="n">
-        <v>6786586</v>
+        <v>6786894</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10360,6 +10361,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10378,41 +10380,40 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129082582</v>
+        <v>129082525</v>
       </c>
       <c r="B99" t="n">
-        <v>8450</v>
+        <v>57883</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -10422,10 +10423,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436138</v>
+        <v>435948</v>
       </c>
       <c r="R99" t="n">
-        <v>6786894</v>
+        <v>6786586</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10466,7 +10467,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11578,7 +11578,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129082632</v>
+        <v>129082609</v>
       </c>
       <c r="B111" t="n">
         <v>79034</v>
@@ -11613,10 +11613,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>436334</v>
+        <v>435914</v>
       </c>
       <c r="R111" t="n">
-        <v>6786685</v>
+        <v>6786598</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11675,10 +11675,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129082609</v>
+        <v>129082592</v>
       </c>
       <c r="B112" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11686,21 +11686,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11710,10 +11710,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>435914</v>
+        <v>436095</v>
       </c>
       <c r="R112" t="n">
-        <v>6786598</v>
+        <v>6786744</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11772,10 +11772,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129082592</v>
+        <v>129082627</v>
       </c>
       <c r="B113" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11783,21 +11783,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11807,10 +11807,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>436095</v>
+        <v>436246</v>
       </c>
       <c r="R113" t="n">
-        <v>6786744</v>
+        <v>6786881</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11869,7 +11869,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129082627</v>
+        <v>129082668</v>
       </c>
       <c r="B114" t="n">
         <v>79034</v>
@@ -11904,10 +11904,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>436246</v>
+        <v>435933</v>
       </c>
       <c r="R114" t="n">
-        <v>6786881</v>
+        <v>6786585</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11966,7 +11966,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129082668</v>
+        <v>129082632</v>
       </c>
       <c r="B115" t="n">
         <v>79034</v>
@@ -12001,10 +12001,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>435933</v>
+        <v>436334</v>
       </c>
       <c r="R115" t="n">
-        <v>6786585</v>
+        <v>6786685</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12063,45 +12063,54 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129082645</v>
+        <v>129082560</v>
       </c>
       <c r="B116" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>436405</v>
+        <v>435897</v>
       </c>
       <c r="R116" t="n">
-        <v>6786825</v>
+        <v>6786676</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12142,6 +12151,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12160,45 +12170,54 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129082554</v>
+        <v>129082576</v>
       </c>
       <c r="B117" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>436096</v>
+        <v>436417</v>
       </c>
       <c r="R117" t="n">
-        <v>6786876</v>
+        <v>6786827</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12239,6 +12258,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12257,7 +12277,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129082560</v>
+        <v>129082586</v>
       </c>
       <c r="B118" t="n">
         <v>8450</v>
@@ -12301,10 +12321,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>435897</v>
+        <v>435931</v>
       </c>
       <c r="R118" t="n">
-        <v>6786676</v>
+        <v>6786572</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12364,7 +12384,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129082576</v>
+        <v>129082580</v>
       </c>
       <c r="B119" t="n">
         <v>8450</v>
@@ -12408,10 +12428,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>436417</v>
+        <v>436280</v>
       </c>
       <c r="R119" t="n">
-        <v>6786827</v>
+        <v>6786936</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12471,7 +12491,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129082633</v>
+        <v>129082645</v>
       </c>
       <c r="B120" t="n">
         <v>79034</v>
@@ -12506,10 +12526,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>436347</v>
+        <v>436405</v>
       </c>
       <c r="R120" t="n">
-        <v>6786689</v>
+        <v>6786825</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12568,54 +12588,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129082586</v>
+        <v>129082633</v>
       </c>
       <c r="B121" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>435931</v>
+        <v>436347</v>
       </c>
       <c r="R121" t="n">
-        <v>6786572</v>
+        <v>6786689</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12656,7 +12667,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12675,54 +12685,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129082580</v>
+        <v>129082554</v>
       </c>
       <c r="B122" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>436280</v>
+        <v>436096</v>
       </c>
       <c r="R122" t="n">
-        <v>6786936</v>
+        <v>6786876</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12763,7 +12764,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12782,54 +12782,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129082563</v>
+        <v>129082618</v>
       </c>
       <c r="B123" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>436055</v>
+        <v>436027</v>
       </c>
       <c r="R123" t="n">
-        <v>6786776</v>
+        <v>6786735</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12870,7 +12861,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12889,54 +12879,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129082565</v>
+        <v>129082598</v>
       </c>
       <c r="B124" t="n">
-        <v>8450</v>
+        <v>78791</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>436230</v>
+        <v>436107</v>
       </c>
       <c r="R124" t="n">
-        <v>6786855</v>
+        <v>6786875</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12977,7 +12958,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -12996,7 +12976,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129082618</v>
+        <v>129082613</v>
       </c>
       <c r="B125" t="n">
         <v>79034</v>
@@ -13031,10 +13011,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>436027</v>
+        <v>435886</v>
       </c>
       <c r="R125" t="n">
-        <v>6786735</v>
+        <v>6786666</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13093,45 +13073,54 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129082598</v>
+        <v>129082563</v>
       </c>
       <c r="B126" t="n">
-        <v>78791</v>
+        <v>8450</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436107</v>
+        <v>436055</v>
       </c>
       <c r="R126" t="n">
-        <v>6786875</v>
+        <v>6786776</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13172,6 +13161,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13190,45 +13180,54 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129082613</v>
+        <v>129082565</v>
       </c>
       <c r="B127" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>435886</v>
+        <v>436230</v>
       </c>
       <c r="R127" t="n">
-        <v>6786666</v>
+        <v>6786855</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13269,6 +13268,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13287,54 +13287,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129082558</v>
+        <v>129082596</v>
       </c>
       <c r="B128" t="n">
-        <v>8450</v>
+        <v>78791</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>435909</v>
+        <v>436432</v>
       </c>
       <c r="R128" t="n">
-        <v>6786616</v>
+        <v>6786558</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13375,7 +13366,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13394,54 +13384,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129082583</v>
+        <v>129082626</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>436011</v>
+        <v>436240</v>
       </c>
       <c r="R129" t="n">
-        <v>6786844</v>
+        <v>6786833</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13482,7 +13463,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13501,10 +13481,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129082547</v>
+        <v>129082664</v>
       </c>
       <c r="B130" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13512,21 +13492,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13536,10 +13516,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436172</v>
+        <v>436029</v>
       </c>
       <c r="R130" t="n">
-        <v>6786825</v>
+        <v>6786750</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13598,10 +13578,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129082596</v>
+        <v>129082535</v>
       </c>
       <c r="B131" t="n">
-        <v>78791</v>
+        <v>57720</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13609,34 +13589,42 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>436432</v>
+        <v>436575</v>
       </c>
       <c r="R131" t="n">
-        <v>6786558</v>
+        <v>6786632</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13695,45 +13683,54 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129082626</v>
+        <v>129082558</v>
       </c>
       <c r="B132" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>436240</v>
+        <v>435909</v>
       </c>
       <c r="R132" t="n">
-        <v>6786833</v>
+        <v>6786616</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13774,6 +13771,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13792,45 +13790,54 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129082664</v>
+        <v>129082583</v>
       </c>
       <c r="B133" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>436029</v>
+        <v>436011</v>
       </c>
       <c r="R133" t="n">
-        <v>6786750</v>
+        <v>6786844</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13871,6 +13878,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -13889,10 +13897,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129082535</v>
+        <v>129082547</v>
       </c>
       <c r="B134" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13900,42 +13908,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>436575</v>
+        <v>436172</v>
       </c>
       <c r="R134" t="n">
-        <v>6786632</v>
+        <v>6786825</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>

--- a/artfynd/A 49064-2025 artfynd.xlsx
+++ b/artfynd/A 49064-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129082641</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129082659</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129082637</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129082546</v>
+        <v>129082544</v>
       </c>
       <c r="B6" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436092</v>
+        <v>436044</v>
       </c>
       <c r="R6" t="n">
-        <v>6786744</v>
+        <v>6786741</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129082544</v>
+        <v>129082546</v>
       </c>
       <c r="B7" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436044</v>
+        <v>436092</v>
       </c>
       <c r="R7" t="n">
-        <v>6786741</v>
+        <v>6786744</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,45 +1267,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129082651</v>
+        <v>129082575</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436254</v>
+        <v>436432</v>
       </c>
       <c r="R8" t="n">
-        <v>6786925</v>
+        <v>6786759</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,6 +1355,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1364,45 +1374,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129082638</v>
+        <v>129082574</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436456</v>
+        <v>436455</v>
       </c>
       <c r="R9" t="n">
-        <v>6786598</v>
+        <v>6786732</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1443,6 +1462,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1461,54 +1481,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129082575</v>
+        <v>129082651</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436432</v>
+        <v>436254</v>
       </c>
       <c r="R10" t="n">
-        <v>6786759</v>
+        <v>6786925</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,7 +1560,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1568,54 +1578,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129082574</v>
+        <v>129082638</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436455</v>
+        <v>436456</v>
       </c>
       <c r="R11" t="n">
-        <v>6786732</v>
+        <v>6786598</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1656,7 +1657,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1675,45 +1675,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129082508</v>
+        <v>129082559</v>
       </c>
       <c r="B12" t="n">
-        <v>79653</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436338</v>
+        <v>435893</v>
       </c>
       <c r="R12" t="n">
-        <v>6786741</v>
+        <v>6786660</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1754,6 +1763,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1772,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129082510</v>
+        <v>129082508</v>
       </c>
       <c r="B13" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1807,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436506</v>
+        <v>436338</v>
       </c>
       <c r="R13" t="n">
-        <v>6786715</v>
+        <v>6786741</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1869,54 +1879,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129082559</v>
+        <v>129082510</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435893</v>
+        <v>436506</v>
       </c>
       <c r="R14" t="n">
-        <v>6786660</v>
+        <v>6786715</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1957,7 +1958,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>129082652</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>129082622</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>129082629</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>129082630</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2364,10 +2364,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129082522</v>
+        <v>129082568</v>
       </c>
       <c r="B19" t="n">
-        <v>56913</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2375,29 +2375,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2407,10 +2408,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436195</v>
+        <v>436409</v>
       </c>
       <c r="R19" t="n">
-        <v>6786902</v>
+        <v>6786563</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,6 +2452,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2469,7 +2471,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129082568</v>
+        <v>129082566</v>
       </c>
       <c r="B20" t="n">
         <v>8450</v>
@@ -2503,7 +2505,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2513,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436409</v>
+        <v>436258</v>
       </c>
       <c r="R20" t="n">
-        <v>6786563</v>
+        <v>6786851</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2576,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129082566</v>
+        <v>129082522</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>56913</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2587,30 +2589,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2620,10 +2621,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436258</v>
+        <v>436195</v>
       </c>
       <c r="R21" t="n">
-        <v>6786851</v>
+        <v>6786902</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,7 +2665,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129082614</v>
+        <v>129082537</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2694,34 +2694,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435889</v>
+        <v>436399</v>
       </c>
       <c r="R22" t="n">
-        <v>6786670</v>
+        <v>6786867</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2780,10 +2788,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129082640</v>
+        <v>129082549</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>78793</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2791,21 +2799,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2815,10 +2823,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436530</v>
+        <v>436322</v>
       </c>
       <c r="R23" t="n">
-        <v>6786657</v>
+        <v>6786798</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2877,10 +2885,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129082537</v>
+        <v>129082614</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2888,42 +2896,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436399</v>
+        <v>435889</v>
       </c>
       <c r="R24" t="n">
-        <v>6786867</v>
+        <v>6786670</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2982,10 +2982,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129082549</v>
+        <v>129082640</v>
       </c>
       <c r="B25" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2993,21 +2993,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436322</v>
+        <v>436530</v>
       </c>
       <c r="R25" t="n">
-        <v>6786798</v>
+        <v>6786657</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129082524</v>
+        <v>129082504</v>
       </c>
       <c r="B26" t="n">
-        <v>57883</v>
+        <v>79654</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3090,42 +3090,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436189</v>
+        <v>436031</v>
       </c>
       <c r="R26" t="n">
-        <v>6786920</v>
+        <v>6786744</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3184,54 +3176,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129082562</v>
+        <v>129082636</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436015</v>
+        <v>436431</v>
       </c>
       <c r="R27" t="n">
-        <v>6786713</v>
+        <v>6786583</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3272,7 +3255,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3291,10 +3273,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129082504</v>
+        <v>129082505</v>
       </c>
       <c r="B28" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3326,10 +3308,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436031</v>
+        <v>436095</v>
       </c>
       <c r="R28" t="n">
-        <v>6786744</v>
+        <v>6786747</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3388,10 +3370,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129082636</v>
+        <v>129082653</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3417,16 +3399,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436431</v>
+        <v>436092</v>
       </c>
       <c r="R29" t="n">
-        <v>6786583</v>
+        <v>6786889</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3467,6 +3452,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3485,10 +3471,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129082505</v>
+        <v>129082512</v>
       </c>
       <c r="B30" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3520,10 +3506,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436095</v>
+        <v>436428</v>
       </c>
       <c r="R30" t="n">
-        <v>6786747</v>
+        <v>6786809</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3582,10 +3568,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129082653</v>
+        <v>129082589</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3593,37 +3579,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436092</v>
+        <v>436033</v>
       </c>
       <c r="R31" t="n">
-        <v>6786889</v>
+        <v>6786758</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3664,7 +3647,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3683,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129082512</v>
+        <v>129082524</v>
       </c>
       <c r="B32" t="n">
-        <v>79653</v>
+        <v>57883</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3694,34 +3676,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436428</v>
+        <v>436189</v>
       </c>
       <c r="R32" t="n">
-        <v>6786809</v>
+        <v>6786920</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3780,45 +3770,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129082589</v>
+        <v>129082562</v>
       </c>
       <c r="B33" t="n">
-        <v>78791</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436033</v>
+        <v>436015</v>
       </c>
       <c r="R33" t="n">
-        <v>6786758</v>
+        <v>6786713</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3859,6 +3858,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3877,40 +3877,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129082538</v>
+        <v>129082573</v>
       </c>
       <c r="B34" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3920,10 +3921,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436141</v>
+        <v>436525</v>
       </c>
       <c r="R34" t="n">
-        <v>6786882</v>
+        <v>6786729</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3964,6 +3965,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3982,10 +3984,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129082533</v>
+        <v>129082543</v>
       </c>
       <c r="B35" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3993,42 +3995,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436445</v>
+        <v>436027</v>
       </c>
       <c r="R35" t="n">
-        <v>6786610</v>
+        <v>6786747</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4087,53 +4081,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129082588</v>
+        <v>129082551</v>
       </c>
       <c r="B36" t="n">
-        <v>58093</v>
+        <v>78793</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435979</v>
+        <v>436436</v>
       </c>
       <c r="R36" t="n">
-        <v>6786531</v>
+        <v>6786563</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4192,10 +4178,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129082543</v>
+        <v>129082662</v>
       </c>
       <c r="B37" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4203,21 +4189,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4227,10 +4213,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436027</v>
+        <v>435932</v>
       </c>
       <c r="R37" t="n">
-        <v>6786747</v>
+        <v>6786581</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4289,10 +4275,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129082551</v>
+        <v>129082612</v>
       </c>
       <c r="B38" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4300,21 +4286,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4324,10 +4310,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436436</v>
+        <v>435883</v>
       </c>
       <c r="R38" t="n">
-        <v>6786563</v>
+        <v>6786641</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4386,10 +4372,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129082662</v>
+        <v>129082646</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4421,10 +4407,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435932</v>
+        <v>436400</v>
       </c>
       <c r="R39" t="n">
-        <v>6786581</v>
+        <v>6786855</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4483,10 +4469,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129082612</v>
+        <v>129082533</v>
       </c>
       <c r="B40" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4494,34 +4480,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435883</v>
+        <v>436445</v>
       </c>
       <c r="R40" t="n">
-        <v>6786641</v>
+        <v>6786610</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4580,10 +4574,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129082646</v>
+        <v>129082538</v>
       </c>
       <c r="B41" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4591,34 +4585,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436400</v>
+        <v>436141</v>
       </c>
       <c r="R41" t="n">
-        <v>6786855</v>
+        <v>6786882</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4677,10 +4679,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129082573</v>
+        <v>129082588</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>58093</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4688,30 +4690,29 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -4721,10 +4722,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436525</v>
+        <v>435979</v>
       </c>
       <c r="R42" t="n">
-        <v>6786729</v>
+        <v>6786531</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4765,7 +4766,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4787,7 +4787,7 @@
         <v>129082590</v>
       </c>
       <c r="B43" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>129082593</v>
       </c>
       <c r="B44" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>129082663</v>
       </c>
       <c r="B45" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>129082553</v>
       </c>
       <c r="B47" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5279,10 +5279,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129082529</v>
+        <v>129082648</v>
       </c>
       <c r="B48" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5290,31 +5290,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5322,10 +5317,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436057</v>
+        <v>436353</v>
       </c>
       <c r="R48" t="n">
-        <v>6786761</v>
+        <v>6786940</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5366,6 +5361,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5384,10 +5380,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129082648</v>
+        <v>129082611</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5413,19 +5409,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436353</v>
+        <v>435898</v>
       </c>
       <c r="R49" t="n">
-        <v>6786940</v>
+        <v>6786619</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5466,7 +5459,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5485,10 +5477,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129082611</v>
+        <v>129082624</v>
       </c>
       <c r="B50" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5520,10 +5512,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435898</v>
+        <v>436138</v>
       </c>
       <c r="R50" t="n">
-        <v>6786619</v>
+        <v>6786811</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5582,10 +5574,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129082624</v>
+        <v>129082655</v>
       </c>
       <c r="B51" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5617,10 +5609,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436138</v>
+        <v>436020</v>
       </c>
       <c r="R51" t="n">
-        <v>6786811</v>
+        <v>6786856</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5679,10 +5671,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129082655</v>
+        <v>129082529</v>
       </c>
       <c r="B52" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5690,34 +5682,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436020</v>
+        <v>436057</v>
       </c>
       <c r="R52" t="n">
-        <v>6786856</v>
+        <v>6786761</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5993,7 +5993,7 @@
         <v>129082555</v>
       </c>
       <c r="B55" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>129082647</v>
       </c>
       <c r="B56" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>129082656</v>
       </c>
       <c r="B57" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>129082644</v>
       </c>
       <c r="B60" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6596,10 +6596,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129082597</v>
+        <v>129082666</v>
       </c>
       <c r="B61" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6607,21 +6607,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6631,10 +6631,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436469</v>
+        <v>436618</v>
       </c>
       <c r="R61" t="n">
-        <v>6786748</v>
+        <v>6786620</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6693,10 +6693,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129082666</v>
+        <v>129082597</v>
       </c>
       <c r="B62" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6704,21 +6704,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6728,10 +6728,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>436618</v>
+        <v>436469</v>
       </c>
       <c r="R62" t="n">
-        <v>6786620</v>
+        <v>6786748</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6793,7 +6793,7 @@
         <v>129082506</v>
       </c>
       <c r="B63" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6891,10 +6891,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129082548</v>
+        <v>129082515</v>
       </c>
       <c r="B64" t="n">
-        <v>78792</v>
+        <v>79625</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6902,34 +6902,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>436268</v>
+        <v>436075</v>
       </c>
       <c r="R64" t="n">
-        <v>6786874</v>
+        <v>6786747</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6970,6 +6973,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6988,10 +6992,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129082516</v>
+        <v>129082548</v>
       </c>
       <c r="B65" t="n">
-        <v>79624</v>
+        <v>78793</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6999,37 +7003,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>436470</v>
+        <v>436268</v>
       </c>
       <c r="R65" t="n">
-        <v>6786714</v>
+        <v>6786874</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7070,7 +7071,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7089,10 +7089,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129082545</v>
+        <v>129082516</v>
       </c>
       <c r="B66" t="n">
-        <v>78792</v>
+        <v>79625</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7100,21 +7100,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436085</v>
+        <v>436470</v>
       </c>
       <c r="R66" t="n">
-        <v>6786778</v>
+        <v>6786714</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7190,10 +7190,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129082515</v>
+        <v>129082545</v>
       </c>
       <c r="B67" t="n">
-        <v>79624</v>
+        <v>78793</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7201,21 +7201,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7228,10 +7228,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436075</v>
+        <v>436085</v>
       </c>
       <c r="R67" t="n">
-        <v>6786747</v>
+        <v>6786778</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7291,54 +7291,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129082572</v>
+        <v>129082550</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436553</v>
+        <v>436361</v>
       </c>
       <c r="R68" t="n">
-        <v>6786640</v>
+        <v>6786687</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7379,7 +7370,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7398,10 +7388,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129082507</v>
+        <v>129082552</v>
       </c>
       <c r="B69" t="n">
-        <v>79653</v>
+        <v>78793</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7409,21 +7399,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7433,10 +7423,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>436265</v>
+        <v>436206</v>
       </c>
       <c r="R69" t="n">
-        <v>6786874</v>
+        <v>6786892</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7495,10 +7485,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129082610</v>
+        <v>129082507</v>
       </c>
       <c r="B70" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7506,21 +7496,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7530,10 +7520,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435906</v>
+        <v>436265</v>
       </c>
       <c r="R70" t="n">
-        <v>6786603</v>
+        <v>6786874</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7592,10 +7582,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129082528</v>
+        <v>129082610</v>
       </c>
       <c r="B71" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7603,42 +7593,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436042</v>
+        <v>435906</v>
       </c>
       <c r="R71" t="n">
-        <v>6786785</v>
+        <v>6786603</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7697,10 +7679,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129082552</v>
+        <v>129082528</v>
       </c>
       <c r="B72" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7708,34 +7690,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436206</v>
+        <v>436042</v>
       </c>
       <c r="R72" t="n">
-        <v>6786892</v>
+        <v>6786785</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7794,45 +7784,54 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129082550</v>
+        <v>129082572</v>
       </c>
       <c r="B73" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436361</v>
+        <v>436553</v>
       </c>
       <c r="R73" t="n">
-        <v>6786687</v>
+        <v>6786640</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7873,6 +7872,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7891,41 +7891,40 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129082579</v>
+        <v>129082540</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -7935,10 +7934,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436306</v>
+        <v>436188</v>
       </c>
       <c r="R74" t="n">
-        <v>6786960</v>
+        <v>6786921</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7979,7 +7978,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7998,10 +7996,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129082639</v>
+        <v>129082534</v>
       </c>
       <c r="B75" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8009,34 +8007,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436568</v>
+        <v>436565</v>
       </c>
       <c r="R75" t="n">
-        <v>6786650</v>
+        <v>6786624</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8095,10 +8101,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129082503</v>
+        <v>129082539</v>
       </c>
       <c r="B76" t="n">
-        <v>79653</v>
+        <v>57720</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8106,34 +8112,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436052</v>
+        <v>436069</v>
       </c>
       <c r="R76" t="n">
-        <v>6786720</v>
+        <v>6786886</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8192,45 +8206,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129082634</v>
+        <v>129082579</v>
       </c>
       <c r="B77" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436338</v>
+        <v>436306</v>
       </c>
       <c r="R77" t="n">
-        <v>6786664</v>
+        <v>6786960</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8271,6 +8294,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8289,10 +8313,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129082534</v>
+        <v>129082639</v>
       </c>
       <c r="B78" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8300,42 +8324,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436565</v>
+        <v>436568</v>
       </c>
       <c r="R78" t="n">
-        <v>6786624</v>
+        <v>6786650</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8394,10 +8410,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129082539</v>
+        <v>129082503</v>
       </c>
       <c r="B79" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8405,42 +8421,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436069</v>
+        <v>436052</v>
       </c>
       <c r="R79" t="n">
-        <v>6786886</v>
+        <v>6786720</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8499,10 +8507,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129082540</v>
+        <v>129082634</v>
       </c>
       <c r="B80" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8510,42 +8518,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436188</v>
+        <v>436338</v>
       </c>
       <c r="R80" t="n">
-        <v>6786921</v>
+        <v>6786664</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8607,7 +8607,7 @@
         <v>129082620</v>
       </c>
       <c r="B81" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>129082513</v>
       </c>
       <c r="B82" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>129082635</v>
       </c>
       <c r="B83" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>129082649</v>
       </c>
       <c r="B84" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8992,10 +8992,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129082667</v>
+        <v>129082617</v>
       </c>
       <c r="B85" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9027,10 +9027,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>435965</v>
+        <v>436010</v>
       </c>
       <c r="R85" t="n">
-        <v>6786476</v>
+        <v>6786752</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9089,53 +9089,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129082521</v>
+        <v>129082667</v>
       </c>
       <c r="B86" t="n">
-        <v>56913</v>
+        <v>79035</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>436093</v>
+        <v>435965</v>
       </c>
       <c r="R86" t="n">
-        <v>6786769</v>
+        <v>6786476</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9194,45 +9186,53 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129082617</v>
+        <v>129082521</v>
       </c>
       <c r="B87" t="n">
-        <v>79034</v>
+        <v>56913</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>436010</v>
+        <v>436093</v>
       </c>
       <c r="R87" t="n">
-        <v>6786752</v>
+        <v>6786769</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9291,48 +9291,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129082671</v>
+        <v>129082625</v>
       </c>
       <c r="B88" t="n">
-        <v>92816</v>
+        <v>79035</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>436349</v>
+        <v>436202</v>
       </c>
       <c r="R88" t="n">
-        <v>6786689</v>
+        <v>6786849</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9373,7 +9370,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9392,45 +9388,48 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129082654</v>
+        <v>129082671</v>
       </c>
       <c r="B89" t="n">
-        <v>79034</v>
+        <v>92819</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>436054</v>
+        <v>436349</v>
       </c>
       <c r="R89" t="n">
-        <v>6786881</v>
+        <v>6786689</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9471,6 +9470,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9489,10 +9489,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129082625</v>
+        <v>129082654</v>
       </c>
       <c r="B90" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9524,10 +9524,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436202</v>
+        <v>436054</v>
       </c>
       <c r="R90" t="n">
-        <v>6786849</v>
+        <v>6786881</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9589,7 +9589,7 @@
         <v>129082665</v>
       </c>
       <c r="B91" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>129082606</v>
       </c>
       <c r="B92" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>129082619</v>
       </c>
       <c r="B93" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>129082616</v>
       </c>
       <c r="B94" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>129082595</v>
       </c>
       <c r="B95" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>129082594</v>
       </c>
       <c r="B96" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10168,10 +10168,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129082536</v>
+        <v>129082525</v>
       </c>
       <c r="B97" t="n">
-        <v>57720</v>
+        <v>57883</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10179,21 +10179,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10201,7 +10201,7 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -10211,10 +10211,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436544</v>
+        <v>435948</v>
       </c>
       <c r="R97" t="n">
-        <v>6786666</v>
+        <v>6786586</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10380,10 +10380,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129082525</v>
+        <v>129082556</v>
       </c>
       <c r="B99" t="n">
-        <v>57883</v>
+        <v>78793</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10391,42 +10391,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>435948</v>
+        <v>436010</v>
       </c>
       <c r="R99" t="n">
-        <v>6786586</v>
+        <v>6786852</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10488,7 +10480,7 @@
         <v>129082514</v>
       </c>
       <c r="B100" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10582,10 +10574,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129082556</v>
+        <v>129082536</v>
       </c>
       <c r="B101" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10593,34 +10585,42 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>436010</v>
+        <v>436544</v>
       </c>
       <c r="R101" t="n">
-        <v>6786852</v>
+        <v>6786666</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10682,7 +10682,7 @@
         <v>129082621</v>
       </c>
       <c r="B102" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>129082642</v>
       </c>
       <c r="B103" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>129082591</v>
       </c>
       <c r="B104" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>129082650</v>
       </c>
       <c r="B105" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129082532</v>
+        <v>129082531</v>
       </c>
       <c r="B106" t="n">
         <v>57720</v>
@@ -11110,10 +11110,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>436295</v>
+        <v>436246</v>
       </c>
       <c r="R106" t="n">
-        <v>6786848</v>
+        <v>6786863</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11172,7 +11172,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129082531</v>
+        <v>129082532</v>
       </c>
       <c r="B107" t="n">
         <v>57720</v>
@@ -11215,10 +11215,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436246</v>
+        <v>436295</v>
       </c>
       <c r="R107" t="n">
-        <v>6786863</v>
+        <v>6786848</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11384,10 +11384,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129082509</v>
+        <v>129082628</v>
       </c>
       <c r="B109" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11395,21 +11395,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11419,10 +11419,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>436482</v>
+        <v>436327</v>
       </c>
       <c r="R109" t="n">
-        <v>6786616</v>
+        <v>6786767</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11481,10 +11481,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129082628</v>
+        <v>129082632</v>
       </c>
       <c r="B110" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11516,10 +11516,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>436327</v>
+        <v>436334</v>
       </c>
       <c r="R110" t="n">
-        <v>6786767</v>
+        <v>6786685</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11581,7 +11581,7 @@
         <v>129082609</v>
       </c>
       <c r="B111" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>129082592</v>
       </c>
       <c r="B112" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>129082627</v>
       </c>
       <c r="B113" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11869,10 +11869,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129082668</v>
+        <v>129082509</v>
       </c>
       <c r="B114" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11880,21 +11880,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11904,10 +11904,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>435933</v>
+        <v>436482</v>
       </c>
       <c r="R114" t="n">
-        <v>6786585</v>
+        <v>6786616</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11966,10 +11966,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129082632</v>
+        <v>129082668</v>
       </c>
       <c r="B115" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12001,10 +12001,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>436334</v>
+        <v>435933</v>
       </c>
       <c r="R115" t="n">
-        <v>6786685</v>
+        <v>6786585</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12063,54 +12063,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129082560</v>
+        <v>129082645</v>
       </c>
       <c r="B116" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>435897</v>
+        <v>436405</v>
       </c>
       <c r="R116" t="n">
-        <v>6786676</v>
+        <v>6786825</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12151,7 +12142,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12170,54 +12160,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129082576</v>
+        <v>129082633</v>
       </c>
       <c r="B117" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>436417</v>
+        <v>436347</v>
       </c>
       <c r="R117" t="n">
-        <v>6786827</v>
+        <v>6786689</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12258,7 +12239,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12277,54 +12257,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129082586</v>
+        <v>129082554</v>
       </c>
       <c r="B118" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>435931</v>
+        <v>436096</v>
       </c>
       <c r="R118" t="n">
-        <v>6786572</v>
+        <v>6786876</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12365,7 +12336,6 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12384,7 +12354,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129082580</v>
+        <v>129082560</v>
       </c>
       <c r="B119" t="n">
         <v>8450</v>
@@ -12428,10 +12398,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>436280</v>
+        <v>435897</v>
       </c>
       <c r="R119" t="n">
-        <v>6786936</v>
+        <v>6786676</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12491,45 +12461,54 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129082645</v>
+        <v>129082576</v>
       </c>
       <c r="B120" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>436405</v>
+        <v>436417</v>
       </c>
       <c r="R120" t="n">
-        <v>6786825</v>
+        <v>6786827</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12570,6 +12549,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12588,45 +12568,54 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129082633</v>
+        <v>129082586</v>
       </c>
       <c r="B121" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>436347</v>
+        <v>435931</v>
       </c>
       <c r="R121" t="n">
-        <v>6786689</v>
+        <v>6786572</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12667,6 +12656,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12685,45 +12675,54 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129082554</v>
+        <v>129082580</v>
       </c>
       <c r="B122" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>436096</v>
+        <v>436280</v>
       </c>
       <c r="R122" t="n">
-        <v>6786876</v>
+        <v>6786936</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12764,6 +12763,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12785,7 +12785,7 @@
         <v>129082618</v>
       </c>
       <c r="B123" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>129082598</v>
       </c>
       <c r="B124" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>129082613</v>
       </c>
       <c r="B125" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13287,10 +13287,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129082596</v>
+        <v>129082535</v>
       </c>
       <c r="B128" t="n">
-        <v>78791</v>
+        <v>57720</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13298,34 +13298,42 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>436432</v>
+        <v>436575</v>
       </c>
       <c r="R128" t="n">
-        <v>6786558</v>
+        <v>6786632</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13384,45 +13392,54 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129082626</v>
+        <v>129082558</v>
       </c>
       <c r="B129" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>436240</v>
+        <v>435909</v>
       </c>
       <c r="R129" t="n">
-        <v>6786833</v>
+        <v>6786616</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13463,6 +13480,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13481,45 +13499,54 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129082664</v>
+        <v>129082583</v>
       </c>
       <c r="B130" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436029</v>
+        <v>436011</v>
       </c>
       <c r="R130" t="n">
-        <v>6786750</v>
+        <v>6786844</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13560,6 +13587,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13578,10 +13606,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129082535</v>
+        <v>129082547</v>
       </c>
       <c r="B131" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13589,42 +13617,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>436575</v>
+        <v>436172</v>
       </c>
       <c r="R131" t="n">
-        <v>6786632</v>
+        <v>6786825</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13683,54 +13703,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129082558</v>
+        <v>129082596</v>
       </c>
       <c r="B132" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>435909</v>
+        <v>436432</v>
       </c>
       <c r="R132" t="n">
-        <v>6786616</v>
+        <v>6786558</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13771,7 +13782,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13790,54 +13800,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129082583</v>
+        <v>129082626</v>
       </c>
       <c r="B133" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>436011</v>
+        <v>436240</v>
       </c>
       <c r="R133" t="n">
-        <v>6786844</v>
+        <v>6786833</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13878,7 +13879,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -13897,10 +13897,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129082547</v>
+        <v>129082664</v>
       </c>
       <c r="B134" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13908,21 +13908,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13932,10 +13932,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>436172</v>
+        <v>436029</v>
       </c>
       <c r="R134" t="n">
-        <v>6786825</v>
+        <v>6786750</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>

--- a/artfynd/A 49064-2025 artfynd.xlsx
+++ b/artfynd/A 49064-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129082570</v>
+        <v>129082641</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436428</v>
+        <v>436537</v>
       </c>
       <c r="R2" t="n">
-        <v>6786577</v>
+        <v>6786684</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129082641</v>
+        <v>129082659</v>
       </c>
       <c r="B3" t="n">
         <v>79035</v>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436537</v>
+        <v>435974</v>
       </c>
       <c r="R3" t="n">
-        <v>6786684</v>
+        <v>6786534</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129082659</v>
+        <v>129082637</v>
       </c>
       <c r="B4" t="n">
         <v>79035</v>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435974</v>
+        <v>436410</v>
       </c>
       <c r="R4" t="n">
-        <v>6786534</v>
+        <v>6786560</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129082637</v>
+        <v>129082544</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436410</v>
+        <v>436044</v>
       </c>
       <c r="R5" t="n">
-        <v>6786560</v>
+        <v>6786741</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129082544</v>
+        <v>129082546</v>
       </c>
       <c r="B6" t="n">
         <v>78793</v>
@@ -1108,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436044</v>
+        <v>436092</v>
       </c>
       <c r="R6" t="n">
-        <v>6786741</v>
+        <v>6786744</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,45 +1160,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129082546</v>
+        <v>129082570</v>
       </c>
       <c r="B7" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436092</v>
+        <v>436428</v>
       </c>
       <c r="R7" t="n">
-        <v>6786744</v>
+        <v>6786577</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,6 +1248,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1675,54 +1675,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129082559</v>
+        <v>129082508</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435893</v>
+        <v>436338</v>
       </c>
       <c r="R12" t="n">
-        <v>6786660</v>
+        <v>6786741</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,7 +1754,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1782,7 +1772,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129082508</v>
+        <v>129082510</v>
       </c>
       <c r="B13" t="n">
         <v>79654</v>
@@ -1817,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436338</v>
+        <v>436506</v>
       </c>
       <c r="R13" t="n">
-        <v>6786741</v>
+        <v>6786715</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,45 +1869,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129082510</v>
+        <v>129082559</v>
       </c>
       <c r="B14" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436506</v>
+        <v>435893</v>
       </c>
       <c r="R14" t="n">
-        <v>6786715</v>
+        <v>6786660</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1958,6 +1957,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2364,10 +2364,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129082568</v>
+        <v>129082522</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>56913</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2375,30 +2375,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2408,10 +2407,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436409</v>
+        <v>436195</v>
       </c>
       <c r="R19" t="n">
-        <v>6786563</v>
+        <v>6786902</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2452,7 +2451,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2578,10 +2576,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129082522</v>
+        <v>129082568</v>
       </c>
       <c r="B21" t="n">
-        <v>56913</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,29 +2587,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2621,10 +2620,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436195</v>
+        <v>436409</v>
       </c>
       <c r="R21" t="n">
-        <v>6786902</v>
+        <v>6786563</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2665,6 +2664,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129082537</v>
+        <v>129082549</v>
       </c>
       <c r="B22" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2694,42 +2694,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436399</v>
+        <v>436322</v>
       </c>
       <c r="R22" t="n">
-        <v>6786867</v>
+        <v>6786798</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2788,10 +2780,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129082549</v>
+        <v>129082614</v>
       </c>
       <c r="B23" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2799,21 +2791,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2823,10 +2815,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436322</v>
+        <v>435889</v>
       </c>
       <c r="R23" t="n">
-        <v>6786798</v>
+        <v>6786670</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2885,7 +2877,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129082614</v>
+        <v>129082640</v>
       </c>
       <c r="B24" t="n">
         <v>79035</v>
@@ -2920,10 +2912,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435889</v>
+        <v>436530</v>
       </c>
       <c r="R24" t="n">
-        <v>6786670</v>
+        <v>6786657</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2982,10 +2974,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129082640</v>
+        <v>129082537</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2993,34 +2985,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436530</v>
+        <v>436399</v>
       </c>
       <c r="R25" t="n">
-        <v>6786657</v>
+        <v>6786867</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3877,41 +3877,40 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129082573</v>
+        <v>129082538</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3921,10 +3920,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436525</v>
+        <v>436141</v>
       </c>
       <c r="R34" t="n">
-        <v>6786729</v>
+        <v>6786882</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3965,7 +3964,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3984,10 +3982,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129082543</v>
+        <v>129082533</v>
       </c>
       <c r="B35" t="n">
-        <v>78793</v>
+        <v>57720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3995,34 +3993,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436027</v>
+        <v>436445</v>
       </c>
       <c r="R35" t="n">
-        <v>6786747</v>
+        <v>6786610</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4081,45 +4087,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129082551</v>
+        <v>129082588</v>
       </c>
       <c r="B36" t="n">
-        <v>78793</v>
+        <v>58093</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436436</v>
+        <v>435979</v>
       </c>
       <c r="R36" t="n">
-        <v>6786563</v>
+        <v>6786531</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4178,10 +4192,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129082662</v>
+        <v>129082543</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4189,21 +4203,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4213,10 +4227,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435932</v>
+        <v>436027</v>
       </c>
       <c r="R37" t="n">
-        <v>6786581</v>
+        <v>6786747</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4275,10 +4289,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129082612</v>
+        <v>129082551</v>
       </c>
       <c r="B38" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4286,21 +4300,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4310,10 +4324,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435883</v>
+        <v>436436</v>
       </c>
       <c r="R38" t="n">
-        <v>6786641</v>
+        <v>6786563</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4372,45 +4386,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129082646</v>
+        <v>129082573</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436400</v>
+        <v>436525</v>
       </c>
       <c r="R39" t="n">
-        <v>6786855</v>
+        <v>6786729</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4451,6 +4474,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4469,10 +4493,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129082533</v>
+        <v>129082662</v>
       </c>
       <c r="B40" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4480,42 +4504,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436445</v>
+        <v>435932</v>
       </c>
       <c r="R40" t="n">
-        <v>6786610</v>
+        <v>6786581</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4574,10 +4590,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129082538</v>
+        <v>129082612</v>
       </c>
       <c r="B41" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4585,42 +4601,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436141</v>
+        <v>435883</v>
       </c>
       <c r="R41" t="n">
-        <v>6786882</v>
+        <v>6786641</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4679,53 +4687,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129082588</v>
+        <v>129082646</v>
       </c>
       <c r="B42" t="n">
-        <v>58093</v>
+        <v>79035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435979</v>
+        <v>436400</v>
       </c>
       <c r="R42" t="n">
-        <v>6786531</v>
+        <v>6786855</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4784,45 +4784,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129082590</v>
+        <v>129082581</v>
       </c>
       <c r="B43" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436051</v>
+        <v>436252</v>
       </c>
       <c r="R43" t="n">
-        <v>6786730</v>
+        <v>6786963</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4863,6 +4872,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4881,7 +4891,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129082593</v>
+        <v>129082590</v>
       </c>
       <c r="B44" t="n">
         <v>78792</v>
@@ -4916,10 +4926,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436271</v>
+        <v>436051</v>
       </c>
       <c r="R44" t="n">
-        <v>6786851</v>
+        <v>6786730</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4978,10 +4988,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129082663</v>
+        <v>129082593</v>
       </c>
       <c r="B45" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4989,21 +4999,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5013,10 +5023,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435984</v>
+        <v>436271</v>
       </c>
       <c r="R45" t="n">
-        <v>6786452</v>
+        <v>6786851</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5075,54 +5085,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129082581</v>
+        <v>129082663</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436252</v>
+        <v>435984</v>
       </c>
       <c r="R46" t="n">
-        <v>6786963</v>
+        <v>6786452</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5163,7 +5164,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5279,10 +5279,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129082648</v>
+        <v>129082529</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5290,26 +5290,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5317,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436353</v>
+        <v>436057</v>
       </c>
       <c r="R48" t="n">
-        <v>6786940</v>
+        <v>6786761</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5361,7 +5366,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5380,7 +5384,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129082611</v>
+        <v>129082648</v>
       </c>
       <c r="B49" t="n">
         <v>79035</v>
@@ -5409,16 +5413,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435898</v>
+        <v>436353</v>
       </c>
       <c r="R49" t="n">
-        <v>6786619</v>
+        <v>6786940</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5459,6 +5466,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5477,7 +5485,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129082624</v>
+        <v>129082611</v>
       </c>
       <c r="B50" t="n">
         <v>79035</v>
@@ -5512,10 +5520,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436138</v>
+        <v>435898</v>
       </c>
       <c r="R50" t="n">
-        <v>6786811</v>
+        <v>6786619</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5574,7 +5582,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129082655</v>
+        <v>129082624</v>
       </c>
       <c r="B51" t="n">
         <v>79035</v>
@@ -5609,10 +5617,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436020</v>
+        <v>436138</v>
       </c>
       <c r="R51" t="n">
-        <v>6786856</v>
+        <v>6786811</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5671,10 +5679,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129082529</v>
+        <v>129082655</v>
       </c>
       <c r="B52" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5682,42 +5690,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436057</v>
+        <v>436020</v>
       </c>
       <c r="R52" t="n">
-        <v>6786761</v>
+        <v>6786856</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5990,10 +5990,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129082555</v>
+        <v>129082647</v>
       </c>
       <c r="B55" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6001,37 +6001,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436072</v>
+        <v>436372</v>
       </c>
       <c r="R55" t="n">
-        <v>6786886</v>
+        <v>6786946</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6072,7 +6069,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6091,7 +6087,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129082647</v>
+        <v>129082656</v>
       </c>
       <c r="B56" t="n">
         <v>79035</v>
@@ -6126,10 +6122,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>436372</v>
+        <v>435996</v>
       </c>
       <c r="R56" t="n">
-        <v>6786946</v>
+        <v>6786755</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6188,10 +6184,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129082656</v>
+        <v>129082555</v>
       </c>
       <c r="B57" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6199,34 +6195,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435996</v>
+        <v>436072</v>
       </c>
       <c r="R57" t="n">
-        <v>6786755</v>
+        <v>6786886</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6267,6 +6266,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6499,10 +6499,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129082644</v>
+        <v>129082548</v>
       </c>
       <c r="B60" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6510,21 +6510,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>436432</v>
+        <v>436268</v>
       </c>
       <c r="R60" t="n">
-        <v>6786765</v>
+        <v>6786874</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6596,10 +6596,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129082666</v>
+        <v>129082516</v>
       </c>
       <c r="B61" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6607,34 +6607,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436618</v>
+        <v>436470</v>
       </c>
       <c r="R61" t="n">
-        <v>6786620</v>
+        <v>6786714</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6675,6 +6678,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6693,10 +6697,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129082597</v>
+        <v>129082545</v>
       </c>
       <c r="B62" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6704,34 +6708,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>436469</v>
+        <v>436085</v>
       </c>
       <c r="R62" t="n">
-        <v>6786748</v>
+        <v>6786778</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6772,6 +6779,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6790,10 +6798,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129082506</v>
+        <v>129082644</v>
       </c>
       <c r="B63" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6801,37 +6809,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>436172</v>
+        <v>436432</v>
       </c>
       <c r="R63" t="n">
-        <v>6786831</v>
+        <v>6786765</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6872,7 +6877,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6891,10 +6895,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129082515</v>
+        <v>129082597</v>
       </c>
       <c r="B64" t="n">
-        <v>79625</v>
+        <v>78792</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6902,37 +6906,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>436075</v>
+        <v>436469</v>
       </c>
       <c r="R64" t="n">
-        <v>6786747</v>
+        <v>6786748</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6973,7 +6974,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129082548</v>
+        <v>129082666</v>
       </c>
       <c r="B65" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7003,21 +7003,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7027,10 +7027,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>436268</v>
+        <v>436618</v>
       </c>
       <c r="R65" t="n">
-        <v>6786874</v>
+        <v>6786620</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7089,10 +7089,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129082516</v>
+        <v>129082506</v>
       </c>
       <c r="B66" t="n">
-        <v>79625</v>
+        <v>79654</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7100,21 +7100,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436470</v>
+        <v>436172</v>
       </c>
       <c r="R66" t="n">
-        <v>6786714</v>
+        <v>6786831</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7190,10 +7190,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129082545</v>
+        <v>129082515</v>
       </c>
       <c r="B67" t="n">
-        <v>78793</v>
+        <v>79625</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7201,21 +7201,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7228,10 +7228,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436085</v>
+        <v>436075</v>
       </c>
       <c r="R67" t="n">
-        <v>6786778</v>
+        <v>6786747</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7388,45 +7388,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129082552</v>
+        <v>129082572</v>
       </c>
       <c r="B69" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>436206</v>
+        <v>436553</v>
       </c>
       <c r="R69" t="n">
-        <v>6786892</v>
+        <v>6786640</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7467,6 +7476,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7784,54 +7794,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129082572</v>
+        <v>129082552</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436553</v>
+        <v>436206</v>
       </c>
       <c r="R73" t="n">
-        <v>6786640</v>
+        <v>6786892</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7872,7 +7873,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7891,7 +7891,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129082540</v>
+        <v>129082534</v>
       </c>
       <c r="B74" t="n">
         <v>57720</v>
@@ -7934,10 +7934,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436188</v>
+        <v>436565</v>
       </c>
       <c r="R74" t="n">
-        <v>6786921</v>
+        <v>6786624</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7996,7 +7996,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129082534</v>
+        <v>129082539</v>
       </c>
       <c r="B75" t="n">
         <v>57720</v>
@@ -8029,7 +8029,7 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436565</v>
+        <v>436069</v>
       </c>
       <c r="R75" t="n">
-        <v>6786624</v>
+        <v>6786886</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8101,7 +8101,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129082539</v>
+        <v>129082540</v>
       </c>
       <c r="B76" t="n">
         <v>57720</v>
@@ -8134,7 +8134,7 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -8144,10 +8144,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436069</v>
+        <v>436188</v>
       </c>
       <c r="R76" t="n">
-        <v>6786886</v>
+        <v>6786921</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8206,54 +8206,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129082579</v>
+        <v>129082639</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436306</v>
+        <v>436568</v>
       </c>
       <c r="R77" t="n">
-        <v>6786960</v>
+        <v>6786650</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8294,7 +8285,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8313,10 +8303,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129082639</v>
+        <v>129082503</v>
       </c>
       <c r="B78" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8324,21 +8314,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8348,10 +8338,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436568</v>
+        <v>436052</v>
       </c>
       <c r="R78" t="n">
-        <v>6786650</v>
+        <v>6786720</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8410,10 +8400,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129082503</v>
+        <v>129082634</v>
       </c>
       <c r="B79" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8421,21 +8411,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8445,10 +8435,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436052</v>
+        <v>436338</v>
       </c>
       <c r="R79" t="n">
-        <v>6786720</v>
+        <v>6786664</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8507,45 +8497,54 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129082634</v>
+        <v>129082579</v>
       </c>
       <c r="B80" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436338</v>
+        <v>436306</v>
       </c>
       <c r="R80" t="n">
-        <v>6786664</v>
+        <v>6786960</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8586,6 +8585,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9291,45 +9291,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129082625</v>
+        <v>129082671</v>
       </c>
       <c r="B88" t="n">
-        <v>79035</v>
+        <v>92819</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>436202</v>
+        <v>436349</v>
       </c>
       <c r="R88" t="n">
-        <v>6786849</v>
+        <v>6786689</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9370,6 +9373,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9388,48 +9392,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129082671</v>
+        <v>129082654</v>
       </c>
       <c r="B89" t="n">
-        <v>92819</v>
+        <v>79035</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>436349</v>
+        <v>436054</v>
       </c>
       <c r="R89" t="n">
-        <v>6786689</v>
+        <v>6786881</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9470,7 +9471,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9489,7 +9489,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129082654</v>
+        <v>129082625</v>
       </c>
       <c r="B90" t="n">
         <v>79035</v>
@@ -9524,10 +9524,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436054</v>
+        <v>436202</v>
       </c>
       <c r="R90" t="n">
-        <v>6786881</v>
+        <v>6786849</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10168,10 +10168,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129082525</v>
+        <v>129082536</v>
       </c>
       <c r="B97" t="n">
-        <v>57883</v>
+        <v>57720</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10179,21 +10179,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10201,7 +10201,7 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -10211,10 +10211,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>435948</v>
+        <v>436544</v>
       </c>
       <c r="R97" t="n">
-        <v>6786586</v>
+        <v>6786666</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10273,54 +10273,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129082582</v>
+        <v>129082556</v>
       </c>
       <c r="B98" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436138</v>
+        <v>436010</v>
       </c>
       <c r="R98" t="n">
-        <v>6786894</v>
+        <v>6786852</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10361,7 +10352,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10380,10 +10370,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129082556</v>
+        <v>129082514</v>
       </c>
       <c r="B99" t="n">
-        <v>78793</v>
+        <v>79625</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10391,21 +10381,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10415,10 +10405,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436010</v>
+        <v>436044</v>
       </c>
       <c r="R99" t="n">
-        <v>6786852</v>
+        <v>6786741</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10477,10 +10467,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129082514</v>
+        <v>129082525</v>
       </c>
       <c r="B100" t="n">
-        <v>79625</v>
+        <v>57883</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10488,34 +10478,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436044</v>
+        <v>435948</v>
       </c>
       <c r="R100" t="n">
-        <v>6786741</v>
+        <v>6786586</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10574,40 +10572,41 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129082536</v>
+        <v>129082582</v>
       </c>
       <c r="B101" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -10617,10 +10616,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>436544</v>
+        <v>436138</v>
       </c>
       <c r="R101" t="n">
-        <v>6786666</v>
+        <v>6786894</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10661,6 +10660,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11067,7 +11067,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129082531</v>
+        <v>129082532</v>
       </c>
       <c r="B106" t="n">
         <v>57720</v>
@@ -11110,10 +11110,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>436246</v>
+        <v>436295</v>
       </c>
       <c r="R106" t="n">
-        <v>6786863</v>
+        <v>6786848</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11172,7 +11172,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129082532</v>
+        <v>129082531</v>
       </c>
       <c r="B107" t="n">
         <v>57720</v>
@@ -11215,10 +11215,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436295</v>
+        <v>436246</v>
       </c>
       <c r="R107" t="n">
-        <v>6786848</v>
+        <v>6786863</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11384,10 +11384,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129082628</v>
+        <v>129082509</v>
       </c>
       <c r="B109" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11395,21 +11395,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11419,10 +11419,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>436327</v>
+        <v>436482</v>
       </c>
       <c r="R109" t="n">
-        <v>6786767</v>
+        <v>6786616</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11481,7 +11481,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129082632</v>
+        <v>129082628</v>
       </c>
       <c r="B110" t="n">
         <v>79035</v>
@@ -11516,10 +11516,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>436334</v>
+        <v>436327</v>
       </c>
       <c r="R110" t="n">
-        <v>6786685</v>
+        <v>6786767</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11578,7 +11578,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129082609</v>
+        <v>129082632</v>
       </c>
       <c r="B111" t="n">
         <v>79035</v>
@@ -11613,10 +11613,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>435914</v>
+        <v>436334</v>
       </c>
       <c r="R111" t="n">
-        <v>6786598</v>
+        <v>6786685</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11675,10 +11675,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129082592</v>
+        <v>129082609</v>
       </c>
       <c r="B112" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11686,21 +11686,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11710,10 +11710,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>436095</v>
+        <v>435914</v>
       </c>
       <c r="R112" t="n">
-        <v>6786744</v>
+        <v>6786598</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11772,10 +11772,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129082627</v>
+        <v>129082592</v>
       </c>
       <c r="B113" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11783,21 +11783,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11807,10 +11807,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>436246</v>
+        <v>436095</v>
       </c>
       <c r="R113" t="n">
-        <v>6786881</v>
+        <v>6786744</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11869,10 +11869,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129082509</v>
+        <v>129082627</v>
       </c>
       <c r="B114" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11880,21 +11880,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11904,10 +11904,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>436482</v>
+        <v>436246</v>
       </c>
       <c r="R114" t="n">
-        <v>6786616</v>
+        <v>6786881</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12063,10 +12063,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129082645</v>
+        <v>129082554</v>
       </c>
       <c r="B116" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12074,21 +12074,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12098,10 +12098,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>436405</v>
+        <v>436096</v>
       </c>
       <c r="R116" t="n">
-        <v>6786825</v>
+        <v>6786876</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12160,45 +12160,54 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129082633</v>
+        <v>129082586</v>
       </c>
       <c r="B117" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>436347</v>
+        <v>435931</v>
       </c>
       <c r="R117" t="n">
-        <v>6786689</v>
+        <v>6786572</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12239,6 +12248,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12257,45 +12267,54 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129082554</v>
+        <v>129082576</v>
       </c>
       <c r="B118" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>436096</v>
+        <v>436417</v>
       </c>
       <c r="R118" t="n">
-        <v>6786876</v>
+        <v>6786827</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12336,6 +12355,7 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12354,7 +12374,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129082560</v>
+        <v>129082580</v>
       </c>
       <c r="B119" t="n">
         <v>8450</v>
@@ -12398,10 +12418,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>435897</v>
+        <v>436280</v>
       </c>
       <c r="R119" t="n">
-        <v>6786676</v>
+        <v>6786936</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12461,7 +12481,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129082576</v>
+        <v>129082560</v>
       </c>
       <c r="B120" t="n">
         <v>8450</v>
@@ -12505,10 +12525,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>436417</v>
+        <v>435897</v>
       </c>
       <c r="R120" t="n">
-        <v>6786827</v>
+        <v>6786676</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12568,54 +12588,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129082586</v>
+        <v>129082645</v>
       </c>
       <c r="B121" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>435931</v>
+        <v>436405</v>
       </c>
       <c r="R121" t="n">
-        <v>6786572</v>
+        <v>6786825</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12656,7 +12667,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12675,54 +12685,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129082580</v>
+        <v>129082633</v>
       </c>
       <c r="B122" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>436280</v>
+        <v>436347</v>
       </c>
       <c r="R122" t="n">
-        <v>6786936</v>
+        <v>6786689</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12763,7 +12764,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12782,45 +12782,54 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129082618</v>
+        <v>129082565</v>
       </c>
       <c r="B123" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>436027</v>
+        <v>436230</v>
       </c>
       <c r="R123" t="n">
-        <v>6786735</v>
+        <v>6786855</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12861,6 +12870,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12879,45 +12889,54 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129082598</v>
+        <v>129082563</v>
       </c>
       <c r="B124" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>436107</v>
+        <v>436055</v>
       </c>
       <c r="R124" t="n">
-        <v>6786875</v>
+        <v>6786776</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12958,6 +12977,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -12976,7 +12996,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129082613</v>
+        <v>129082618</v>
       </c>
       <c r="B125" t="n">
         <v>79035</v>
@@ -13011,10 +13031,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>435886</v>
+        <v>436027</v>
       </c>
       <c r="R125" t="n">
-        <v>6786666</v>
+        <v>6786735</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13073,54 +13093,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129082563</v>
+        <v>129082598</v>
       </c>
       <c r="B126" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436055</v>
+        <v>436107</v>
       </c>
       <c r="R126" t="n">
-        <v>6786776</v>
+        <v>6786875</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13161,7 +13172,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13180,54 +13190,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129082565</v>
+        <v>129082613</v>
       </c>
       <c r="B127" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>436230</v>
+        <v>435886</v>
       </c>
       <c r="R127" t="n">
-        <v>6786855</v>
+        <v>6786666</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13268,7 +13269,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13287,10 +13287,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129082535</v>
+        <v>129082596</v>
       </c>
       <c r="B128" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13298,42 +13298,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>436575</v>
+        <v>436432</v>
       </c>
       <c r="R128" t="n">
-        <v>6786632</v>
+        <v>6786558</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13392,54 +13384,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129082558</v>
+        <v>129082626</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>435909</v>
+        <v>436240</v>
       </c>
       <c r="R129" t="n">
-        <v>6786616</v>
+        <v>6786833</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13480,7 +13463,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13499,54 +13481,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129082583</v>
+        <v>129082664</v>
       </c>
       <c r="B130" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436011</v>
+        <v>436029</v>
       </c>
       <c r="R130" t="n">
-        <v>6786844</v>
+        <v>6786750</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13587,7 +13560,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13606,10 +13578,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129082547</v>
+        <v>129082535</v>
       </c>
       <c r="B131" t="n">
-        <v>78793</v>
+        <v>57720</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13617,34 +13589,42 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>436172</v>
+        <v>436575</v>
       </c>
       <c r="R131" t="n">
-        <v>6786825</v>
+        <v>6786632</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13703,10 +13683,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129082596</v>
+        <v>129082547</v>
       </c>
       <c r="B132" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13714,21 +13694,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13738,10 +13718,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>436432</v>
+        <v>436172</v>
       </c>
       <c r="R132" t="n">
-        <v>6786558</v>
+        <v>6786825</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13800,45 +13780,54 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129082626</v>
+        <v>129082583</v>
       </c>
       <c r="B133" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>436240</v>
+        <v>436011</v>
       </c>
       <c r="R133" t="n">
-        <v>6786833</v>
+        <v>6786844</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13879,6 +13868,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -13897,45 +13887,54 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129082664</v>
+        <v>129082558</v>
       </c>
       <c r="B134" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>436029</v>
+        <v>435909</v>
       </c>
       <c r="R134" t="n">
-        <v>6786750</v>
+        <v>6786616</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13976,6 +13975,7 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49064-2025 artfynd.xlsx
+++ b/artfynd/A 49064-2025 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129082641</v>
+        <v>129082570</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436537</v>
+        <v>436428</v>
       </c>
       <c r="R2" t="n">
-        <v>6786684</v>
+        <v>6786577</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129082659</v>
+        <v>129082641</v>
       </c>
       <c r="B3" t="n">
         <v>79035</v>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435974</v>
+        <v>436537</v>
       </c>
       <c r="R3" t="n">
-        <v>6786534</v>
+        <v>6786684</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129082637</v>
+        <v>129082659</v>
       </c>
       <c r="B4" t="n">
         <v>79035</v>
@@ -904,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436410</v>
+        <v>435974</v>
       </c>
       <c r="R4" t="n">
-        <v>6786560</v>
+        <v>6786534</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129082544</v>
+        <v>129082637</v>
       </c>
       <c r="B5" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436044</v>
+        <v>436410</v>
       </c>
       <c r="R5" t="n">
-        <v>6786741</v>
+        <v>6786560</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129082546</v>
+        <v>129082544</v>
       </c>
       <c r="B6" t="n">
         <v>78793</v>
@@ -1098,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436092</v>
+        <v>436044</v>
       </c>
       <c r="R6" t="n">
-        <v>6786744</v>
+        <v>6786741</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,54 +1170,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129082570</v>
+        <v>129082546</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436428</v>
+        <v>436092</v>
       </c>
       <c r="R7" t="n">
-        <v>6786577</v>
+        <v>6786744</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,7 +1249,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1267,54 +1267,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129082575</v>
+        <v>129082651</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436432</v>
+        <v>436254</v>
       </c>
       <c r="R8" t="n">
-        <v>6786759</v>
+        <v>6786925</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,7 +1346,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1374,54 +1364,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129082574</v>
+        <v>129082638</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436455</v>
+        <v>436456</v>
       </c>
       <c r="R9" t="n">
-        <v>6786732</v>
+        <v>6786598</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1462,7 +1443,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1481,45 +1461,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129082651</v>
+        <v>129082575</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436254</v>
+        <v>436432</v>
       </c>
       <c r="R10" t="n">
-        <v>6786925</v>
+        <v>6786759</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,6 +1549,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1578,45 +1568,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129082638</v>
+        <v>129082574</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436456</v>
+        <v>436455</v>
       </c>
       <c r="R11" t="n">
-        <v>6786598</v>
+        <v>6786732</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,6 +1656,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129082549</v>
+        <v>129082614</v>
       </c>
       <c r="B22" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2694,21 +2694,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436322</v>
+        <v>435889</v>
       </c>
       <c r="R22" t="n">
-        <v>6786798</v>
+        <v>6786670</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2780,7 +2780,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129082614</v>
+        <v>129082640</v>
       </c>
       <c r="B23" t="n">
         <v>79035</v>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435889</v>
+        <v>436530</v>
       </c>
       <c r="R23" t="n">
-        <v>6786670</v>
+        <v>6786657</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129082640</v>
+        <v>129082537</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2888,34 +2888,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436530</v>
+        <v>436399</v>
       </c>
       <c r="R24" t="n">
-        <v>6786657</v>
+        <v>6786867</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2974,10 +2982,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129082537</v>
+        <v>129082549</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2985,42 +2993,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436399</v>
+        <v>436322</v>
       </c>
       <c r="R25" t="n">
-        <v>6786867</v>
+        <v>6786798</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3665,40 +3665,41 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129082524</v>
+        <v>129082562</v>
       </c>
       <c r="B32" t="n">
-        <v>57883</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3708,10 +3709,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436189</v>
+        <v>436015</v>
       </c>
       <c r="R32" t="n">
-        <v>6786920</v>
+        <v>6786713</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3752,6 +3753,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3770,41 +3772,40 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129082562</v>
+        <v>129082524</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>57883</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3814,10 +3815,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436015</v>
+        <v>436189</v>
       </c>
       <c r="R33" t="n">
-        <v>6786713</v>
+        <v>6786920</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3858,7 +3859,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4087,10 +4087,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129082588</v>
+        <v>129082573</v>
       </c>
       <c r="B36" t="n">
-        <v>58093</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4098,29 +4098,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4130,10 +4131,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435979</v>
+        <v>436525</v>
       </c>
       <c r="R36" t="n">
-        <v>6786531</v>
+        <v>6786729</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4174,6 +4175,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4192,10 +4194,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129082543</v>
+        <v>129082662</v>
       </c>
       <c r="B37" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4203,21 +4205,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4227,10 +4229,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436027</v>
+        <v>435932</v>
       </c>
       <c r="R37" t="n">
-        <v>6786747</v>
+        <v>6786581</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4289,10 +4291,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129082551</v>
+        <v>129082612</v>
       </c>
       <c r="B38" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4300,21 +4302,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4324,10 +4326,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436436</v>
+        <v>435883</v>
       </c>
       <c r="R38" t="n">
-        <v>6786563</v>
+        <v>6786641</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4386,54 +4388,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129082573</v>
+        <v>129082646</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436525</v>
+        <v>436400</v>
       </c>
       <c r="R39" t="n">
-        <v>6786729</v>
+        <v>6786855</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4474,7 +4467,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4493,45 +4485,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129082662</v>
+        <v>129082588</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>58093</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435932</v>
+        <v>435979</v>
       </c>
       <c r="R40" t="n">
-        <v>6786581</v>
+        <v>6786531</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4590,10 +4590,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129082612</v>
+        <v>129082543</v>
       </c>
       <c r="B41" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4601,21 +4601,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4625,10 +4625,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435883</v>
+        <v>436027</v>
       </c>
       <c r="R41" t="n">
-        <v>6786641</v>
+        <v>6786747</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4687,10 +4687,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129082646</v>
+        <v>129082551</v>
       </c>
       <c r="B42" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4698,21 +4698,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4722,10 +4722,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436400</v>
+        <v>436436</v>
       </c>
       <c r="R42" t="n">
-        <v>6786855</v>
+        <v>6786563</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4784,54 +4784,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129082581</v>
+        <v>129082590</v>
       </c>
       <c r="B43" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436252</v>
+        <v>436051</v>
       </c>
       <c r="R43" t="n">
-        <v>6786963</v>
+        <v>6786730</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4872,7 +4863,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4891,7 +4881,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129082590</v>
+        <v>129082593</v>
       </c>
       <c r="B44" t="n">
         <v>78792</v>
@@ -4926,10 +4916,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436051</v>
+        <v>436271</v>
       </c>
       <c r="R44" t="n">
-        <v>6786730</v>
+        <v>6786851</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4988,10 +4978,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129082593</v>
+        <v>129082663</v>
       </c>
       <c r="B45" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4999,21 +4989,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5023,10 +5013,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436271</v>
+        <v>435984</v>
       </c>
       <c r="R45" t="n">
-        <v>6786851</v>
+        <v>6786452</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5085,10 +5075,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129082663</v>
+        <v>129082553</v>
       </c>
       <c r="B46" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5096,21 +5086,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5120,10 +5110,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435984</v>
+        <v>436197</v>
       </c>
       <c r="R46" t="n">
-        <v>6786452</v>
+        <v>6786924</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5182,45 +5172,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129082553</v>
+        <v>129082581</v>
       </c>
       <c r="B47" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436197</v>
+        <v>436252</v>
       </c>
       <c r="R47" t="n">
-        <v>6786924</v>
+        <v>6786963</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5261,6 +5260,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -7291,10 +7291,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129082550</v>
+        <v>129082507</v>
       </c>
       <c r="B68" t="n">
-        <v>78793</v>
+        <v>79654</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7302,21 +7302,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436361</v>
+        <v>436265</v>
       </c>
       <c r="R68" t="n">
-        <v>6786687</v>
+        <v>6786874</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7388,54 +7388,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129082572</v>
+        <v>129082610</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>436553</v>
+        <v>435906</v>
       </c>
       <c r="R69" t="n">
-        <v>6786640</v>
+        <v>6786603</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7476,7 +7467,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7495,10 +7485,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129082507</v>
+        <v>129082528</v>
       </c>
       <c r="B70" t="n">
-        <v>79654</v>
+        <v>57720</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7506,34 +7496,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436265</v>
+        <v>436042</v>
       </c>
       <c r="R70" t="n">
-        <v>6786874</v>
+        <v>6786785</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7592,10 +7590,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129082610</v>
+        <v>129082550</v>
       </c>
       <c r="B71" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7603,21 +7601,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7627,10 +7625,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>435906</v>
+        <v>436361</v>
       </c>
       <c r="R71" t="n">
-        <v>6786603</v>
+        <v>6786687</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7689,10 +7687,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129082528</v>
+        <v>129082552</v>
       </c>
       <c r="B72" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7700,42 +7698,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436042</v>
+        <v>436206</v>
       </c>
       <c r="R72" t="n">
-        <v>6786785</v>
+        <v>6786892</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7794,45 +7784,54 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129082552</v>
+        <v>129082572</v>
       </c>
       <c r="B73" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436206</v>
+        <v>436553</v>
       </c>
       <c r="R73" t="n">
-        <v>6786892</v>
+        <v>6786640</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7873,6 +7872,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7891,10 +7891,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129082534</v>
+        <v>129082639</v>
       </c>
       <c r="B74" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7902,42 +7902,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436565</v>
+        <v>436568</v>
       </c>
       <c r="R74" t="n">
-        <v>6786624</v>
+        <v>6786650</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7996,10 +7988,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129082539</v>
+        <v>129082503</v>
       </c>
       <c r="B75" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8007,42 +7999,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436069</v>
+        <v>436052</v>
       </c>
       <c r="R75" t="n">
-        <v>6786886</v>
+        <v>6786720</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8101,10 +8085,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129082540</v>
+        <v>129082634</v>
       </c>
       <c r="B76" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8112,42 +8096,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436188</v>
+        <v>436338</v>
       </c>
       <c r="R76" t="n">
-        <v>6786921</v>
+        <v>6786664</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8206,45 +8182,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129082639</v>
+        <v>129082579</v>
       </c>
       <c r="B77" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436568</v>
+        <v>436306</v>
       </c>
       <c r="R77" t="n">
-        <v>6786650</v>
+        <v>6786960</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8285,6 +8270,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8303,10 +8289,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129082503</v>
+        <v>129082534</v>
       </c>
       <c r="B78" t="n">
-        <v>79654</v>
+        <v>57720</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8314,34 +8300,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436052</v>
+        <v>436565</v>
       </c>
       <c r="R78" t="n">
-        <v>6786720</v>
+        <v>6786624</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8400,10 +8394,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129082634</v>
+        <v>129082539</v>
       </c>
       <c r="B79" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8411,34 +8405,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436338</v>
+        <v>436069</v>
       </c>
       <c r="R79" t="n">
-        <v>6786664</v>
+        <v>6786886</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8497,41 +8499,40 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129082579</v>
+        <v>129082540</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8541,10 +8542,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436306</v>
+        <v>436188</v>
       </c>
       <c r="R80" t="n">
-        <v>6786960</v>
+        <v>6786921</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8585,7 +8586,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49064-2025 artfynd.xlsx
+++ b/artfynd/A 49064-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129082641</v>
+        <v>129082546</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436537</v>
+        <v>436092</v>
       </c>
       <c r="R3" t="n">
-        <v>6786684</v>
+        <v>6786744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129082659</v>
+        <v>129082544</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435974</v>
+        <v>436044</v>
       </c>
       <c r="R4" t="n">
-        <v>6786534</v>
+        <v>6786741</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129082637</v>
+        <v>129082659</v>
       </c>
       <c r="B5" t="n">
         <v>79035</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436410</v>
+        <v>435974</v>
       </c>
       <c r="R5" t="n">
-        <v>6786560</v>
+        <v>6786534</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129082544</v>
+        <v>129082641</v>
       </c>
       <c r="B6" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436044</v>
+        <v>436537</v>
       </c>
       <c r="R6" t="n">
-        <v>6786741</v>
+        <v>6786684</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129082546</v>
+        <v>129082637</v>
       </c>
       <c r="B7" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436092</v>
+        <v>436410</v>
       </c>
       <c r="R7" t="n">
-        <v>6786744</v>
+        <v>6786560</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,45 +1267,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129082651</v>
+        <v>129082575</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436254</v>
+        <v>436432</v>
       </c>
       <c r="R8" t="n">
-        <v>6786925</v>
+        <v>6786759</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,6 +1355,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1364,45 +1374,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129082638</v>
+        <v>129082574</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436456</v>
+        <v>436455</v>
       </c>
       <c r="R9" t="n">
-        <v>6786598</v>
+        <v>6786732</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1443,6 +1462,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1461,54 +1481,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129082575</v>
+        <v>129082638</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436432</v>
+        <v>436456</v>
       </c>
       <c r="R10" t="n">
-        <v>6786759</v>
+        <v>6786598</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,7 +1560,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1568,54 +1578,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129082574</v>
+        <v>129082651</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436455</v>
+        <v>436254</v>
       </c>
       <c r="R11" t="n">
-        <v>6786732</v>
+        <v>6786925</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1656,7 +1657,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1675,45 +1675,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129082508</v>
+        <v>129082559</v>
       </c>
       <c r="B12" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436338</v>
+        <v>435893</v>
       </c>
       <c r="R12" t="n">
-        <v>6786741</v>
+        <v>6786660</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1754,6 +1763,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1772,7 +1782,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129082510</v>
+        <v>129082508</v>
       </c>
       <c r="B13" t="n">
         <v>79654</v>
@@ -1807,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436506</v>
+        <v>436338</v>
       </c>
       <c r="R13" t="n">
-        <v>6786715</v>
+        <v>6786741</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1869,54 +1879,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129082559</v>
+        <v>129082510</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435893</v>
+        <v>436506</v>
       </c>
       <c r="R14" t="n">
-        <v>6786660</v>
+        <v>6786715</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1957,7 +1958,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2073,7 +2073,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129082622</v>
+        <v>129082629</v>
       </c>
       <c r="B16" t="n">
         <v>79035</v>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436101</v>
+        <v>436335</v>
       </c>
       <c r="R16" t="n">
-        <v>6786774</v>
+        <v>6786743</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2170,7 +2170,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129082629</v>
+        <v>129082630</v>
       </c>
       <c r="B17" t="n">
         <v>79035</v>
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436335</v>
+        <v>436320</v>
       </c>
       <c r="R17" t="n">
-        <v>6786743</v>
+        <v>6786718</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2267,7 +2267,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129082630</v>
+        <v>129082622</v>
       </c>
       <c r="B18" t="n">
         <v>79035</v>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436320</v>
+        <v>436101</v>
       </c>
       <c r="R18" t="n">
-        <v>6786718</v>
+        <v>6786774</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,7 +2469,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129082566</v>
+        <v>129082568</v>
       </c>
       <c r="B20" t="n">
         <v>8450</v>
@@ -2503,7 +2503,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2513,10 +2513,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436258</v>
+        <v>436409</v>
       </c>
       <c r="R20" t="n">
-        <v>6786851</v>
+        <v>6786563</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2576,7 +2576,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129082568</v>
+        <v>129082566</v>
       </c>
       <c r="B21" t="n">
         <v>8450</v>
@@ -2610,7 +2610,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436409</v>
+        <v>436258</v>
       </c>
       <c r="R21" t="n">
-        <v>6786563</v>
+        <v>6786851</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129082504</v>
+        <v>129082524</v>
       </c>
       <c r="B26" t="n">
-        <v>79654</v>
+        <v>57883</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3090,34 +3090,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436031</v>
+        <v>436189</v>
       </c>
       <c r="R26" t="n">
-        <v>6786744</v>
+        <v>6786920</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3176,10 +3184,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129082636</v>
+        <v>129082504</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3187,21 +3195,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3211,10 +3219,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436431</v>
+        <v>436031</v>
       </c>
       <c r="R27" t="n">
-        <v>6786583</v>
+        <v>6786744</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,10 +3378,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129082653</v>
+        <v>129082512</v>
       </c>
       <c r="B29" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3381,37 +3389,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436092</v>
+        <v>436428</v>
       </c>
       <c r="R29" t="n">
-        <v>6786889</v>
+        <v>6786809</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3452,7 +3457,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3471,10 +3475,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129082512</v>
+        <v>129082589</v>
       </c>
       <c r="B30" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3482,21 +3486,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3506,10 +3510,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436428</v>
+        <v>436033</v>
       </c>
       <c r="R30" t="n">
-        <v>6786809</v>
+        <v>6786758</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3568,10 +3572,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129082589</v>
+        <v>129082653</v>
       </c>
       <c r="B31" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3579,34 +3583,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436033</v>
+        <v>436092</v>
       </c>
       <c r="R31" t="n">
-        <v>6786758</v>
+        <v>6786889</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3647,6 +3654,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3772,10 +3780,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129082524</v>
+        <v>129082636</v>
       </c>
       <c r="B33" t="n">
-        <v>57883</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3783,42 +3791,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436189</v>
+        <v>436431</v>
       </c>
       <c r="R33" t="n">
-        <v>6786920</v>
+        <v>6786583</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3877,27 +3877,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129082538</v>
+        <v>129082588</v>
       </c>
       <c r="B34" t="n">
-        <v>57720</v>
+        <v>58093</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3910,7 +3910,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436141</v>
+        <v>435979</v>
       </c>
       <c r="R34" t="n">
-        <v>6786882</v>
+        <v>6786531</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3982,10 +3982,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129082533</v>
+        <v>129082662</v>
       </c>
       <c r="B35" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3993,42 +3993,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436445</v>
+        <v>435932</v>
       </c>
       <c r="R35" t="n">
-        <v>6786610</v>
+        <v>6786581</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4087,54 +4079,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129082573</v>
+        <v>129082612</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436525</v>
+        <v>435883</v>
       </c>
       <c r="R36" t="n">
-        <v>6786729</v>
+        <v>6786641</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4175,7 +4158,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4194,7 +4176,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129082662</v>
+        <v>129082646</v>
       </c>
       <c r="B37" t="n">
         <v>79035</v>
@@ -4229,10 +4211,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435932</v>
+        <v>436400</v>
       </c>
       <c r="R37" t="n">
-        <v>6786581</v>
+        <v>6786855</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4291,10 +4273,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129082612</v>
+        <v>129082538</v>
       </c>
       <c r="B38" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4302,34 +4284,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435883</v>
+        <v>436141</v>
       </c>
       <c r="R38" t="n">
-        <v>6786641</v>
+        <v>6786882</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4388,10 +4378,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129082646</v>
+        <v>129082533</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4399,34 +4389,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436400</v>
+        <v>436445</v>
       </c>
       <c r="R39" t="n">
-        <v>6786855</v>
+        <v>6786610</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4485,53 +4483,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129082588</v>
+        <v>129082543</v>
       </c>
       <c r="B40" t="n">
-        <v>58093</v>
+        <v>78793</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435979</v>
+        <v>436027</v>
       </c>
       <c r="R40" t="n">
-        <v>6786531</v>
+        <v>6786747</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4590,7 +4580,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129082543</v>
+        <v>129082551</v>
       </c>
       <c r="B41" t="n">
         <v>78793</v>
@@ -4625,10 +4615,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436027</v>
+        <v>436436</v>
       </c>
       <c r="R41" t="n">
-        <v>6786747</v>
+        <v>6786563</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4687,45 +4677,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129082551</v>
+        <v>129082573</v>
       </c>
       <c r="B42" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436436</v>
+        <v>436525</v>
       </c>
       <c r="R42" t="n">
-        <v>6786563</v>
+        <v>6786729</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4766,6 +4765,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4784,10 +4784,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129082590</v>
+        <v>129082553</v>
       </c>
       <c r="B43" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4795,21 +4795,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436051</v>
+        <v>436197</v>
       </c>
       <c r="R43" t="n">
-        <v>6786730</v>
+        <v>6786924</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5075,10 +5075,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129082553</v>
+        <v>129082590</v>
       </c>
       <c r="B46" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5086,21 +5086,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436197</v>
+        <v>436051</v>
       </c>
       <c r="R46" t="n">
-        <v>6786924</v>
+        <v>6786730</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5279,40 +5279,41 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129082529</v>
+        <v>129082567</v>
       </c>
       <c r="B48" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5322,10 +5323,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436057</v>
+        <v>436312</v>
       </c>
       <c r="R48" t="n">
-        <v>6786761</v>
+        <v>6786810</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5366,6 +5367,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5384,37 +5386,43 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129082648</v>
+        <v>129082585</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5422,10 +5430,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436353</v>
+        <v>435948</v>
       </c>
       <c r="R49" t="n">
-        <v>6786940</v>
+        <v>6786565</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5485,10 +5493,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129082611</v>
+        <v>129082529</v>
       </c>
       <c r="B50" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5496,34 +5504,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435898</v>
+        <v>436057</v>
       </c>
       <c r="R50" t="n">
-        <v>6786619</v>
+        <v>6786761</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5582,7 +5598,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129082624</v>
+        <v>129082648</v>
       </c>
       <c r="B51" t="n">
         <v>79035</v>
@@ -5611,16 +5627,19 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436138</v>
+        <v>436353</v>
       </c>
       <c r="R51" t="n">
-        <v>6786811</v>
+        <v>6786940</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5661,6 +5680,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5679,7 +5699,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129082655</v>
+        <v>129082611</v>
       </c>
       <c r="B52" t="n">
         <v>79035</v>
@@ -5714,10 +5734,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436020</v>
+        <v>435898</v>
       </c>
       <c r="R52" t="n">
-        <v>6786856</v>
+        <v>6786619</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5776,54 +5796,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129082567</v>
+        <v>129082624</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436312</v>
+        <v>436138</v>
       </c>
       <c r="R53" t="n">
-        <v>6786810</v>
+        <v>6786811</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5864,7 +5875,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5883,54 +5893,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129082585</v>
+        <v>129082655</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435948</v>
+        <v>436020</v>
       </c>
       <c r="R54" t="n">
-        <v>6786565</v>
+        <v>6786856</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5971,7 +5972,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6184,37 +6184,43 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129082555</v>
+        <v>129082577</v>
       </c>
       <c r="B57" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6222,10 +6228,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>436072</v>
+        <v>436381</v>
       </c>
       <c r="R57" t="n">
-        <v>6786886</v>
+        <v>6786936</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6285,7 +6291,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129082577</v>
+        <v>129082564</v>
       </c>
       <c r="B58" t="n">
         <v>8450</v>
@@ -6319,7 +6325,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6329,10 +6335,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>436381</v>
+        <v>436166</v>
       </c>
       <c r="R58" t="n">
-        <v>6786936</v>
+        <v>6786846</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6392,43 +6398,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129082564</v>
+        <v>129082555</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>436166</v>
+        <v>436072</v>
       </c>
       <c r="R59" t="n">
-        <v>6786846</v>
+        <v>6786886</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6499,10 +6499,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129082548</v>
+        <v>129082644</v>
       </c>
       <c r="B60" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6510,21 +6510,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>436268</v>
+        <v>436432</v>
       </c>
       <c r="R60" t="n">
-        <v>6786874</v>
+        <v>6786765</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6596,10 +6596,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129082516</v>
+        <v>129082666</v>
       </c>
       <c r="B61" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6607,37 +6607,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436470</v>
+        <v>436618</v>
       </c>
       <c r="R61" t="n">
-        <v>6786714</v>
+        <v>6786620</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6678,7 +6675,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6697,10 +6693,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129082545</v>
+        <v>129082597</v>
       </c>
       <c r="B62" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6708,37 +6704,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>436085</v>
+        <v>436469</v>
       </c>
       <c r="R62" t="n">
-        <v>6786778</v>
+        <v>6786748</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6779,7 +6772,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6798,10 +6790,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129082644</v>
+        <v>129082506</v>
       </c>
       <c r="B63" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6809,34 +6801,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>436432</v>
+        <v>436172</v>
       </c>
       <c r="R63" t="n">
-        <v>6786765</v>
+        <v>6786831</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6877,6 +6872,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6895,10 +6891,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129082597</v>
+        <v>129082548</v>
       </c>
       <c r="B64" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6906,21 +6902,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6930,10 +6926,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>436469</v>
+        <v>436268</v>
       </c>
       <c r="R64" t="n">
-        <v>6786748</v>
+        <v>6786874</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6992,10 +6988,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129082666</v>
+        <v>129082516</v>
       </c>
       <c r="B65" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7003,34 +6999,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>436618</v>
+        <v>436470</v>
       </c>
       <c r="R65" t="n">
-        <v>6786620</v>
+        <v>6786714</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7071,6 +7070,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7089,10 +7089,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129082506</v>
+        <v>129082545</v>
       </c>
       <c r="B66" t="n">
-        <v>79654</v>
+        <v>78793</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7100,21 +7100,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436172</v>
+        <v>436085</v>
       </c>
       <c r="R66" t="n">
-        <v>6786831</v>
+        <v>6786778</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7291,45 +7291,54 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129082507</v>
+        <v>129082572</v>
       </c>
       <c r="B68" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436265</v>
+        <v>436553</v>
       </c>
       <c r="R68" t="n">
-        <v>6786874</v>
+        <v>6786640</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7370,6 +7379,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7388,10 +7398,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129082610</v>
+        <v>129082528</v>
       </c>
       <c r="B69" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7399,34 +7409,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435906</v>
+        <v>436042</v>
       </c>
       <c r="R69" t="n">
-        <v>6786603</v>
+        <v>6786785</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7485,10 +7503,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129082528</v>
+        <v>129082552</v>
       </c>
       <c r="B70" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7496,42 +7514,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436042</v>
+        <v>436206</v>
       </c>
       <c r="R70" t="n">
-        <v>6786785</v>
+        <v>6786892</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7687,10 +7697,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129082552</v>
+        <v>129082610</v>
       </c>
       <c r="B72" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7698,21 +7708,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7722,10 +7732,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436206</v>
+        <v>435906</v>
       </c>
       <c r="R72" t="n">
-        <v>6786892</v>
+        <v>6786603</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7784,54 +7794,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129082572</v>
+        <v>129082507</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436553</v>
+        <v>436265</v>
       </c>
       <c r="R73" t="n">
-        <v>6786640</v>
+        <v>6786874</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7872,7 +7873,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7891,10 +7891,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129082639</v>
+        <v>129082503</v>
       </c>
       <c r="B74" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7902,21 +7902,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436568</v>
+        <v>436052</v>
       </c>
       <c r="R74" t="n">
-        <v>6786650</v>
+        <v>6786720</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7988,10 +7988,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129082503</v>
+        <v>129082639</v>
       </c>
       <c r="B75" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7999,21 +7999,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436052</v>
+        <v>436568</v>
       </c>
       <c r="R75" t="n">
-        <v>6786720</v>
+        <v>6786650</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8182,41 +8182,40 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129082579</v>
+        <v>129082534</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -8226,10 +8225,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436306</v>
+        <v>436565</v>
       </c>
       <c r="R77" t="n">
-        <v>6786960</v>
+        <v>6786624</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8270,7 +8269,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8289,7 +8287,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129082534</v>
+        <v>129082540</v>
       </c>
       <c r="B78" t="n">
         <v>57720</v>
@@ -8332,10 +8330,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436565</v>
+        <v>436188</v>
       </c>
       <c r="R78" t="n">
-        <v>6786624</v>
+        <v>6786921</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8499,40 +8497,41 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129082540</v>
+        <v>129082579</v>
       </c>
       <c r="B80" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8542,10 +8541,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436188</v>
+        <v>436306</v>
       </c>
       <c r="R80" t="n">
-        <v>6786921</v>
+        <v>6786960</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8586,6 +8585,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8701,10 +8701,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129082513</v>
+        <v>129082635</v>
       </c>
       <c r="B82" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8712,21 +8712,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>436205</v>
+        <v>436350</v>
       </c>
       <c r="R82" t="n">
-        <v>6786914</v>
+        <v>6786631</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8798,7 +8798,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129082635</v>
+        <v>129082617</v>
       </c>
       <c r="B83" t="n">
         <v>79035</v>
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>436350</v>
+        <v>436010</v>
       </c>
       <c r="R83" t="n">
-        <v>6786631</v>
+        <v>6786752</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8895,7 +8895,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129082649</v>
+        <v>129082667</v>
       </c>
       <c r="B84" t="n">
         <v>79035</v>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>436277</v>
+        <v>435965</v>
       </c>
       <c r="R84" t="n">
-        <v>6786944</v>
+        <v>6786476</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8992,45 +8992,53 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129082617</v>
+        <v>129082521</v>
       </c>
       <c r="B85" t="n">
-        <v>79035</v>
+        <v>56913</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>436010</v>
+        <v>436093</v>
       </c>
       <c r="R85" t="n">
-        <v>6786752</v>
+        <v>6786769</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9089,7 +9097,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129082667</v>
+        <v>129082649</v>
       </c>
       <c r="B86" t="n">
         <v>79035</v>
@@ -9124,10 +9132,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>435965</v>
+        <v>436277</v>
       </c>
       <c r="R86" t="n">
-        <v>6786476</v>
+        <v>6786944</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9186,53 +9194,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129082521</v>
+        <v>129082513</v>
       </c>
       <c r="B87" t="n">
-        <v>56913</v>
+        <v>79654</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>436093</v>
+        <v>436205</v>
       </c>
       <c r="R87" t="n">
-        <v>6786769</v>
+        <v>6786914</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9291,48 +9291,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129082671</v>
+        <v>129082595</v>
       </c>
       <c r="B88" t="n">
-        <v>92819</v>
+        <v>78792</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>436349</v>
+        <v>436361</v>
       </c>
       <c r="R88" t="n">
-        <v>6786689</v>
+        <v>6786688</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9373,7 +9370,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9974,10 +9970,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129082595</v>
+        <v>129082525</v>
       </c>
       <c r="B95" t="n">
-        <v>78792</v>
+        <v>57883</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9985,34 +9981,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436361</v>
+        <v>435948</v>
       </c>
       <c r="R95" t="n">
-        <v>6786688</v>
+        <v>6786586</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10071,45 +10075,48 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129082594</v>
+        <v>129082671</v>
       </c>
       <c r="B96" t="n">
-        <v>78792</v>
+        <v>92819</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436339</v>
+        <v>436349</v>
       </c>
       <c r="R96" t="n">
-        <v>6786747</v>
+        <v>6786689</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10150,6 +10157,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10168,10 +10176,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129082536</v>
+        <v>129082594</v>
       </c>
       <c r="B97" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10179,42 +10187,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436544</v>
+        <v>436339</v>
       </c>
       <c r="R97" t="n">
-        <v>6786666</v>
+        <v>6786747</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10273,10 +10273,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129082556</v>
+        <v>129082536</v>
       </c>
       <c r="B98" t="n">
-        <v>78793</v>
+        <v>57720</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10284,34 +10284,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436010</v>
+        <v>436544</v>
       </c>
       <c r="R98" t="n">
-        <v>6786852</v>
+        <v>6786666</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10370,45 +10378,54 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129082514</v>
+        <v>129082582</v>
       </c>
       <c r="B99" t="n">
-        <v>79625</v>
+        <v>8450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436044</v>
+        <v>436138</v>
       </c>
       <c r="R99" t="n">
-        <v>6786741</v>
+        <v>6786894</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10449,6 +10466,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10467,10 +10485,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129082525</v>
+        <v>129082514</v>
       </c>
       <c r="B100" t="n">
-        <v>57883</v>
+        <v>79625</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10478,42 +10496,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>435948</v>
+        <v>436044</v>
       </c>
       <c r="R100" t="n">
-        <v>6786586</v>
+        <v>6786741</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10572,54 +10582,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129082582</v>
+        <v>129082556</v>
       </c>
       <c r="B101" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>436138</v>
+        <v>436010</v>
       </c>
       <c r="R101" t="n">
-        <v>6786894</v>
+        <v>6786852</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10660,7 +10661,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -10873,10 +10873,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129082591</v>
+        <v>129082650</v>
       </c>
       <c r="B104" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10884,21 +10884,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10908,10 +10908,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>436044</v>
+        <v>436235</v>
       </c>
       <c r="R104" t="n">
-        <v>6786741</v>
+        <v>6786944</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10970,10 +10970,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129082650</v>
+        <v>129082531</v>
       </c>
       <c r="B105" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10981,34 +10981,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>436235</v>
+        <v>436246</v>
       </c>
       <c r="R105" t="n">
-        <v>6786944</v>
+        <v>6786863</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11172,10 +11180,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129082531</v>
+        <v>129082591</v>
       </c>
       <c r="B107" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11183,42 +11191,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436246</v>
+        <v>436044</v>
       </c>
       <c r="R107" t="n">
-        <v>6786863</v>
+        <v>6786741</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11578,7 +11578,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129082632</v>
+        <v>129082627</v>
       </c>
       <c r="B111" t="n">
         <v>79035</v>
@@ -11613,10 +11613,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>436334</v>
+        <v>436246</v>
       </c>
       <c r="R111" t="n">
-        <v>6786685</v>
+        <v>6786881</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11675,7 +11675,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129082609</v>
+        <v>129082668</v>
       </c>
       <c r="B112" t="n">
         <v>79035</v>
@@ -11710,10 +11710,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>435914</v>
+        <v>435933</v>
       </c>
       <c r="R112" t="n">
-        <v>6786598</v>
+        <v>6786585</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11772,10 +11772,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129082592</v>
+        <v>129082632</v>
       </c>
       <c r="B113" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11783,21 +11783,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11807,10 +11807,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>436095</v>
+        <v>436334</v>
       </c>
       <c r="R113" t="n">
-        <v>6786744</v>
+        <v>6786685</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11869,7 +11869,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129082627</v>
+        <v>129082609</v>
       </c>
       <c r="B114" t="n">
         <v>79035</v>
@@ -11904,10 +11904,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>436246</v>
+        <v>435914</v>
       </c>
       <c r="R114" t="n">
-        <v>6786881</v>
+        <v>6786598</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11966,10 +11966,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129082668</v>
+        <v>129082592</v>
       </c>
       <c r="B115" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11977,21 +11977,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12001,10 +12001,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>435933</v>
+        <v>436095</v>
       </c>
       <c r="R115" t="n">
-        <v>6786585</v>
+        <v>6786744</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12063,10 +12063,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129082554</v>
+        <v>129082645</v>
       </c>
       <c r="B116" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12074,21 +12074,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12098,10 +12098,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>436096</v>
+        <v>436405</v>
       </c>
       <c r="R116" t="n">
-        <v>6786876</v>
+        <v>6786825</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12160,54 +12160,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129082586</v>
+        <v>129082633</v>
       </c>
       <c r="B117" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>435931</v>
+        <v>436347</v>
       </c>
       <c r="R117" t="n">
-        <v>6786572</v>
+        <v>6786689</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12248,7 +12239,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12267,7 +12257,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129082576</v>
+        <v>129082580</v>
       </c>
       <c r="B118" t="n">
         <v>8450</v>
@@ -12311,10 +12301,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>436417</v>
+        <v>436280</v>
       </c>
       <c r="R118" t="n">
-        <v>6786827</v>
+        <v>6786936</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12374,7 +12364,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129082580</v>
+        <v>129082560</v>
       </c>
       <c r="B119" t="n">
         <v>8450</v>
@@ -12418,10 +12408,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>436280</v>
+        <v>435897</v>
       </c>
       <c r="R119" t="n">
-        <v>6786936</v>
+        <v>6786676</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12481,7 +12471,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129082560</v>
+        <v>129082576</v>
       </c>
       <c r="B120" t="n">
         <v>8450</v>
@@ -12525,10 +12515,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>435897</v>
+        <v>436417</v>
       </c>
       <c r="R120" t="n">
-        <v>6786676</v>
+        <v>6786827</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12588,45 +12578,54 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129082645</v>
+        <v>129082586</v>
       </c>
       <c r="B121" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>436405</v>
+        <v>435931</v>
       </c>
       <c r="R121" t="n">
-        <v>6786825</v>
+        <v>6786572</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12667,6 +12666,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12685,10 +12685,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129082633</v>
+        <v>129082554</v>
       </c>
       <c r="B122" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12696,21 +12696,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12720,10 +12720,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>436347</v>
+        <v>436096</v>
       </c>
       <c r="R122" t="n">
-        <v>6786689</v>
+        <v>6786876</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12782,54 +12782,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129082565</v>
+        <v>129082618</v>
       </c>
       <c r="B123" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>436230</v>
+        <v>436027</v>
       </c>
       <c r="R123" t="n">
-        <v>6786855</v>
+        <v>6786735</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12870,7 +12861,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12889,54 +12879,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129082563</v>
+        <v>129082613</v>
       </c>
       <c r="B124" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>436055</v>
+        <v>435886</v>
       </c>
       <c r="R124" t="n">
-        <v>6786776</v>
+        <v>6786666</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12977,7 +12958,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -12996,10 +12976,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129082618</v>
+        <v>129082598</v>
       </c>
       <c r="B125" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13007,21 +12987,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13031,10 +13011,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>436027</v>
+        <v>436107</v>
       </c>
       <c r="R125" t="n">
-        <v>6786735</v>
+        <v>6786875</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13093,45 +13073,54 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129082598</v>
+        <v>129082563</v>
       </c>
       <c r="B126" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436107</v>
+        <v>436055</v>
       </c>
       <c r="R126" t="n">
-        <v>6786875</v>
+        <v>6786776</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13172,6 +13161,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13190,45 +13180,54 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129082613</v>
+        <v>129082565</v>
       </c>
       <c r="B127" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>435886</v>
+        <v>436230</v>
       </c>
       <c r="R127" t="n">
-        <v>6786666</v>
+        <v>6786855</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13269,6 +13268,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13683,45 +13683,54 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129082547</v>
+        <v>129082558</v>
       </c>
       <c r="B132" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>436172</v>
+        <v>435909</v>
       </c>
       <c r="R132" t="n">
-        <v>6786825</v>
+        <v>6786616</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13762,6 +13771,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13887,54 +13897,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129082558</v>
+        <v>129082547</v>
       </c>
       <c r="B134" t="n">
-        <v>8450</v>
+        <v>78793</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>435909</v>
+        <v>436172</v>
       </c>
       <c r="R134" t="n">
-        <v>6786616</v>
+        <v>6786825</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13975,7 +13976,6 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49064-2025 artfynd.xlsx
+++ b/artfynd/A 49064-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129082570</v>
+        <v>129082641</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436428</v>
+        <v>436537</v>
       </c>
       <c r="R2" t="n">
-        <v>6786577</v>
+        <v>6786684</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129082546</v>
+        <v>129082637</v>
       </c>
       <c r="B3" t="n">
-        <v>78793</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436092</v>
+        <v>436410</v>
       </c>
       <c r="R3" t="n">
-        <v>6786744</v>
+        <v>6786560</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129082544</v>
+        <v>129082659</v>
       </c>
       <c r="B4" t="n">
-        <v>78793</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436044</v>
+        <v>435974</v>
       </c>
       <c r="R4" t="n">
-        <v>6786741</v>
+        <v>6786534</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129082659</v>
+        <v>129082546</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>78797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435974</v>
+        <v>436092</v>
       </c>
       <c r="R5" t="n">
-        <v>6786534</v>
+        <v>6786744</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129082641</v>
+        <v>129082544</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>78797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436537</v>
+        <v>436044</v>
       </c>
       <c r="R6" t="n">
-        <v>6786684</v>
+        <v>6786741</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,45 +1160,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129082637</v>
+        <v>129082570</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436410</v>
+        <v>436428</v>
       </c>
       <c r="R7" t="n">
-        <v>6786560</v>
+        <v>6786577</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,6 +1248,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1267,54 +1267,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129082575</v>
+        <v>129082651</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436432</v>
+        <v>436254</v>
       </c>
       <c r="R8" t="n">
-        <v>6786759</v>
+        <v>6786925</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,7 +1346,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1374,54 +1364,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129082574</v>
+        <v>129082638</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436455</v>
+        <v>436456</v>
       </c>
       <c r="R9" t="n">
-        <v>6786732</v>
+        <v>6786598</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1462,7 +1443,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1481,45 +1461,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129082638</v>
+        <v>129082575</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436456</v>
+        <v>436432</v>
       </c>
       <c r="R10" t="n">
-        <v>6786598</v>
+        <v>6786759</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,6 +1549,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1578,45 +1568,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129082651</v>
+        <v>129082574</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436254</v>
+        <v>436455</v>
       </c>
       <c r="R11" t="n">
-        <v>6786925</v>
+        <v>6786732</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,6 +1656,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1675,54 +1675,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129082559</v>
+        <v>129082508</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435893</v>
+        <v>436338</v>
       </c>
       <c r="R12" t="n">
-        <v>6786660</v>
+        <v>6786741</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,7 +1754,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1782,10 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129082508</v>
+        <v>129082510</v>
       </c>
       <c r="B13" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1817,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436338</v>
+        <v>436506</v>
       </c>
       <c r="R13" t="n">
-        <v>6786741</v>
+        <v>6786715</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,45 +1869,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129082510</v>
+        <v>129082559</v>
       </c>
       <c r="B14" t="n">
-        <v>79654</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436506</v>
+        <v>435893</v>
       </c>
       <c r="R14" t="n">
-        <v>6786715</v>
+        <v>6786660</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1958,6 +1957,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1976,45 +1976,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129082652</v>
+        <v>129082522</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>56915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436190</v>
+        <v>436195</v>
       </c>
       <c r="R15" t="n">
-        <v>6786911</v>
+        <v>6786902</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2073,45 +2081,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129082629</v>
+        <v>129082566</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436335</v>
+        <v>436258</v>
       </c>
       <c r="R16" t="n">
-        <v>6786743</v>
+        <v>6786851</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2152,6 +2169,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2170,45 +2188,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129082630</v>
+        <v>129082568</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436320</v>
+        <v>436409</v>
       </c>
       <c r="R17" t="n">
-        <v>6786718</v>
+        <v>6786563</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2249,6 +2276,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2267,10 +2295,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129082622</v>
+        <v>129082652</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2302,10 +2330,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436101</v>
+        <v>436190</v>
       </c>
       <c r="R18" t="n">
-        <v>6786774</v>
+        <v>6786911</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2364,53 +2392,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129082522</v>
+        <v>129082622</v>
       </c>
       <c r="B19" t="n">
-        <v>56913</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436195</v>
+        <v>436101</v>
       </c>
       <c r="R19" t="n">
-        <v>6786902</v>
+        <v>6786774</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2469,54 +2489,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129082568</v>
+        <v>129082629</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436409</v>
+        <v>436335</v>
       </c>
       <c r="R20" t="n">
-        <v>6786563</v>
+        <v>6786743</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2557,7 +2568,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2576,54 +2586,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129082566</v>
+        <v>129082630</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436258</v>
+        <v>436320</v>
       </c>
       <c r="R21" t="n">
-        <v>6786851</v>
+        <v>6786718</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,7 +2665,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2686,7 +2686,7 @@
         <v>129082614</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2780,10 +2780,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129082640</v>
+        <v>129082537</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2791,34 +2791,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436530</v>
+        <v>436399</v>
       </c>
       <c r="R23" t="n">
-        <v>6786657</v>
+        <v>6786867</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2877,10 +2885,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129082537</v>
+        <v>129082549</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>78797</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2888,42 +2896,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436399</v>
+        <v>436322</v>
       </c>
       <c r="R24" t="n">
-        <v>6786867</v>
+        <v>6786798</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2982,10 +2982,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129082549</v>
+        <v>129082640</v>
       </c>
       <c r="B25" t="n">
-        <v>78793</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2993,21 +2993,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436322</v>
+        <v>436530</v>
       </c>
       <c r="R25" t="n">
-        <v>6786798</v>
+        <v>6786657</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129082524</v>
+        <v>129082504</v>
       </c>
       <c r="B26" t="n">
-        <v>57883</v>
+        <v>79658</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3090,42 +3090,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436189</v>
+        <v>436031</v>
       </c>
       <c r="R26" t="n">
-        <v>6786920</v>
+        <v>6786744</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3184,10 +3176,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129082504</v>
+        <v>129082636</v>
       </c>
       <c r="B27" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3195,21 +3187,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3219,10 +3211,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436031</v>
+        <v>436431</v>
       </c>
       <c r="R27" t="n">
-        <v>6786744</v>
+        <v>6786583</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3284,7 +3276,7 @@
         <v>129082505</v>
       </c>
       <c r="B28" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3378,10 +3370,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129082512</v>
+        <v>129082653</v>
       </c>
       <c r="B29" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3389,34 +3381,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436428</v>
+        <v>436092</v>
       </c>
       <c r="R29" t="n">
-        <v>6786809</v>
+        <v>6786889</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3457,6 +3452,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3475,10 +3471,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129082589</v>
+        <v>129082512</v>
       </c>
       <c r="B30" t="n">
-        <v>78792</v>
+        <v>79658</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3486,21 +3482,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3510,10 +3506,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436033</v>
+        <v>436428</v>
       </c>
       <c r="R30" t="n">
-        <v>6786758</v>
+        <v>6786809</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3572,10 +3568,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129082653</v>
+        <v>129082589</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3583,37 +3579,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436092</v>
+        <v>436033</v>
       </c>
       <c r="R31" t="n">
-        <v>6786889</v>
+        <v>6786758</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3654,7 +3647,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3673,41 +3665,40 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129082562</v>
+        <v>129082524</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>57885</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3717,10 +3708,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436015</v>
+        <v>436189</v>
       </c>
       <c r="R32" t="n">
-        <v>6786713</v>
+        <v>6786920</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3761,7 +3752,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3780,45 +3770,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129082636</v>
+        <v>129082562</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436431</v>
+        <v>436015</v>
       </c>
       <c r="R33" t="n">
-        <v>6786583</v>
+        <v>6786713</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3859,6 +3858,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>129082588</v>
       </c>
       <c r="B34" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3982,10 +3982,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129082662</v>
+        <v>129082543</v>
       </c>
       <c r="B35" t="n">
-        <v>79035</v>
+        <v>78797</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3993,21 +3993,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435932</v>
+        <v>436027</v>
       </c>
       <c r="R35" t="n">
-        <v>6786581</v>
+        <v>6786747</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4079,10 +4079,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129082612</v>
+        <v>129082551</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>78797</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4090,21 +4090,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435883</v>
+        <v>436436</v>
       </c>
       <c r="R36" t="n">
-        <v>6786641</v>
+        <v>6786563</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4176,10 +4176,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129082646</v>
+        <v>129082662</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436400</v>
+        <v>435932</v>
       </c>
       <c r="R37" t="n">
-        <v>6786855</v>
+        <v>6786581</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4273,10 +4273,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129082538</v>
+        <v>129082612</v>
       </c>
       <c r="B38" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4284,42 +4284,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436141</v>
+        <v>435883</v>
       </c>
       <c r="R38" t="n">
-        <v>6786882</v>
+        <v>6786641</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4378,10 +4370,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129082533</v>
+        <v>129082646</v>
       </c>
       <c r="B39" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4389,42 +4381,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436445</v>
+        <v>436400</v>
       </c>
       <c r="R39" t="n">
-        <v>6786610</v>
+        <v>6786855</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4483,10 +4467,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129082543</v>
+        <v>129082538</v>
       </c>
       <c r="B40" t="n">
-        <v>78793</v>
+        <v>57722</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4494,34 +4478,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436027</v>
+        <v>436141</v>
       </c>
       <c r="R40" t="n">
-        <v>6786747</v>
+        <v>6786882</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4580,10 +4572,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129082551</v>
+        <v>129082533</v>
       </c>
       <c r="B41" t="n">
-        <v>78793</v>
+        <v>57722</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4591,34 +4583,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436436</v>
+        <v>436445</v>
       </c>
       <c r="R41" t="n">
-        <v>6786563</v>
+        <v>6786610</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4784,10 +4784,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129082553</v>
+        <v>129082590</v>
       </c>
       <c r="B43" t="n">
-        <v>78793</v>
+        <v>78796</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4795,21 +4795,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436197</v>
+        <v>436051</v>
       </c>
       <c r="R43" t="n">
-        <v>6786924</v>
+        <v>6786730</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4884,7 +4884,7 @@
         <v>129082593</v>
       </c>
       <c r="B44" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>129082663</v>
       </c>
       <c r="B45" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5075,45 +5075,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129082590</v>
+        <v>129082581</v>
       </c>
       <c r="B46" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436051</v>
+        <v>436252</v>
       </c>
       <c r="R46" t="n">
-        <v>6786730</v>
+        <v>6786963</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5154,6 +5163,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5172,54 +5182,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129082581</v>
+        <v>129082553</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>78797</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436252</v>
+        <v>436197</v>
       </c>
       <c r="R47" t="n">
-        <v>6786963</v>
+        <v>6786924</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5260,7 +5261,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5279,43 +5279,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129082567</v>
+        <v>129082648</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5323,10 +5317,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436312</v>
+        <v>436353</v>
       </c>
       <c r="R48" t="n">
-        <v>6786810</v>
+        <v>6786940</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5386,54 +5380,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129082585</v>
+        <v>129082611</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435948</v>
+        <v>435898</v>
       </c>
       <c r="R49" t="n">
-        <v>6786565</v>
+        <v>6786619</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5474,7 +5459,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5493,10 +5477,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129082529</v>
+        <v>129082624</v>
       </c>
       <c r="B50" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5504,42 +5488,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436057</v>
+        <v>436138</v>
       </c>
       <c r="R50" t="n">
-        <v>6786761</v>
+        <v>6786811</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5598,10 +5574,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129082648</v>
+        <v>129082655</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5627,19 +5603,16 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436353</v>
+        <v>436020</v>
       </c>
       <c r="R51" t="n">
-        <v>6786940</v>
+        <v>6786856</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5680,7 +5653,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5699,10 +5671,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129082611</v>
+        <v>129082529</v>
       </c>
       <c r="B52" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5710,34 +5682,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435898</v>
+        <v>436057</v>
       </c>
       <c r="R52" t="n">
-        <v>6786619</v>
+        <v>6786761</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5796,45 +5776,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129082624</v>
+        <v>129082567</v>
       </c>
       <c r="B53" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436138</v>
+        <v>436312</v>
       </c>
       <c r="R53" t="n">
-        <v>6786811</v>
+        <v>6786810</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5875,6 +5864,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5893,45 +5883,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129082655</v>
+        <v>129082585</v>
       </c>
       <c r="B54" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>436020</v>
+        <v>435948</v>
       </c>
       <c r="R54" t="n">
-        <v>6786856</v>
+        <v>6786565</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5972,6 +5971,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5993,7 +5993,7 @@
         <v>129082647</v>
       </c>
       <c r="B55" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>129082656</v>
       </c>
       <c r="B56" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6184,43 +6184,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129082577</v>
+        <v>129082555</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>78797</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6228,10 +6222,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>436381</v>
+        <v>436072</v>
       </c>
       <c r="R57" t="n">
-        <v>6786936</v>
+        <v>6786886</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6291,7 +6285,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129082564</v>
+        <v>129082577</v>
       </c>
       <c r="B58" t="n">
         <v>8450</v>
@@ -6325,7 +6319,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6335,10 +6329,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>436166</v>
+        <v>436381</v>
       </c>
       <c r="R58" t="n">
-        <v>6786846</v>
+        <v>6786936</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6398,37 +6392,43 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129082555</v>
+        <v>129082564</v>
       </c>
       <c r="B59" t="n">
-        <v>78793</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>436072</v>
+        <v>436166</v>
       </c>
       <c r="R59" t="n">
-        <v>6786886</v>
+        <v>6786846</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6502,7 +6502,7 @@
         <v>129082644</v>
       </c>
       <c r="B60" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6596,10 +6596,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129082666</v>
+        <v>129082597</v>
       </c>
       <c r="B61" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6607,21 +6607,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6631,10 +6631,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436618</v>
+        <v>436469</v>
       </c>
       <c r="R61" t="n">
-        <v>6786620</v>
+        <v>6786748</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6693,10 +6693,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129082597</v>
+        <v>129082666</v>
       </c>
       <c r="B62" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6704,21 +6704,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6728,10 +6728,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>436469</v>
+        <v>436618</v>
       </c>
       <c r="R62" t="n">
-        <v>6786748</v>
+        <v>6786620</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6793,7 +6793,7 @@
         <v>129082506</v>
       </c>
       <c r="B63" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>129082548</v>
       </c>
       <c r="B64" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>129082516</v>
       </c>
       <c r="B65" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>129082545</v>
       </c>
       <c r="B66" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>129082515</v>
       </c>
       <c r="B67" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7398,10 +7398,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129082528</v>
+        <v>129082552</v>
       </c>
       <c r="B69" t="n">
-        <v>57720</v>
+        <v>78797</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7409,42 +7409,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>436042</v>
+        <v>436206</v>
       </c>
       <c r="R69" t="n">
-        <v>6786785</v>
+        <v>6786892</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7503,10 +7495,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129082552</v>
+        <v>129082550</v>
       </c>
       <c r="B70" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7538,10 +7530,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436206</v>
+        <v>436361</v>
       </c>
       <c r="R70" t="n">
-        <v>6786892</v>
+        <v>6786687</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7600,10 +7592,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129082550</v>
+        <v>129082507</v>
       </c>
       <c r="B71" t="n">
-        <v>78793</v>
+        <v>79658</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7611,21 +7603,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7635,10 +7627,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436361</v>
+        <v>436265</v>
       </c>
       <c r="R71" t="n">
-        <v>6786687</v>
+        <v>6786874</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7700,7 +7692,7 @@
         <v>129082610</v>
       </c>
       <c r="B72" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7794,10 +7786,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129082507</v>
+        <v>129082528</v>
       </c>
       <c r="B73" t="n">
-        <v>79654</v>
+        <v>57722</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7805,34 +7797,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436265</v>
+        <v>436042</v>
       </c>
       <c r="R73" t="n">
-        <v>6786874</v>
+        <v>6786785</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7891,10 +7891,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129082503</v>
+        <v>129082639</v>
       </c>
       <c r="B74" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7902,21 +7902,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436052</v>
+        <v>436568</v>
       </c>
       <c r="R74" t="n">
-        <v>6786720</v>
+        <v>6786650</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7988,10 +7988,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129082639</v>
+        <v>129082503</v>
       </c>
       <c r="B75" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7999,21 +7999,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436568</v>
+        <v>436052</v>
       </c>
       <c r="R75" t="n">
-        <v>6786650</v>
+        <v>6786720</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8088,7 +8088,7 @@
         <v>129082634</v>
       </c>
       <c r="B76" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>129082534</v>
       </c>
       <c r="B77" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8287,10 +8287,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129082540</v>
+        <v>129082539</v>
       </c>
       <c r="B78" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436188</v>
+        <v>436069</v>
       </c>
       <c r="R78" t="n">
-        <v>6786921</v>
+        <v>6786886</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8392,10 +8392,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129082539</v>
+        <v>129082540</v>
       </c>
       <c r="B79" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -8435,10 +8435,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436069</v>
+        <v>436188</v>
       </c>
       <c r="R79" t="n">
-        <v>6786886</v>
+        <v>6786921</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8604,45 +8604,53 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129082620</v>
+        <v>129082521</v>
       </c>
       <c r="B81" t="n">
-        <v>79035</v>
+        <v>56915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>436035</v>
+        <v>436093</v>
       </c>
       <c r="R81" t="n">
-        <v>6786730</v>
+        <v>6786769</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8701,10 +8709,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129082635</v>
+        <v>129082620</v>
       </c>
       <c r="B82" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8736,10 +8744,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>436350</v>
+        <v>436035</v>
       </c>
       <c r="R82" t="n">
-        <v>6786631</v>
+        <v>6786730</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8798,10 +8806,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129082617</v>
+        <v>129082513</v>
       </c>
       <c r="B83" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8809,21 +8817,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8833,10 +8841,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>436010</v>
+        <v>436205</v>
       </c>
       <c r="R83" t="n">
-        <v>6786752</v>
+        <v>6786914</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8895,10 +8903,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129082667</v>
+        <v>129082635</v>
       </c>
       <c r="B84" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8930,10 +8938,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>435965</v>
+        <v>436350</v>
       </c>
       <c r="R84" t="n">
-        <v>6786476</v>
+        <v>6786631</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8992,53 +9000,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129082521</v>
+        <v>129082649</v>
       </c>
       <c r="B85" t="n">
-        <v>56913</v>
+        <v>79039</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>436093</v>
+        <v>436277</v>
       </c>
       <c r="R85" t="n">
-        <v>6786769</v>
+        <v>6786944</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9097,10 +9097,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129082649</v>
+        <v>129082617</v>
       </c>
       <c r="B86" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9132,10 +9132,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>436277</v>
+        <v>436010</v>
       </c>
       <c r="R86" t="n">
-        <v>6786944</v>
+        <v>6786752</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9194,10 +9194,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129082513</v>
+        <v>129082667</v>
       </c>
       <c r="B87" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9205,21 +9205,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9229,10 +9229,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>436205</v>
+        <v>435965</v>
       </c>
       <c r="R87" t="n">
-        <v>6786914</v>
+        <v>6786476</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9291,10 +9291,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129082595</v>
+        <v>129082654</v>
       </c>
       <c r="B88" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9302,21 +9302,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9326,10 +9326,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>436361</v>
+        <v>436054</v>
       </c>
       <c r="R88" t="n">
-        <v>6786688</v>
+        <v>6786881</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9388,10 +9388,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129082654</v>
+        <v>129082625</v>
       </c>
       <c r="B89" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9423,10 +9423,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>436054</v>
+        <v>436202</v>
       </c>
       <c r="R89" t="n">
-        <v>6786881</v>
+        <v>6786849</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9485,10 +9485,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129082625</v>
+        <v>129082665</v>
       </c>
       <c r="B90" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9520,10 +9520,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436202</v>
+        <v>436330</v>
       </c>
       <c r="R90" t="n">
-        <v>6786849</v>
+        <v>6786736</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9582,10 +9582,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129082665</v>
+        <v>129082606</v>
       </c>
       <c r="B91" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9617,10 +9617,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>436330</v>
+        <v>435970</v>
       </c>
       <c r="R91" t="n">
-        <v>6786736</v>
+        <v>6786458</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9679,10 +9679,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129082606</v>
+        <v>129082619</v>
       </c>
       <c r="B92" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9714,10 +9714,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>435970</v>
+        <v>436034</v>
       </c>
       <c r="R92" t="n">
-        <v>6786458</v>
+        <v>6786743</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9776,10 +9776,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129082619</v>
+        <v>129082616</v>
       </c>
       <c r="B93" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9811,10 +9811,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436034</v>
+        <v>436012</v>
       </c>
       <c r="R93" t="n">
-        <v>6786743</v>
+        <v>6786734</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9873,10 +9873,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129082616</v>
+        <v>129082595</v>
       </c>
       <c r="B94" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9884,21 +9884,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9908,10 +9908,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436012</v>
+        <v>436361</v>
       </c>
       <c r="R94" t="n">
-        <v>6786734</v>
+        <v>6786688</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9970,10 +9970,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129082525</v>
+        <v>129082594</v>
       </c>
       <c r="B95" t="n">
-        <v>57883</v>
+        <v>78796</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9981,42 +9981,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>435948</v>
+        <v>436339</v>
       </c>
       <c r="R95" t="n">
-        <v>6786586</v>
+        <v>6786747</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10075,37 +10067,42 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129082671</v>
+        <v>129082525</v>
       </c>
       <c r="B96" t="n">
-        <v>92819</v>
+        <v>57885</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10113,10 +10110,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436349</v>
+        <v>435948</v>
       </c>
       <c r="R96" t="n">
-        <v>6786689</v>
+        <v>6786586</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10157,7 +10154,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10176,45 +10172,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129082594</v>
+        <v>129082671</v>
       </c>
       <c r="B97" t="n">
-        <v>78792</v>
+        <v>92826</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436339</v>
+        <v>436349</v>
       </c>
       <c r="R97" t="n">
-        <v>6786747</v>
+        <v>6786689</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10255,6 +10254,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10276,7 +10276,7 @@
         <v>129082536</v>
       </c>
       <c r="B98" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>129082514</v>
       </c>
       <c r="B100" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>129082556</v>
       </c>
       <c r="B101" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10679,10 +10679,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129082621</v>
+        <v>129082532</v>
       </c>
       <c r="B102" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10690,34 +10690,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>436086</v>
+        <v>436295</v>
       </c>
       <c r="R102" t="n">
-        <v>6786788</v>
+        <v>6786848</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10776,10 +10784,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129082642</v>
+        <v>129082531</v>
       </c>
       <c r="B103" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10787,34 +10795,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>436506</v>
+        <v>436246</v>
       </c>
       <c r="R103" t="n">
-        <v>6786683</v>
+        <v>6786863</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10873,45 +10889,54 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129082650</v>
+        <v>129082578</v>
       </c>
       <c r="B104" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>436235</v>
+        <v>436368</v>
       </c>
       <c r="R104" t="n">
-        <v>6786944</v>
+        <v>6786971</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10952,6 +10977,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -10970,10 +10996,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129082531</v>
+        <v>129082621</v>
       </c>
       <c r="B105" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10981,42 +11007,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>436246</v>
+        <v>436086</v>
       </c>
       <c r="R105" t="n">
-        <v>6786863</v>
+        <v>6786788</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11075,10 +11093,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129082532</v>
+        <v>129082642</v>
       </c>
       <c r="B106" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11086,42 +11104,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>436295</v>
+        <v>436506</v>
       </c>
       <c r="R106" t="n">
-        <v>6786848</v>
+        <v>6786683</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11183,7 +11193,7 @@
         <v>129082591</v>
       </c>
       <c r="B107" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11277,54 +11287,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129082578</v>
+        <v>129082650</v>
       </c>
       <c r="B108" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>436368</v>
+        <v>436235</v>
       </c>
       <c r="R108" t="n">
-        <v>6786971</v>
+        <v>6786944</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11365,7 +11366,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11387,7 +11387,7 @@
         <v>129082509</v>
       </c>
       <c r="B109" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>129082628</v>
       </c>
       <c r="B110" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11578,10 +11578,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129082627</v>
+        <v>129082632</v>
       </c>
       <c r="B111" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11613,10 +11613,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>436246</v>
+        <v>436334</v>
       </c>
       <c r="R111" t="n">
-        <v>6786881</v>
+        <v>6786685</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11675,10 +11675,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129082668</v>
+        <v>129082609</v>
       </c>
       <c r="B112" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11710,10 +11710,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>435933</v>
+        <v>435914</v>
       </c>
       <c r="R112" t="n">
-        <v>6786585</v>
+        <v>6786598</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11772,10 +11772,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129082632</v>
+        <v>129082592</v>
       </c>
       <c r="B113" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11783,21 +11783,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11807,10 +11807,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>436334</v>
+        <v>436095</v>
       </c>
       <c r="R113" t="n">
-        <v>6786685</v>
+        <v>6786744</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11869,10 +11869,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129082609</v>
+        <v>129082627</v>
       </c>
       <c r="B114" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11904,10 +11904,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>435914</v>
+        <v>436246</v>
       </c>
       <c r="R114" t="n">
-        <v>6786598</v>
+        <v>6786881</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11966,10 +11966,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129082592</v>
+        <v>129082668</v>
       </c>
       <c r="B115" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11977,21 +11977,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12001,10 +12001,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>436095</v>
+        <v>435933</v>
       </c>
       <c r="R115" t="n">
-        <v>6786744</v>
+        <v>6786585</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12066,7 +12066,7 @@
         <v>129082645</v>
       </c>
       <c r="B116" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>129082633</v>
       </c>
       <c r="B117" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129082580</v>
+        <v>129082586</v>
       </c>
       <c r="B118" t="n">
         <v>8450</v>
@@ -12301,10 +12301,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>436280</v>
+        <v>435931</v>
       </c>
       <c r="R118" t="n">
-        <v>6786936</v>
+        <v>6786572</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12364,7 +12364,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129082560</v>
+        <v>129082576</v>
       </c>
       <c r="B119" t="n">
         <v>8450</v>
@@ -12408,10 +12408,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>435897</v>
+        <v>436417</v>
       </c>
       <c r="R119" t="n">
-        <v>6786676</v>
+        <v>6786827</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12471,7 +12471,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129082576</v>
+        <v>129082580</v>
       </c>
       <c r="B120" t="n">
         <v>8450</v>
@@ -12515,10 +12515,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>436417</v>
+        <v>436280</v>
       </c>
       <c r="R120" t="n">
-        <v>6786827</v>
+        <v>6786936</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12578,7 +12578,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129082586</v>
+        <v>129082560</v>
       </c>
       <c r="B121" t="n">
         <v>8450</v>
@@ -12622,10 +12622,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>435931</v>
+        <v>435897</v>
       </c>
       <c r="R121" t="n">
-        <v>6786572</v>
+        <v>6786676</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12688,7 +12688,7 @@
         <v>129082554</v>
       </c>
       <c r="B122" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>129082618</v>
       </c>
       <c r="B123" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12879,10 +12879,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129082613</v>
+        <v>129082598</v>
       </c>
       <c r="B124" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12890,21 +12890,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12914,10 +12914,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>435886</v>
+        <v>436107</v>
       </c>
       <c r="R124" t="n">
-        <v>6786666</v>
+        <v>6786875</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12976,10 +12976,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129082598</v>
+        <v>129082613</v>
       </c>
       <c r="B125" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12987,21 +12987,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13011,10 +13011,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>436107</v>
+        <v>435886</v>
       </c>
       <c r="R125" t="n">
-        <v>6786875</v>
+        <v>6786666</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13073,7 +13073,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129082563</v>
+        <v>129082565</v>
       </c>
       <c r="B126" t="n">
         <v>8450</v>
@@ -13117,10 +13117,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436055</v>
+        <v>436230</v>
       </c>
       <c r="R126" t="n">
-        <v>6786776</v>
+        <v>6786855</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13180,7 +13180,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129082565</v>
+        <v>129082563</v>
       </c>
       <c r="B127" t="n">
         <v>8450</v>
@@ -13224,10 +13224,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>436230</v>
+        <v>436055</v>
       </c>
       <c r="R127" t="n">
-        <v>6786855</v>
+        <v>6786776</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13287,45 +13287,54 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129082596</v>
+        <v>129082583</v>
       </c>
       <c r="B128" t="n">
-        <v>78792</v>
+        <v>8450</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>436432</v>
+        <v>436011</v>
       </c>
       <c r="R128" t="n">
-        <v>6786558</v>
+        <v>6786844</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13366,6 +13375,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13384,45 +13394,54 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129082626</v>
+        <v>129082558</v>
       </c>
       <c r="B129" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>436240</v>
+        <v>435909</v>
       </c>
       <c r="R129" t="n">
-        <v>6786833</v>
+        <v>6786616</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13463,6 +13482,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13481,10 +13501,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129082664</v>
+        <v>129082547</v>
       </c>
       <c r="B130" t="n">
-        <v>79035</v>
+        <v>78797</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13492,21 +13512,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13516,10 +13536,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436029</v>
+        <v>436172</v>
       </c>
       <c r="R130" t="n">
-        <v>6786750</v>
+        <v>6786825</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13581,7 +13601,7 @@
         <v>129082535</v>
       </c>
       <c r="B131" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13683,54 +13703,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129082558</v>
+        <v>129082596</v>
       </c>
       <c r="B132" t="n">
-        <v>8450</v>
+        <v>78796</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>435909</v>
+        <v>436432</v>
       </c>
       <c r="R132" t="n">
-        <v>6786616</v>
+        <v>6786558</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13771,7 +13782,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13790,54 +13800,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129082583</v>
+        <v>129082626</v>
       </c>
       <c r="B133" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>436011</v>
+        <v>436240</v>
       </c>
       <c r="R133" t="n">
-        <v>6786844</v>
+        <v>6786833</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13878,7 +13879,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -13897,10 +13897,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129082547</v>
+        <v>129082664</v>
       </c>
       <c r="B134" t="n">
-        <v>78793</v>
+        <v>79039</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13908,21 +13908,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13932,10 +13932,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>436172</v>
+        <v>436029</v>
       </c>
       <c r="R134" t="n">
-        <v>6786825</v>
+        <v>6786750</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>

--- a/artfynd/A 49064-2025 artfynd.xlsx
+++ b/artfynd/A 49064-2025 artfynd.xlsx
@@ -1267,45 +1267,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129082651</v>
+        <v>129082575</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436254</v>
+        <v>436432</v>
       </c>
       <c r="R8" t="n">
-        <v>6786925</v>
+        <v>6786759</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,6 +1355,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1364,45 +1374,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129082638</v>
+        <v>129082574</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436456</v>
+        <v>436455</v>
       </c>
       <c r="R9" t="n">
-        <v>6786598</v>
+        <v>6786732</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1443,6 +1462,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1461,54 +1481,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129082575</v>
+        <v>129082651</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436432</v>
+        <v>436254</v>
       </c>
       <c r="R10" t="n">
-        <v>6786759</v>
+        <v>6786925</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,7 +1560,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1568,54 +1578,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129082574</v>
+        <v>129082638</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436455</v>
+        <v>436456</v>
       </c>
       <c r="R11" t="n">
-        <v>6786732</v>
+        <v>6786598</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1656,7 +1657,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2683,7 +2683,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129082614</v>
+        <v>129082640</v>
       </c>
       <c r="B22" t="n">
         <v>79039</v>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435889</v>
+        <v>436530</v>
       </c>
       <c r="R22" t="n">
-        <v>6786670</v>
+        <v>6786657</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129082549</v>
+        <v>129082614</v>
       </c>
       <c r="B24" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2896,21 +2896,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436322</v>
+        <v>435889</v>
       </c>
       <c r="R24" t="n">
-        <v>6786798</v>
+        <v>6786670</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2982,10 +2982,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129082640</v>
+        <v>129082549</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>78797</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2993,21 +2993,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436530</v>
+        <v>436322</v>
       </c>
       <c r="R25" t="n">
-        <v>6786657</v>
+        <v>6786798</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -7291,54 +7291,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129082572</v>
+        <v>129082507</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>79658</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436553</v>
+        <v>436265</v>
       </c>
       <c r="R68" t="n">
-        <v>6786640</v>
+        <v>6786874</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7379,7 +7370,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7398,10 +7388,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129082552</v>
+        <v>129082610</v>
       </c>
       <c r="B69" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7409,21 +7399,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7433,10 +7423,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>436206</v>
+        <v>435906</v>
       </c>
       <c r="R69" t="n">
-        <v>6786892</v>
+        <v>6786603</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7495,10 +7485,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129082550</v>
+        <v>129082528</v>
       </c>
       <c r="B70" t="n">
-        <v>78797</v>
+        <v>57722</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7506,34 +7496,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436361</v>
+        <v>436042</v>
       </c>
       <c r="R70" t="n">
-        <v>6786687</v>
+        <v>6786785</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7592,45 +7590,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129082507</v>
+        <v>129082572</v>
       </c>
       <c r="B71" t="n">
-        <v>79658</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436265</v>
+        <v>436553</v>
       </c>
       <c r="R71" t="n">
-        <v>6786874</v>
+        <v>6786640</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7671,6 +7678,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7689,10 +7697,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129082610</v>
+        <v>129082552</v>
       </c>
       <c r="B72" t="n">
-        <v>79039</v>
+        <v>78797</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7700,21 +7708,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7724,10 +7732,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435906</v>
+        <v>436206</v>
       </c>
       <c r="R72" t="n">
-        <v>6786603</v>
+        <v>6786892</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7786,10 +7794,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129082528</v>
+        <v>129082550</v>
       </c>
       <c r="B73" t="n">
-        <v>57722</v>
+        <v>78797</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7797,42 +7805,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436042</v>
+        <v>436361</v>
       </c>
       <c r="R73" t="n">
-        <v>6786785</v>
+        <v>6786687</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8604,53 +8604,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129082521</v>
+        <v>129082620</v>
       </c>
       <c r="B81" t="n">
-        <v>56915</v>
+        <v>79039</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>436093</v>
+        <v>436035</v>
       </c>
       <c r="R81" t="n">
-        <v>6786769</v>
+        <v>6786730</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8709,10 +8701,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129082620</v>
+        <v>129082513</v>
       </c>
       <c r="B82" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8720,21 +8712,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8744,10 +8736,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>436035</v>
+        <v>436205</v>
       </c>
       <c r="R82" t="n">
-        <v>6786730</v>
+        <v>6786914</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8806,10 +8798,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129082513</v>
+        <v>129082635</v>
       </c>
       <c r="B83" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8817,21 +8809,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8841,10 +8833,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>436205</v>
+        <v>436350</v>
       </c>
       <c r="R83" t="n">
-        <v>6786914</v>
+        <v>6786631</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8903,7 +8895,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129082635</v>
+        <v>129082649</v>
       </c>
       <c r="B84" t="n">
         <v>79039</v>
@@ -8938,10 +8930,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>436350</v>
+        <v>436277</v>
       </c>
       <c r="R84" t="n">
-        <v>6786631</v>
+        <v>6786944</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9000,7 +8992,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129082649</v>
+        <v>129082617</v>
       </c>
       <c r="B85" t="n">
         <v>79039</v>
@@ -9035,10 +9027,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>436277</v>
+        <v>436010</v>
       </c>
       <c r="R85" t="n">
-        <v>6786944</v>
+        <v>6786752</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9097,7 +9089,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129082617</v>
+        <v>129082667</v>
       </c>
       <c r="B86" t="n">
         <v>79039</v>
@@ -9132,10 +9124,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>436010</v>
+        <v>435965</v>
       </c>
       <c r="R86" t="n">
-        <v>6786752</v>
+        <v>6786476</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9194,45 +9186,53 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129082667</v>
+        <v>129082521</v>
       </c>
       <c r="B87" t="n">
-        <v>79039</v>
+        <v>56915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>435965</v>
+        <v>436093</v>
       </c>
       <c r="R87" t="n">
-        <v>6786476</v>
+        <v>6786769</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10679,10 +10679,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129082532</v>
+        <v>129082621</v>
       </c>
       <c r="B102" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10690,42 +10690,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>436295</v>
+        <v>436086</v>
       </c>
       <c r="R102" t="n">
-        <v>6786848</v>
+        <v>6786788</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10784,10 +10776,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129082531</v>
+        <v>129082642</v>
       </c>
       <c r="B103" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10795,42 +10787,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>436246</v>
+        <v>436506</v>
       </c>
       <c r="R103" t="n">
-        <v>6786863</v>
+        <v>6786683</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10889,54 +10873,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129082578</v>
+        <v>129082591</v>
       </c>
       <c r="B104" t="n">
-        <v>8450</v>
+        <v>78796</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>436368</v>
+        <v>436044</v>
       </c>
       <c r="R104" t="n">
-        <v>6786971</v>
+        <v>6786741</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10977,7 +10952,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -10996,7 +10970,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129082621</v>
+        <v>129082650</v>
       </c>
       <c r="B105" t="n">
         <v>79039</v>
@@ -11031,10 +11005,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>436086</v>
+        <v>436235</v>
       </c>
       <c r="R105" t="n">
-        <v>6786788</v>
+        <v>6786944</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11093,10 +11067,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129082642</v>
+        <v>129082532</v>
       </c>
       <c r="B106" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11104,34 +11078,42 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>436506</v>
+        <v>436295</v>
       </c>
       <c r="R106" t="n">
-        <v>6786683</v>
+        <v>6786848</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11190,10 +11172,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129082591</v>
+        <v>129082531</v>
       </c>
       <c r="B107" t="n">
-        <v>78796</v>
+        <v>57722</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11201,34 +11183,42 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436044</v>
+        <v>436246</v>
       </c>
       <c r="R107" t="n">
-        <v>6786741</v>
+        <v>6786863</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11287,45 +11277,54 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129082650</v>
+        <v>129082578</v>
       </c>
       <c r="B108" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>436235</v>
+        <v>436368</v>
       </c>
       <c r="R108" t="n">
-        <v>6786944</v>
+        <v>6786971</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11366,6 +11365,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -13287,54 +13287,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129082583</v>
+        <v>129082596</v>
       </c>
       <c r="B128" t="n">
-        <v>8450</v>
+        <v>78796</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>436011</v>
+        <v>436432</v>
       </c>
       <c r="R128" t="n">
-        <v>6786844</v>
+        <v>6786558</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13375,7 +13366,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13394,54 +13384,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129082558</v>
+        <v>129082626</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>435909</v>
+        <v>436240</v>
       </c>
       <c r="R129" t="n">
-        <v>6786616</v>
+        <v>6786833</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13482,7 +13463,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13501,10 +13481,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129082547</v>
+        <v>129082664</v>
       </c>
       <c r="B130" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13512,21 +13492,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13536,10 +13516,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436172</v>
+        <v>436029</v>
       </c>
       <c r="R130" t="n">
-        <v>6786825</v>
+        <v>6786750</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13703,45 +13683,54 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129082596</v>
+        <v>129082583</v>
       </c>
       <c r="B132" t="n">
-        <v>78796</v>
+        <v>8450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>436432</v>
+        <v>436011</v>
       </c>
       <c r="R132" t="n">
-        <v>6786558</v>
+        <v>6786844</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13782,6 +13771,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13800,45 +13790,54 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129082626</v>
+        <v>129082558</v>
       </c>
       <c r="B133" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>436240</v>
+        <v>435909</v>
       </c>
       <c r="R133" t="n">
-        <v>6786833</v>
+        <v>6786616</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13879,6 +13878,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -13897,10 +13897,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129082664</v>
+        <v>129082547</v>
       </c>
       <c r="B134" t="n">
-        <v>79039</v>
+        <v>78797</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13908,21 +13908,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13932,10 +13932,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>436029</v>
+        <v>436172</v>
       </c>
       <c r="R134" t="n">
-        <v>6786750</v>
+        <v>6786825</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>

--- a/artfynd/A 49064-2025 artfynd.xlsx
+++ b/artfynd/A 49064-2025 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129082637</v>
+        <v>129082659</v>
       </c>
       <c r="B3" t="n">
         <v>79039</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436410</v>
+        <v>435974</v>
       </c>
       <c r="R3" t="n">
-        <v>6786560</v>
+        <v>6786534</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129082659</v>
+        <v>129082637</v>
       </c>
       <c r="B4" t="n">
         <v>79039</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435974</v>
+        <v>436410</v>
       </c>
       <c r="R4" t="n">
-        <v>6786534</v>
+        <v>6786560</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,45 +966,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129082546</v>
+        <v>129082570</v>
       </c>
       <c r="B5" t="n">
-        <v>78797</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436092</v>
+        <v>436428</v>
       </c>
       <c r="R5" t="n">
-        <v>6786744</v>
+        <v>6786577</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,6 +1054,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1063,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129082544</v>
+        <v>129082546</v>
       </c>
       <c r="B6" t="n">
         <v>78797</v>
@@ -1098,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436044</v>
+        <v>436092</v>
       </c>
       <c r="R6" t="n">
-        <v>6786741</v>
+        <v>6786744</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,54 +1170,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129082570</v>
+        <v>129082544</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>78797</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436428</v>
+        <v>436044</v>
       </c>
       <c r="R7" t="n">
-        <v>6786577</v>
+        <v>6786741</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,7 +1249,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1267,54 +1267,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129082575</v>
+        <v>129082651</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436432</v>
+        <v>436254</v>
       </c>
       <c r="R8" t="n">
-        <v>6786759</v>
+        <v>6786925</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,7 +1346,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1374,54 +1364,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129082574</v>
+        <v>129082638</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436455</v>
+        <v>436456</v>
       </c>
       <c r="R9" t="n">
-        <v>6786732</v>
+        <v>6786598</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1462,7 +1443,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1481,45 +1461,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129082651</v>
+        <v>129082575</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436254</v>
+        <v>436432</v>
       </c>
       <c r="R10" t="n">
-        <v>6786925</v>
+        <v>6786759</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,6 +1549,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1578,45 +1568,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129082638</v>
+        <v>129082574</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436456</v>
+        <v>436455</v>
       </c>
       <c r="R11" t="n">
-        <v>6786598</v>
+        <v>6786732</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,6 +1656,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129082508</v>
+        <v>129082510</v>
       </c>
       <c r="B12" t="n">
         <v>79658</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436338</v>
+        <v>436506</v>
       </c>
       <c r="R12" t="n">
-        <v>6786741</v>
+        <v>6786715</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129082510</v>
+        <v>129082508</v>
       </c>
       <c r="B13" t="n">
         <v>79658</v>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436506</v>
+        <v>436338</v>
       </c>
       <c r="R13" t="n">
-        <v>6786715</v>
+        <v>6786741</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2188,54 +2188,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129082568</v>
+        <v>129082622</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436409</v>
+        <v>436101</v>
       </c>
       <c r="R17" t="n">
-        <v>6786563</v>
+        <v>6786774</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2276,7 +2267,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2295,7 +2285,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129082652</v>
+        <v>129082630</v>
       </c>
       <c r="B18" t="n">
         <v>79039</v>
@@ -2330,10 +2320,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436190</v>
+        <v>436320</v>
       </c>
       <c r="R18" t="n">
-        <v>6786911</v>
+        <v>6786718</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2392,7 +2382,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129082622</v>
+        <v>129082652</v>
       </c>
       <c r="B19" t="n">
         <v>79039</v>
@@ -2427,10 +2417,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436101</v>
+        <v>436190</v>
       </c>
       <c r="R19" t="n">
-        <v>6786774</v>
+        <v>6786911</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2586,45 +2576,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129082630</v>
+        <v>129082568</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436320</v>
+        <v>436409</v>
       </c>
       <c r="R21" t="n">
-        <v>6786718</v>
+        <v>6786563</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2665,6 +2664,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129082640</v>
+        <v>129082549</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>78797</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2694,21 +2694,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436530</v>
+        <v>436322</v>
       </c>
       <c r="R22" t="n">
-        <v>6786657</v>
+        <v>6786798</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2780,10 +2780,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129082537</v>
+        <v>129082614</v>
       </c>
       <c r="B23" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2791,42 +2791,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436399</v>
+        <v>435889</v>
       </c>
       <c r="R23" t="n">
-        <v>6786867</v>
+        <v>6786670</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2885,7 +2877,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129082614</v>
+        <v>129082640</v>
       </c>
       <c r="B24" t="n">
         <v>79039</v>
@@ -2920,10 +2912,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435889</v>
+        <v>436530</v>
       </c>
       <c r="R24" t="n">
-        <v>6786670</v>
+        <v>6786657</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2982,10 +2974,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129082549</v>
+        <v>129082537</v>
       </c>
       <c r="B25" t="n">
-        <v>78797</v>
+        <v>57722</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2993,34 +2985,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436322</v>
+        <v>436399</v>
       </c>
       <c r="R25" t="n">
-        <v>6786798</v>
+        <v>6786867</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3079,7 +3079,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129082504</v>
+        <v>129082512</v>
       </c>
       <c r="B26" t="n">
         <v>79658</v>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436031</v>
+        <v>436428</v>
       </c>
       <c r="R26" t="n">
-        <v>6786744</v>
+        <v>6786809</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3176,10 +3176,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129082636</v>
+        <v>129082505</v>
       </c>
       <c r="B27" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3187,21 +3187,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3211,10 +3211,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436431</v>
+        <v>436095</v>
       </c>
       <c r="R27" t="n">
-        <v>6786583</v>
+        <v>6786747</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3273,10 +3273,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129082505</v>
+        <v>129082589</v>
       </c>
       <c r="B28" t="n">
-        <v>79658</v>
+        <v>78796</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3284,21 +3284,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436095</v>
+        <v>436033</v>
       </c>
       <c r="R28" t="n">
-        <v>6786747</v>
+        <v>6786758</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3370,10 +3370,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129082653</v>
+        <v>129082504</v>
       </c>
       <c r="B29" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3381,37 +3381,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436092</v>
+        <v>436031</v>
       </c>
       <c r="R29" t="n">
-        <v>6786889</v>
+        <v>6786744</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3452,7 +3449,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3471,10 +3467,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129082512</v>
+        <v>129082636</v>
       </c>
       <c r="B30" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3482,21 +3478,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3506,10 +3502,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436428</v>
+        <v>436431</v>
       </c>
       <c r="R30" t="n">
-        <v>6786809</v>
+        <v>6786583</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3568,10 +3564,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129082589</v>
+        <v>129082653</v>
       </c>
       <c r="B31" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3579,34 +3575,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436033</v>
+        <v>436092</v>
       </c>
       <c r="R31" t="n">
-        <v>6786758</v>
+        <v>6786889</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3647,6 +3646,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3877,53 +3877,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129082588</v>
+        <v>129082662</v>
       </c>
       <c r="B34" t="n">
-        <v>58095</v>
+        <v>79039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435979</v>
+        <v>435932</v>
       </c>
       <c r="R34" t="n">
-        <v>6786531</v>
+        <v>6786581</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3982,10 +3974,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129082543</v>
+        <v>129082612</v>
       </c>
       <c r="B35" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3993,21 +3985,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4017,10 +4009,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436027</v>
+        <v>435883</v>
       </c>
       <c r="R35" t="n">
-        <v>6786747</v>
+        <v>6786641</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4079,10 +4071,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129082551</v>
+        <v>129082646</v>
       </c>
       <c r="B36" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4090,21 +4082,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4114,10 +4106,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436436</v>
+        <v>436400</v>
       </c>
       <c r="R36" t="n">
-        <v>6786563</v>
+        <v>6786855</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4176,10 +4168,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129082662</v>
+        <v>129082538</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4187,34 +4179,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435932</v>
+        <v>436141</v>
       </c>
       <c r="R37" t="n">
-        <v>6786581</v>
+        <v>6786882</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4273,10 +4273,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129082612</v>
+        <v>129082533</v>
       </c>
       <c r="B38" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4284,34 +4284,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435883</v>
+        <v>436445</v>
       </c>
       <c r="R38" t="n">
-        <v>6786641</v>
+        <v>6786610</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4370,45 +4378,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129082646</v>
+        <v>129082588</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>58095</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436400</v>
+        <v>435979</v>
       </c>
       <c r="R39" t="n">
-        <v>6786855</v>
+        <v>6786531</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4467,10 +4483,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129082538</v>
+        <v>129082543</v>
       </c>
       <c r="B40" t="n">
-        <v>57722</v>
+        <v>78797</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,42 +4494,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436141</v>
+        <v>436027</v>
       </c>
       <c r="R40" t="n">
-        <v>6786882</v>
+        <v>6786747</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4572,10 +4580,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129082533</v>
+        <v>129082551</v>
       </c>
       <c r="B41" t="n">
-        <v>57722</v>
+        <v>78797</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4583,42 +4591,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436445</v>
+        <v>436436</v>
       </c>
       <c r="R41" t="n">
-        <v>6786610</v>
+        <v>6786563</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4784,10 +4784,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129082590</v>
+        <v>129082663</v>
       </c>
       <c r="B43" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4795,21 +4795,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436051</v>
+        <v>435984</v>
       </c>
       <c r="R43" t="n">
-        <v>6786730</v>
+        <v>6786452</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4978,10 +4978,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129082663</v>
+        <v>129082590</v>
       </c>
       <c r="B45" t="n">
-        <v>79039</v>
+        <v>78796</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4989,21 +4989,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435984</v>
+        <v>436051</v>
       </c>
       <c r="R45" t="n">
-        <v>6786452</v>
+        <v>6786730</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5279,7 +5279,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129082648</v>
+        <v>129082624</v>
       </c>
       <c r="B48" t="n">
         <v>79039</v>
@@ -5308,19 +5308,16 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436353</v>
+        <v>436138</v>
       </c>
       <c r="R48" t="n">
-        <v>6786940</v>
+        <v>6786811</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5361,7 +5358,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5380,7 +5376,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129082611</v>
+        <v>129082648</v>
       </c>
       <c r="B49" t="n">
         <v>79039</v>
@@ -5409,16 +5405,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435898</v>
+        <v>436353</v>
       </c>
       <c r="R49" t="n">
-        <v>6786619</v>
+        <v>6786940</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5459,6 +5458,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5477,7 +5477,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129082624</v>
+        <v>129082611</v>
       </c>
       <c r="B50" t="n">
         <v>79039</v>
@@ -5512,10 +5512,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436138</v>
+        <v>435898</v>
       </c>
       <c r="R50" t="n">
-        <v>6786811</v>
+        <v>6786619</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6184,37 +6184,43 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129082555</v>
+        <v>129082577</v>
       </c>
       <c r="B57" t="n">
-        <v>78797</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6222,10 +6228,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>436072</v>
+        <v>436381</v>
       </c>
       <c r="R57" t="n">
-        <v>6786886</v>
+        <v>6786936</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6285,7 +6291,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129082577</v>
+        <v>129082564</v>
       </c>
       <c r="B58" t="n">
         <v>8450</v>
@@ -6319,7 +6325,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6329,10 +6335,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>436381</v>
+        <v>436166</v>
       </c>
       <c r="R58" t="n">
-        <v>6786936</v>
+        <v>6786846</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6392,43 +6398,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129082564</v>
+        <v>129082555</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>78797</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>436166</v>
+        <v>436072</v>
       </c>
       <c r="R59" t="n">
-        <v>6786846</v>
+        <v>6786886</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6499,10 +6499,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129082644</v>
+        <v>129082548</v>
       </c>
       <c r="B60" t="n">
-        <v>79039</v>
+        <v>78797</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6510,21 +6510,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>436432</v>
+        <v>436268</v>
       </c>
       <c r="R60" t="n">
-        <v>6786765</v>
+        <v>6786874</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6596,10 +6596,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129082597</v>
+        <v>129082516</v>
       </c>
       <c r="B61" t="n">
-        <v>78796</v>
+        <v>79629</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6607,34 +6607,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436469</v>
+        <v>436470</v>
       </c>
       <c r="R61" t="n">
-        <v>6786748</v>
+        <v>6786714</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6675,6 +6678,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6693,10 +6697,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129082666</v>
+        <v>129082545</v>
       </c>
       <c r="B62" t="n">
-        <v>79039</v>
+        <v>78797</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6704,34 +6708,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>436618</v>
+        <v>436085</v>
       </c>
       <c r="R62" t="n">
-        <v>6786620</v>
+        <v>6786778</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6772,6 +6779,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6790,10 +6798,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129082506</v>
+        <v>129082515</v>
       </c>
       <c r="B63" t="n">
-        <v>79658</v>
+        <v>79629</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6801,21 +6809,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6828,10 +6836,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>436172</v>
+        <v>436075</v>
       </c>
       <c r="R63" t="n">
-        <v>6786831</v>
+        <v>6786747</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6891,10 +6899,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129082548</v>
+        <v>129082597</v>
       </c>
       <c r="B64" t="n">
-        <v>78797</v>
+        <v>78796</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6902,21 +6910,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6926,10 +6934,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>436268</v>
+        <v>436469</v>
       </c>
       <c r="R64" t="n">
-        <v>6786874</v>
+        <v>6786748</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6988,10 +6996,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129082516</v>
+        <v>129082506</v>
       </c>
       <c r="B65" t="n">
-        <v>79629</v>
+        <v>79658</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6999,21 +7007,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7026,10 +7034,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>436470</v>
+        <v>436172</v>
       </c>
       <c r="R65" t="n">
-        <v>6786714</v>
+        <v>6786831</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7089,10 +7097,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129082545</v>
+        <v>129082644</v>
       </c>
       <c r="B66" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7100,37 +7108,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436085</v>
+        <v>436432</v>
       </c>
       <c r="R66" t="n">
-        <v>6786778</v>
+        <v>6786765</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7171,7 +7176,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7190,10 +7194,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129082515</v>
+        <v>129082666</v>
       </c>
       <c r="B67" t="n">
-        <v>79629</v>
+        <v>79039</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7201,37 +7205,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436075</v>
+        <v>436618</v>
       </c>
       <c r="R67" t="n">
-        <v>6786747</v>
+        <v>6786620</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7272,7 +7273,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7291,10 +7291,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129082507</v>
+        <v>129082528</v>
       </c>
       <c r="B68" t="n">
-        <v>79658</v>
+        <v>57722</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7302,34 +7302,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436265</v>
+        <v>436042</v>
       </c>
       <c r="R68" t="n">
-        <v>6786874</v>
+        <v>6786785</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7388,10 +7396,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129082610</v>
+        <v>129082507</v>
       </c>
       <c r="B69" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7399,21 +7407,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7423,10 +7431,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435906</v>
+        <v>436265</v>
       </c>
       <c r="R69" t="n">
-        <v>6786603</v>
+        <v>6786874</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7485,10 +7493,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129082528</v>
+        <v>129082610</v>
       </c>
       <c r="B70" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7496,42 +7504,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436042</v>
+        <v>435906</v>
       </c>
       <c r="R70" t="n">
-        <v>6786785</v>
+        <v>6786603</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7891,10 +7891,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129082639</v>
+        <v>129082503</v>
       </c>
       <c r="B74" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7902,21 +7902,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436568</v>
+        <v>436052</v>
       </c>
       <c r="R74" t="n">
-        <v>6786650</v>
+        <v>6786720</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7988,45 +7988,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129082503</v>
+        <v>129082579</v>
       </c>
       <c r="B75" t="n">
-        <v>79658</v>
+        <v>8450</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436052</v>
+        <v>436306</v>
       </c>
       <c r="R75" t="n">
-        <v>6786720</v>
+        <v>6786960</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8067,6 +8076,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8085,7 +8095,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129082634</v>
+        <v>129082639</v>
       </c>
       <c r="B76" t="n">
         <v>79039</v>
@@ -8120,10 +8130,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436338</v>
+        <v>436568</v>
       </c>
       <c r="R76" t="n">
-        <v>6786664</v>
+        <v>6786650</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8182,10 +8192,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129082534</v>
+        <v>129082634</v>
       </c>
       <c r="B77" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8193,42 +8203,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436565</v>
+        <v>436338</v>
       </c>
       <c r="R77" t="n">
-        <v>6786624</v>
+        <v>6786664</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8287,7 +8289,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129082539</v>
+        <v>129082534</v>
       </c>
       <c r="B78" t="n">
         <v>57722</v>
@@ -8320,7 +8322,7 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -8330,10 +8332,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436069</v>
+        <v>436565</v>
       </c>
       <c r="R78" t="n">
-        <v>6786886</v>
+        <v>6786624</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8392,7 +8394,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129082540</v>
+        <v>129082539</v>
       </c>
       <c r="B79" t="n">
         <v>57722</v>
@@ -8425,7 +8427,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -8435,10 +8437,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436188</v>
+        <v>436069</v>
       </c>
       <c r="R79" t="n">
-        <v>6786921</v>
+        <v>6786886</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8497,41 +8499,40 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129082579</v>
+        <v>129082540</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>57722</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8541,10 +8542,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436306</v>
+        <v>436188</v>
       </c>
       <c r="R80" t="n">
-        <v>6786960</v>
+        <v>6786921</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8585,7 +8586,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8604,7 +8604,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129082620</v>
+        <v>129082667</v>
       </c>
       <c r="B81" t="n">
         <v>79039</v>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>436035</v>
+        <v>435965</v>
       </c>
       <c r="R81" t="n">
-        <v>6786730</v>
+        <v>6786476</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8701,10 +8701,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129082513</v>
+        <v>129082620</v>
       </c>
       <c r="B82" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8712,21 +8712,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>436205</v>
+        <v>436035</v>
       </c>
       <c r="R82" t="n">
-        <v>6786914</v>
+        <v>6786730</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8798,10 +8798,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129082635</v>
+        <v>129082513</v>
       </c>
       <c r="B83" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8809,21 +8809,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>436350</v>
+        <v>436205</v>
       </c>
       <c r="R83" t="n">
-        <v>6786631</v>
+        <v>6786914</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8895,7 +8895,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129082649</v>
+        <v>129082635</v>
       </c>
       <c r="B84" t="n">
         <v>79039</v>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>436277</v>
+        <v>436350</v>
       </c>
       <c r="R84" t="n">
-        <v>6786944</v>
+        <v>6786631</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8992,7 +8992,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129082617</v>
+        <v>129082649</v>
       </c>
       <c r="B85" t="n">
         <v>79039</v>
@@ -9027,10 +9027,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>436010</v>
+        <v>436277</v>
       </c>
       <c r="R85" t="n">
-        <v>6786752</v>
+        <v>6786944</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9089,7 +9089,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129082667</v>
+        <v>129082617</v>
       </c>
       <c r="B86" t="n">
         <v>79039</v>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>435965</v>
+        <v>436010</v>
       </c>
       <c r="R86" t="n">
-        <v>6786476</v>
+        <v>6786752</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9291,10 +9291,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129082654</v>
+        <v>129082536</v>
       </c>
       <c r="B88" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9302,34 +9302,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>436054</v>
+        <v>436544</v>
       </c>
       <c r="R88" t="n">
-        <v>6786881</v>
+        <v>6786666</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9388,45 +9396,48 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129082625</v>
+        <v>129082671</v>
       </c>
       <c r="B89" t="n">
-        <v>79039</v>
+        <v>92833</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>436202</v>
+        <v>436349</v>
       </c>
       <c r="R89" t="n">
-        <v>6786849</v>
+        <v>6786689</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9467,6 +9478,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9485,10 +9497,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129082665</v>
+        <v>129082525</v>
       </c>
       <c r="B90" t="n">
-        <v>79039</v>
+        <v>57885</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9496,34 +9508,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436330</v>
+        <v>435948</v>
       </c>
       <c r="R90" t="n">
-        <v>6786736</v>
+        <v>6786586</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9582,45 +9602,54 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129082606</v>
+        <v>129082582</v>
       </c>
       <c r="B91" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>435970</v>
+        <v>436138</v>
       </c>
       <c r="R91" t="n">
-        <v>6786458</v>
+        <v>6786894</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9661,6 +9690,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9679,10 +9709,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129082619</v>
+        <v>129082514</v>
       </c>
       <c r="B92" t="n">
-        <v>79039</v>
+        <v>79629</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9690,21 +9720,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9714,10 +9744,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>436034</v>
+        <v>436044</v>
       </c>
       <c r="R92" t="n">
-        <v>6786743</v>
+        <v>6786741</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9776,10 +9806,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129082616</v>
+        <v>129082556</v>
       </c>
       <c r="B93" t="n">
-        <v>79039</v>
+        <v>78797</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9787,21 +9817,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9811,10 +9841,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436012</v>
+        <v>436010</v>
       </c>
       <c r="R93" t="n">
-        <v>6786734</v>
+        <v>6786852</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9873,7 +9903,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129082595</v>
+        <v>129082594</v>
       </c>
       <c r="B94" t="n">
         <v>78796</v>
@@ -9908,10 +9938,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436361</v>
+        <v>436339</v>
       </c>
       <c r="R94" t="n">
-        <v>6786688</v>
+        <v>6786747</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9970,7 +10000,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129082594</v>
+        <v>129082595</v>
       </c>
       <c r="B95" t="n">
         <v>78796</v>
@@ -10005,10 +10035,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436339</v>
+        <v>436361</v>
       </c>
       <c r="R95" t="n">
-        <v>6786747</v>
+        <v>6786688</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10067,10 +10097,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129082525</v>
+        <v>129082654</v>
       </c>
       <c r="B96" t="n">
-        <v>57885</v>
+        <v>79039</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10078,42 +10108,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>435948</v>
+        <v>436054</v>
       </c>
       <c r="R96" t="n">
-        <v>6786586</v>
+        <v>6786881</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10172,48 +10194,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129082671</v>
+        <v>129082625</v>
       </c>
       <c r="B97" t="n">
-        <v>92826</v>
+        <v>79039</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436349</v>
+        <v>436202</v>
       </c>
       <c r="R97" t="n">
-        <v>6786689</v>
+        <v>6786849</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10254,7 +10273,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10273,10 +10291,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129082536</v>
+        <v>129082665</v>
       </c>
       <c r="B98" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10284,42 +10302,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436544</v>
+        <v>436330</v>
       </c>
       <c r="R98" t="n">
-        <v>6786666</v>
+        <v>6786736</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10378,54 +10388,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129082582</v>
+        <v>129082606</v>
       </c>
       <c r="B99" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436138</v>
+        <v>435970</v>
       </c>
       <c r="R99" t="n">
-        <v>6786894</v>
+        <v>6786458</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10466,7 +10467,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10485,10 +10485,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129082514</v>
+        <v>129082619</v>
       </c>
       <c r="B100" t="n">
-        <v>79629</v>
+        <v>79039</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10496,21 +10496,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10520,10 +10520,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436044</v>
+        <v>436034</v>
       </c>
       <c r="R100" t="n">
-        <v>6786741</v>
+        <v>6786743</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10582,10 +10582,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129082556</v>
+        <v>129082616</v>
       </c>
       <c r="B101" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10593,21 +10593,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10617,10 +10617,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>436010</v>
+        <v>436012</v>
       </c>
       <c r="R101" t="n">
-        <v>6786852</v>
+        <v>6786734</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10679,7 +10679,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129082621</v>
+        <v>129082642</v>
       </c>
       <c r="B102" t="n">
         <v>79039</v>
@@ -10714,10 +10714,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>436086</v>
+        <v>436506</v>
       </c>
       <c r="R102" t="n">
-        <v>6786788</v>
+        <v>6786683</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10776,10 +10776,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129082642</v>
+        <v>129082591</v>
       </c>
       <c r="B103" t="n">
-        <v>79039</v>
+        <v>78796</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10787,21 +10787,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>436506</v>
+        <v>436044</v>
       </c>
       <c r="R103" t="n">
-        <v>6786683</v>
+        <v>6786741</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10873,10 +10873,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129082591</v>
+        <v>129082621</v>
       </c>
       <c r="B104" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10884,21 +10884,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10908,10 +10908,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>436044</v>
+        <v>436086</v>
       </c>
       <c r="R104" t="n">
-        <v>6786741</v>
+        <v>6786788</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11481,10 +11481,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129082628</v>
+        <v>129082592</v>
       </c>
       <c r="B110" t="n">
-        <v>79039</v>
+        <v>78796</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11492,21 +11492,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11516,10 +11516,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>436327</v>
+        <v>436095</v>
       </c>
       <c r="R110" t="n">
-        <v>6786767</v>
+        <v>6786744</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11578,7 +11578,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129082632</v>
+        <v>129082628</v>
       </c>
       <c r="B111" t="n">
         <v>79039</v>
@@ -11613,10 +11613,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>436334</v>
+        <v>436327</v>
       </c>
       <c r="R111" t="n">
-        <v>6786685</v>
+        <v>6786767</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11675,7 +11675,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129082609</v>
+        <v>129082632</v>
       </c>
       <c r="B112" t="n">
         <v>79039</v>
@@ -11710,10 +11710,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>435914</v>
+        <v>436334</v>
       </c>
       <c r="R112" t="n">
-        <v>6786598</v>
+        <v>6786685</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11772,10 +11772,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129082592</v>
+        <v>129082609</v>
       </c>
       <c r="B113" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11783,21 +11783,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11807,10 +11807,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>436095</v>
+        <v>435914</v>
       </c>
       <c r="R113" t="n">
-        <v>6786744</v>
+        <v>6786598</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12782,10 +12782,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129082618</v>
+        <v>129082598</v>
       </c>
       <c r="B123" t="n">
-        <v>79039</v>
+        <v>78796</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12793,21 +12793,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12817,10 +12817,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>436027</v>
+        <v>436107</v>
       </c>
       <c r="R123" t="n">
-        <v>6786735</v>
+        <v>6786875</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12879,10 +12879,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129082598</v>
+        <v>129082618</v>
       </c>
       <c r="B124" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12890,21 +12890,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12914,10 +12914,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>436107</v>
+        <v>436027</v>
       </c>
       <c r="R124" t="n">
-        <v>6786875</v>
+        <v>6786735</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12976,45 +12976,54 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129082613</v>
+        <v>129082565</v>
       </c>
       <c r="B125" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>435886</v>
+        <v>436230</v>
       </c>
       <c r="R125" t="n">
-        <v>6786666</v>
+        <v>6786855</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13055,6 +13064,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13073,7 +13083,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129082565</v>
+        <v>129082563</v>
       </c>
       <c r="B126" t="n">
         <v>8450</v>
@@ -13117,10 +13127,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436230</v>
+        <v>436055</v>
       </c>
       <c r="R126" t="n">
-        <v>6786855</v>
+        <v>6786776</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13180,54 +13190,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129082563</v>
+        <v>129082613</v>
       </c>
       <c r="B127" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>436055</v>
+        <v>435886</v>
       </c>
       <c r="R127" t="n">
-        <v>6786776</v>
+        <v>6786666</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13268,7 +13269,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13287,10 +13287,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129082596</v>
+        <v>129082547</v>
       </c>
       <c r="B128" t="n">
-        <v>78796</v>
+        <v>78797</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13298,21 +13298,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13322,10 +13322,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>436432</v>
+        <v>436172</v>
       </c>
       <c r="R128" t="n">
-        <v>6786558</v>
+        <v>6786825</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13384,10 +13384,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129082626</v>
+        <v>129082596</v>
       </c>
       <c r="B129" t="n">
-        <v>79039</v>
+        <v>78796</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13395,21 +13395,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>436240</v>
+        <v>436432</v>
       </c>
       <c r="R129" t="n">
-        <v>6786833</v>
+        <v>6786558</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13481,7 +13481,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129082664</v>
+        <v>129082626</v>
       </c>
       <c r="B130" t="n">
         <v>79039</v>
@@ -13516,10 +13516,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436029</v>
+        <v>436240</v>
       </c>
       <c r="R130" t="n">
-        <v>6786750</v>
+        <v>6786833</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13578,10 +13578,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129082535</v>
+        <v>129082664</v>
       </c>
       <c r="B131" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13589,42 +13589,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>436575</v>
+        <v>436029</v>
       </c>
       <c r="R131" t="n">
-        <v>6786632</v>
+        <v>6786750</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13683,41 +13675,40 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129082583</v>
+        <v>129082535</v>
       </c>
       <c r="B132" t="n">
-        <v>8450</v>
+        <v>57722</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -13727,10 +13718,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>436011</v>
+        <v>436575</v>
       </c>
       <c r="R132" t="n">
-        <v>6786844</v>
+        <v>6786632</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13771,7 +13762,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13790,7 +13780,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129082558</v>
+        <v>129082583</v>
       </c>
       <c r="B133" t="n">
         <v>8450</v>
@@ -13834,10 +13824,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>435909</v>
+        <v>436011</v>
       </c>
       <c r="R133" t="n">
-        <v>6786616</v>
+        <v>6786844</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13897,45 +13887,54 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129082547</v>
+        <v>129082558</v>
       </c>
       <c r="B134" t="n">
-        <v>78797</v>
+        <v>8450</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>436172</v>
+        <v>435909</v>
       </c>
       <c r="R134" t="n">
-        <v>6786825</v>
+        <v>6786616</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13976,6 +13975,7 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49064-2025 artfynd.xlsx
+++ b/artfynd/A 49064-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129082641</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129082659</v>
+        <v>129082637</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435974</v>
+        <v>436410</v>
       </c>
       <c r="R3" t="n">
-        <v>6786534</v>
+        <v>6786560</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129082637</v>
+        <v>129082659</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436410</v>
+        <v>435974</v>
       </c>
       <c r="R4" t="n">
-        <v>6786560</v>
+        <v>6786534</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,54 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129082570</v>
+        <v>129082546</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436428</v>
+        <v>436092</v>
       </c>
       <c r="R5" t="n">
-        <v>6786577</v>
+        <v>6786744</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,7 +1045,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1073,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129082546</v>
+        <v>129082544</v>
       </c>
       <c r="B6" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436092</v>
+        <v>436044</v>
       </c>
       <c r="R6" t="n">
-        <v>6786744</v>
+        <v>6786741</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,45 +1160,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129082544</v>
+        <v>129082570</v>
       </c>
       <c r="B7" t="n">
-        <v>78797</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436044</v>
+        <v>436428</v>
       </c>
       <c r="R7" t="n">
-        <v>6786741</v>
+        <v>6786577</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,6 +1248,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1267,45 +1267,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129082651</v>
+        <v>129082575</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436254</v>
+        <v>436432</v>
       </c>
       <c r="R8" t="n">
-        <v>6786925</v>
+        <v>6786759</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,6 +1355,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1364,45 +1374,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129082638</v>
+        <v>129082574</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436456</v>
+        <v>436455</v>
       </c>
       <c r="R9" t="n">
-        <v>6786598</v>
+        <v>6786732</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1443,6 +1462,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1461,54 +1481,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129082575</v>
+        <v>129082638</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436432</v>
+        <v>436456</v>
       </c>
       <c r="R10" t="n">
-        <v>6786759</v>
+        <v>6786598</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,7 +1560,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1568,54 +1578,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129082574</v>
+        <v>129082651</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436455</v>
+        <v>436254</v>
       </c>
       <c r="R11" t="n">
-        <v>6786732</v>
+        <v>6786925</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1656,7 +1657,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>129082510</v>
       </c>
       <c r="B12" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>129082508</v>
       </c>
       <c r="B13" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,53 +1976,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129082522</v>
+        <v>129082622</v>
       </c>
       <c r="B15" t="n">
-        <v>56915</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436195</v>
+        <v>436101</v>
       </c>
       <c r="R15" t="n">
-        <v>6786902</v>
+        <v>6786774</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2081,54 +2073,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129082566</v>
+        <v>129082629</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436258</v>
+        <v>436335</v>
       </c>
       <c r="R16" t="n">
-        <v>6786851</v>
+        <v>6786743</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2169,7 +2152,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2188,10 +2170,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129082622</v>
+        <v>129082630</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2223,10 +2205,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436101</v>
+        <v>436320</v>
       </c>
       <c r="R17" t="n">
-        <v>6786774</v>
+        <v>6786718</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2285,10 +2267,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129082630</v>
+        <v>129082652</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2320,10 +2302,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436320</v>
+        <v>436190</v>
       </c>
       <c r="R18" t="n">
-        <v>6786718</v>
+        <v>6786911</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2382,45 +2364,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129082652</v>
+        <v>129082568</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436190</v>
+        <v>436409</v>
       </c>
       <c r="R19" t="n">
-        <v>6786911</v>
+        <v>6786563</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2461,6 +2452,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2479,45 +2471,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129082629</v>
+        <v>129082566</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436335</v>
+        <v>436258</v>
       </c>
       <c r="R20" t="n">
-        <v>6786743</v>
+        <v>6786851</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2558,6 +2559,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2576,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129082568</v>
+        <v>129082522</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>56917</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2587,30 +2589,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2620,10 +2621,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436409</v>
+        <v>436195</v>
       </c>
       <c r="R21" t="n">
-        <v>6786563</v>
+        <v>6786902</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,7 +2665,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129082549</v>
+        <v>129082640</v>
       </c>
       <c r="B22" t="n">
-        <v>78797</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2694,21 +2694,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436322</v>
+        <v>436530</v>
       </c>
       <c r="R22" t="n">
-        <v>6786798</v>
+        <v>6786657</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2783,7 +2783,7 @@
         <v>129082614</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129082640</v>
+        <v>129082537</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2888,34 +2888,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436530</v>
+        <v>436399</v>
       </c>
       <c r="R24" t="n">
-        <v>6786657</v>
+        <v>6786867</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2974,10 +2982,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129082537</v>
+        <v>129082549</v>
       </c>
       <c r="B25" t="n">
-        <v>57722</v>
+        <v>78799</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2985,42 +2993,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436399</v>
+        <v>436322</v>
       </c>
       <c r="R25" t="n">
-        <v>6786867</v>
+        <v>6786798</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3082,7 +3082,7 @@
         <v>129082512</v>
       </c>
       <c r="B26" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3176,10 +3176,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129082505</v>
+        <v>129082653</v>
       </c>
       <c r="B27" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3187,34 +3187,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436095</v>
+        <v>436092</v>
       </c>
       <c r="R27" t="n">
-        <v>6786747</v>
+        <v>6786889</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3255,6 +3258,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3273,10 +3277,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129082589</v>
+        <v>129082505</v>
       </c>
       <c r="B28" t="n">
-        <v>78796</v>
+        <v>79660</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3284,21 +3288,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3308,10 +3312,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436033</v>
+        <v>436095</v>
       </c>
       <c r="R28" t="n">
-        <v>6786758</v>
+        <v>6786747</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3370,10 +3374,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129082504</v>
+        <v>129082589</v>
       </c>
       <c r="B29" t="n">
-        <v>79658</v>
+        <v>78798</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3381,21 +3385,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3405,10 +3409,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436031</v>
+        <v>436033</v>
       </c>
       <c r="R29" t="n">
-        <v>6786744</v>
+        <v>6786758</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3470,7 +3474,7 @@
         <v>129082636</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3564,10 +3568,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129082653</v>
+        <v>129082504</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3575,37 +3579,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436092</v>
+        <v>436031</v>
       </c>
       <c r="R31" t="n">
-        <v>6786889</v>
+        <v>6786744</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3646,7 +3647,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>129082524</v>
       </c>
       <c r="B32" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3877,10 +3877,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129082662</v>
+        <v>129082538</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3888,34 +3888,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435932</v>
+        <v>436141</v>
       </c>
       <c r="R34" t="n">
-        <v>6786581</v>
+        <v>6786882</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3974,10 +3982,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129082612</v>
+        <v>129082533</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3985,34 +3993,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435883</v>
+        <v>436445</v>
       </c>
       <c r="R35" t="n">
-        <v>6786641</v>
+        <v>6786610</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4071,45 +4087,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129082646</v>
+        <v>129082588</v>
       </c>
       <c r="B36" t="n">
-        <v>79039</v>
+        <v>58097</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436400</v>
+        <v>435979</v>
       </c>
       <c r="R36" t="n">
-        <v>6786855</v>
+        <v>6786531</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4168,10 +4192,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129082538</v>
+        <v>129082612</v>
       </c>
       <c r="B37" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4179,42 +4203,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436141</v>
+        <v>435883</v>
       </c>
       <c r="R37" t="n">
-        <v>6786882</v>
+        <v>6786641</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4273,10 +4289,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129082533</v>
+        <v>129082662</v>
       </c>
       <c r="B38" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4284,42 +4300,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436445</v>
+        <v>435932</v>
       </c>
       <c r="R38" t="n">
-        <v>6786610</v>
+        <v>6786581</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4378,53 +4386,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129082588</v>
+        <v>129082646</v>
       </c>
       <c r="B39" t="n">
-        <v>58095</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435979</v>
+        <v>436400</v>
       </c>
       <c r="R39" t="n">
-        <v>6786531</v>
+        <v>6786855</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4486,7 +4486,7 @@
         <v>129082543</v>
       </c>
       <c r="B40" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>129082551</v>
       </c>
       <c r="B41" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>129082663</v>
       </c>
       <c r="B43" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>129082593</v>
       </c>
       <c r="B44" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>129082590</v>
       </c>
       <c r="B45" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>129082553</v>
       </c>
       <c r="B47" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5279,45 +5279,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129082624</v>
+        <v>129082585</v>
       </c>
       <c r="B48" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436138</v>
+        <v>435948</v>
       </c>
       <c r="R48" t="n">
-        <v>6786811</v>
+        <v>6786565</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5358,6 +5367,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5379,7 +5389,7 @@
         <v>129082648</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5477,10 +5487,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129082611</v>
+        <v>129082624</v>
       </c>
       <c r="B50" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5512,10 +5522,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435898</v>
+        <v>436138</v>
       </c>
       <c r="R50" t="n">
-        <v>6786619</v>
+        <v>6786811</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5574,10 +5584,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129082655</v>
+        <v>129082611</v>
       </c>
       <c r="B51" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5609,10 +5619,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436020</v>
+        <v>435898</v>
       </c>
       <c r="R51" t="n">
-        <v>6786856</v>
+        <v>6786619</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5671,10 +5681,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129082529</v>
+        <v>129082655</v>
       </c>
       <c r="B52" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5682,42 +5692,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436057</v>
+        <v>436020</v>
       </c>
       <c r="R52" t="n">
-        <v>6786761</v>
+        <v>6786856</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5776,41 +5778,40 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129082567</v>
+        <v>129082529</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5820,10 +5821,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436312</v>
+        <v>436057</v>
       </c>
       <c r="R53" t="n">
-        <v>6786810</v>
+        <v>6786761</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5864,7 +5865,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5883,7 +5883,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129082585</v>
+        <v>129082567</v>
       </c>
       <c r="B54" t="n">
         <v>8450</v>
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435948</v>
+        <v>436312</v>
       </c>
       <c r="R54" t="n">
-        <v>6786565</v>
+        <v>6786810</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5990,10 +5990,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129082647</v>
+        <v>129082656</v>
       </c>
       <c r="B55" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436372</v>
+        <v>435996</v>
       </c>
       <c r="R55" t="n">
-        <v>6786946</v>
+        <v>6786755</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6087,10 +6087,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129082656</v>
+        <v>129082647</v>
       </c>
       <c r="B56" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6122,10 +6122,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435996</v>
+        <v>436372</v>
       </c>
       <c r="R56" t="n">
-        <v>6786755</v>
+        <v>6786946</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6184,43 +6184,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129082577</v>
+        <v>129082555</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6228,10 +6222,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>436381</v>
+        <v>436072</v>
       </c>
       <c r="R57" t="n">
-        <v>6786936</v>
+        <v>6786886</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6291,7 +6285,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129082564</v>
+        <v>129082577</v>
       </c>
       <c r="B58" t="n">
         <v>8450</v>
@@ -6325,7 +6319,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6335,10 +6329,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>436166</v>
+        <v>436381</v>
       </c>
       <c r="R58" t="n">
-        <v>6786846</v>
+        <v>6786936</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6398,37 +6392,43 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129082555</v>
+        <v>129082564</v>
       </c>
       <c r="B59" t="n">
-        <v>78797</v>
+        <v>8450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>436072</v>
+        <v>436166</v>
       </c>
       <c r="R59" t="n">
-        <v>6786886</v>
+        <v>6786846</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6499,10 +6499,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129082548</v>
+        <v>129082644</v>
       </c>
       <c r="B60" t="n">
-        <v>78797</v>
+        <v>79041</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6510,21 +6510,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>436268</v>
+        <v>436432</v>
       </c>
       <c r="R60" t="n">
-        <v>6786874</v>
+        <v>6786765</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6596,10 +6596,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129082516</v>
+        <v>129082597</v>
       </c>
       <c r="B61" t="n">
-        <v>79629</v>
+        <v>78798</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6607,37 +6607,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436470</v>
+        <v>436469</v>
       </c>
       <c r="R61" t="n">
-        <v>6786714</v>
+        <v>6786748</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6678,7 +6675,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6697,10 +6693,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129082545</v>
+        <v>129082666</v>
       </c>
       <c r="B62" t="n">
-        <v>78797</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6708,37 +6704,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>436085</v>
+        <v>436618</v>
       </c>
       <c r="R62" t="n">
-        <v>6786778</v>
+        <v>6786620</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6779,7 +6772,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6798,10 +6790,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129082515</v>
+        <v>129082506</v>
       </c>
       <c r="B63" t="n">
-        <v>79629</v>
+        <v>79660</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6809,21 +6801,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6836,10 +6828,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>436075</v>
+        <v>436172</v>
       </c>
       <c r="R63" t="n">
-        <v>6786747</v>
+        <v>6786831</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6899,10 +6891,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129082597</v>
+        <v>129082548</v>
       </c>
       <c r="B64" t="n">
-        <v>78796</v>
+        <v>78799</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6910,21 +6902,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6934,10 +6926,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>436469</v>
+        <v>436268</v>
       </c>
       <c r="R64" t="n">
-        <v>6786748</v>
+        <v>6786874</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6996,10 +6988,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129082506</v>
+        <v>129082516</v>
       </c>
       <c r="B65" t="n">
-        <v>79658</v>
+        <v>79631</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7007,21 +6999,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7034,10 +7026,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>436172</v>
+        <v>436470</v>
       </c>
       <c r="R65" t="n">
-        <v>6786831</v>
+        <v>6786714</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7097,10 +7089,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129082644</v>
+        <v>129082545</v>
       </c>
       <c r="B66" t="n">
-        <v>79039</v>
+        <v>78799</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7108,34 +7100,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436432</v>
+        <v>436085</v>
       </c>
       <c r="R66" t="n">
-        <v>6786765</v>
+        <v>6786778</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7176,6 +7171,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7194,10 +7190,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129082666</v>
+        <v>129082515</v>
       </c>
       <c r="B67" t="n">
-        <v>79039</v>
+        <v>79631</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7205,34 +7201,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436618</v>
+        <v>436075</v>
       </c>
       <c r="R67" t="n">
-        <v>6786620</v>
+        <v>6786747</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7273,6 +7272,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7291,10 +7291,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129082528</v>
+        <v>129082507</v>
       </c>
       <c r="B68" t="n">
-        <v>57722</v>
+        <v>79660</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7302,42 +7302,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436042</v>
+        <v>436265</v>
       </c>
       <c r="R68" t="n">
-        <v>6786785</v>
+        <v>6786874</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7396,10 +7388,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129082507</v>
+        <v>129082610</v>
       </c>
       <c r="B69" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7407,21 +7399,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7431,10 +7423,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>436265</v>
+        <v>435906</v>
       </c>
       <c r="R69" t="n">
-        <v>6786874</v>
+        <v>6786603</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7493,10 +7485,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129082610</v>
+        <v>129082528</v>
       </c>
       <c r="B70" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7504,34 +7496,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435906</v>
+        <v>436042</v>
       </c>
       <c r="R70" t="n">
-        <v>6786603</v>
+        <v>6786785</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7700,7 +7700,7 @@
         <v>129082552</v>
       </c>
       <c r="B72" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>129082550</v>
       </c>
       <c r="B73" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7891,10 +7891,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129082503</v>
+        <v>129082639</v>
       </c>
       <c r="B74" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7902,21 +7902,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436052</v>
+        <v>436568</v>
       </c>
       <c r="R74" t="n">
-        <v>6786720</v>
+        <v>6786650</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7988,54 +7988,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129082579</v>
+        <v>129082634</v>
       </c>
       <c r="B75" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436306</v>
+        <v>436338</v>
       </c>
       <c r="R75" t="n">
-        <v>6786960</v>
+        <v>6786664</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8076,7 +8067,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8095,10 +8085,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129082639</v>
+        <v>129082503</v>
       </c>
       <c r="B76" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8106,21 +8096,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8130,10 +8120,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436568</v>
+        <v>436052</v>
       </c>
       <c r="R76" t="n">
-        <v>6786650</v>
+        <v>6786720</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8192,45 +8182,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129082634</v>
+        <v>129082579</v>
       </c>
       <c r="B77" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436338</v>
+        <v>436306</v>
       </c>
       <c r="R77" t="n">
-        <v>6786664</v>
+        <v>6786960</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8271,6 +8270,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8292,7 +8292,7 @@
         <v>129082534</v>
       </c>
       <c r="B78" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>129082539</v>
       </c>
       <c r="B79" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>129082540</v>
       </c>
       <c r="B80" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8604,45 +8604,53 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129082667</v>
+        <v>129082521</v>
       </c>
       <c r="B81" t="n">
-        <v>79039</v>
+        <v>56917</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>435965</v>
+        <v>436093</v>
       </c>
       <c r="R81" t="n">
-        <v>6786476</v>
+        <v>6786769</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8701,10 +8709,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129082620</v>
+        <v>129082617</v>
       </c>
       <c r="B82" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8736,10 +8744,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>436035</v>
+        <v>436010</v>
       </c>
       <c r="R82" t="n">
-        <v>6786730</v>
+        <v>6786752</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8798,10 +8806,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129082513</v>
+        <v>129082635</v>
       </c>
       <c r="B83" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8809,21 +8817,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8833,10 +8841,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>436205</v>
+        <v>436350</v>
       </c>
       <c r="R83" t="n">
-        <v>6786914</v>
+        <v>6786631</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8895,10 +8903,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129082635</v>
+        <v>129082667</v>
       </c>
       <c r="B84" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8930,10 +8938,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>436350</v>
+        <v>435965</v>
       </c>
       <c r="R84" t="n">
-        <v>6786631</v>
+        <v>6786476</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8992,10 +9000,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129082649</v>
+        <v>129082620</v>
       </c>
       <c r="B85" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9027,10 +9035,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>436277</v>
+        <v>436035</v>
       </c>
       <c r="R85" t="n">
-        <v>6786944</v>
+        <v>6786730</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9089,10 +9097,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129082617</v>
+        <v>129082513</v>
       </c>
       <c r="B86" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9100,21 +9108,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9124,10 +9132,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>436010</v>
+        <v>436205</v>
       </c>
       <c r="R86" t="n">
-        <v>6786752</v>
+        <v>6786914</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9186,53 +9194,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129082521</v>
+        <v>129082649</v>
       </c>
       <c r="B87" t="n">
-        <v>56915</v>
+        <v>79041</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>436093</v>
+        <v>436277</v>
       </c>
       <c r="R87" t="n">
-        <v>6786769</v>
+        <v>6786944</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9291,42 +9291,37 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129082536</v>
+        <v>129082671</v>
       </c>
       <c r="B88" t="n">
-        <v>57722</v>
+        <v>92835</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9334,10 +9329,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>436544</v>
+        <v>436349</v>
       </c>
       <c r="R88" t="n">
-        <v>6786666</v>
+        <v>6786689</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9378,6 +9373,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9396,48 +9392,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129082671</v>
+        <v>129082616</v>
       </c>
       <c r="B89" t="n">
-        <v>92833</v>
+        <v>79041</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>436349</v>
+        <v>436012</v>
       </c>
       <c r="R89" t="n">
-        <v>6786689</v>
+        <v>6786734</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9478,7 +9471,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9497,10 +9489,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129082525</v>
+        <v>129082625</v>
       </c>
       <c r="B90" t="n">
-        <v>57885</v>
+        <v>79041</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9508,42 +9500,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>435948</v>
+        <v>436202</v>
       </c>
       <c r="R90" t="n">
-        <v>6786586</v>
+        <v>6786849</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9602,54 +9586,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129082582</v>
+        <v>129082619</v>
       </c>
       <c r="B91" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>436138</v>
+        <v>436034</v>
       </c>
       <c r="R91" t="n">
-        <v>6786894</v>
+        <v>6786743</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9690,7 +9665,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9709,10 +9683,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129082514</v>
+        <v>129082606</v>
       </c>
       <c r="B92" t="n">
-        <v>79629</v>
+        <v>79041</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9720,21 +9694,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9744,10 +9718,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>436044</v>
+        <v>435970</v>
       </c>
       <c r="R92" t="n">
-        <v>6786741</v>
+        <v>6786458</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9806,10 +9780,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129082556</v>
+        <v>129082594</v>
       </c>
       <c r="B93" t="n">
-        <v>78797</v>
+        <v>78798</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9817,21 +9791,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9841,10 +9815,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436010</v>
+        <v>436339</v>
       </c>
       <c r="R93" t="n">
-        <v>6786852</v>
+        <v>6786747</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9903,10 +9877,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129082594</v>
+        <v>129082665</v>
       </c>
       <c r="B94" t="n">
-        <v>78796</v>
+        <v>79041</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9914,21 +9888,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9938,10 +9912,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436339</v>
+        <v>436330</v>
       </c>
       <c r="R94" t="n">
-        <v>6786747</v>
+        <v>6786736</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10003,7 +9977,7 @@
         <v>129082595</v>
       </c>
       <c r="B95" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10100,7 +10074,7 @@
         <v>129082654</v>
       </c>
       <c r="B96" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10194,10 +10168,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129082625</v>
+        <v>129082525</v>
       </c>
       <c r="B97" t="n">
-        <v>79039</v>
+        <v>57887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10205,34 +10179,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436202</v>
+        <v>435948</v>
       </c>
       <c r="R97" t="n">
-        <v>6786849</v>
+        <v>6786586</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10291,45 +10273,54 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129082665</v>
+        <v>129082582</v>
       </c>
       <c r="B98" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436330</v>
+        <v>436138</v>
       </c>
       <c r="R98" t="n">
-        <v>6786736</v>
+        <v>6786894</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10370,6 +10361,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10388,10 +10380,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129082606</v>
+        <v>129082536</v>
       </c>
       <c r="B99" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10399,34 +10391,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>435970</v>
+        <v>436544</v>
       </c>
       <c r="R99" t="n">
-        <v>6786458</v>
+        <v>6786666</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10485,10 +10485,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129082619</v>
+        <v>129082514</v>
       </c>
       <c r="B100" t="n">
-        <v>79039</v>
+        <v>79631</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10496,21 +10496,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10520,10 +10520,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436034</v>
+        <v>436044</v>
       </c>
       <c r="R100" t="n">
-        <v>6786743</v>
+        <v>6786741</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10582,10 +10582,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129082616</v>
+        <v>129082556</v>
       </c>
       <c r="B101" t="n">
-        <v>79039</v>
+        <v>78799</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10593,21 +10593,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10617,10 +10617,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>436012</v>
+        <v>436010</v>
       </c>
       <c r="R101" t="n">
-        <v>6786734</v>
+        <v>6786852</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10679,10 +10679,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129082642</v>
+        <v>129082532</v>
       </c>
       <c r="B102" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10690,34 +10690,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>436506</v>
+        <v>436295</v>
       </c>
       <c r="R102" t="n">
-        <v>6786683</v>
+        <v>6786848</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10776,10 +10784,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129082591</v>
+        <v>129082531</v>
       </c>
       <c r="B103" t="n">
-        <v>78796</v>
+        <v>57724</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10787,34 +10795,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>436044</v>
+        <v>436246</v>
       </c>
       <c r="R103" t="n">
-        <v>6786741</v>
+        <v>6786863</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10873,45 +10889,54 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129082621</v>
+        <v>129082578</v>
       </c>
       <c r="B104" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>436086</v>
+        <v>436368</v>
       </c>
       <c r="R104" t="n">
-        <v>6786788</v>
+        <v>6786971</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10952,6 +10977,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -10973,7 +10999,7 @@
         <v>129082650</v>
       </c>
       <c r="B105" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11067,10 +11093,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129082532</v>
+        <v>129082621</v>
       </c>
       <c r="B106" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11078,42 +11104,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>436295</v>
+        <v>436086</v>
       </c>
       <c r="R106" t="n">
-        <v>6786848</v>
+        <v>6786788</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11172,10 +11190,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129082531</v>
+        <v>129082642</v>
       </c>
       <c r="B107" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11183,42 +11201,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436246</v>
+        <v>436506</v>
       </c>
       <c r="R107" t="n">
-        <v>6786863</v>
+        <v>6786683</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11277,54 +11287,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129082578</v>
+        <v>129082591</v>
       </c>
       <c r="B108" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>436368</v>
+        <v>436044</v>
       </c>
       <c r="R108" t="n">
-        <v>6786971</v>
+        <v>6786741</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11365,7 +11366,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11387,7 +11387,7 @@
         <v>129082509</v>
       </c>
       <c r="B109" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11481,10 +11481,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129082592</v>
+        <v>129082628</v>
       </c>
       <c r="B110" t="n">
-        <v>78796</v>
+        <v>79041</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11492,21 +11492,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11516,10 +11516,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>436095</v>
+        <v>436327</v>
       </c>
       <c r="R110" t="n">
-        <v>6786744</v>
+        <v>6786767</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11578,10 +11578,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129082628</v>
+        <v>129082609</v>
       </c>
       <c r="B111" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11613,10 +11613,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>436327</v>
+        <v>435914</v>
       </c>
       <c r="R111" t="n">
-        <v>6786767</v>
+        <v>6786598</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11675,10 +11675,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129082632</v>
+        <v>129082627</v>
       </c>
       <c r="B112" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11710,10 +11710,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>436334</v>
+        <v>436246</v>
       </c>
       <c r="R112" t="n">
-        <v>6786685</v>
+        <v>6786881</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11772,10 +11772,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129082609</v>
+        <v>129082668</v>
       </c>
       <c r="B113" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11807,10 +11807,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>435914</v>
+        <v>435933</v>
       </c>
       <c r="R113" t="n">
-        <v>6786598</v>
+        <v>6786585</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11869,10 +11869,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129082627</v>
+        <v>129082632</v>
       </c>
       <c r="B114" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11904,10 +11904,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>436246</v>
+        <v>436334</v>
       </c>
       <c r="R114" t="n">
-        <v>6786881</v>
+        <v>6786685</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11966,10 +11966,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129082668</v>
+        <v>129082592</v>
       </c>
       <c r="B115" t="n">
-        <v>79039</v>
+        <v>78798</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11977,21 +11977,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12001,10 +12001,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>435933</v>
+        <v>436095</v>
       </c>
       <c r="R115" t="n">
-        <v>6786585</v>
+        <v>6786744</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12063,45 +12063,54 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129082645</v>
+        <v>129082560</v>
       </c>
       <c r="B116" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>436405</v>
+        <v>435897</v>
       </c>
       <c r="R116" t="n">
-        <v>6786825</v>
+        <v>6786676</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12142,6 +12151,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12160,45 +12170,54 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129082633</v>
+        <v>129082576</v>
       </c>
       <c r="B117" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>436347</v>
+        <v>436417</v>
       </c>
       <c r="R117" t="n">
-        <v>6786689</v>
+        <v>6786827</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12239,6 +12258,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12364,7 +12384,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129082576</v>
+        <v>129082580</v>
       </c>
       <c r="B119" t="n">
         <v>8450</v>
@@ -12408,10 +12428,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>436417</v>
+        <v>436280</v>
       </c>
       <c r="R119" t="n">
-        <v>6786827</v>
+        <v>6786936</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12471,54 +12491,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129082580</v>
+        <v>129082554</v>
       </c>
       <c r="B120" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>436280</v>
+        <v>436096</v>
       </c>
       <c r="R120" t="n">
-        <v>6786936</v>
+        <v>6786876</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12559,7 +12570,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12578,54 +12588,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129082560</v>
+        <v>129082645</v>
       </c>
       <c r="B121" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>435897</v>
+        <v>436405</v>
       </c>
       <c r="R121" t="n">
-        <v>6786676</v>
+        <v>6786825</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12666,7 +12667,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12685,10 +12685,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129082554</v>
+        <v>129082633</v>
       </c>
       <c r="B122" t="n">
-        <v>78797</v>
+        <v>79041</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12696,21 +12696,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12720,10 +12720,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>436096</v>
+        <v>436347</v>
       </c>
       <c r="R122" t="n">
-        <v>6786876</v>
+        <v>6786689</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12782,10 +12782,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129082598</v>
+        <v>129082613</v>
       </c>
       <c r="B123" t="n">
-        <v>78796</v>
+        <v>79041</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12793,21 +12793,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12817,10 +12817,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>436107</v>
+        <v>435886</v>
       </c>
       <c r="R123" t="n">
-        <v>6786875</v>
+        <v>6786666</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12879,10 +12879,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129082618</v>
+        <v>129082598</v>
       </c>
       <c r="B124" t="n">
-        <v>79039</v>
+        <v>78798</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12890,21 +12890,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12914,10 +12914,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>436027</v>
+        <v>436107</v>
       </c>
       <c r="R124" t="n">
-        <v>6786735</v>
+        <v>6786875</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12976,54 +12976,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129082565</v>
+        <v>129082618</v>
       </c>
       <c r="B125" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>436230</v>
+        <v>436027</v>
       </c>
       <c r="R125" t="n">
-        <v>6786855</v>
+        <v>6786735</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13064,7 +13055,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13190,45 +13180,54 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129082613</v>
+        <v>129082565</v>
       </c>
       <c r="B127" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>435886</v>
+        <v>436230</v>
       </c>
       <c r="R127" t="n">
-        <v>6786666</v>
+        <v>6786855</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13269,6 +13268,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13287,10 +13287,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129082547</v>
+        <v>129082535</v>
       </c>
       <c r="B128" t="n">
-        <v>78797</v>
+        <v>57724</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13298,34 +13298,42 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>436172</v>
+        <v>436575</v>
       </c>
       <c r="R128" t="n">
-        <v>6786825</v>
+        <v>6786632</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13384,45 +13392,54 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129082596</v>
+        <v>129082583</v>
       </c>
       <c r="B129" t="n">
-        <v>78796</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>436432</v>
+        <v>436011</v>
       </c>
       <c r="R129" t="n">
-        <v>6786558</v>
+        <v>6786844</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13463,6 +13480,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13481,10 +13499,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129082626</v>
+        <v>129082547</v>
       </c>
       <c r="B130" t="n">
-        <v>79039</v>
+        <v>78799</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13492,21 +13510,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13516,10 +13534,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436240</v>
+        <v>436172</v>
       </c>
       <c r="R130" t="n">
-        <v>6786833</v>
+        <v>6786825</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13581,7 +13599,7 @@
         <v>129082664</v>
       </c>
       <c r="B131" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13675,10 +13693,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129082535</v>
+        <v>129082626</v>
       </c>
       <c r="B132" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13686,42 +13704,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>436575</v>
+        <v>436240</v>
       </c>
       <c r="R132" t="n">
-        <v>6786632</v>
+        <v>6786833</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13780,54 +13790,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129082583</v>
+        <v>129082596</v>
       </c>
       <c r="B133" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>436011</v>
+        <v>436432</v>
       </c>
       <c r="R133" t="n">
-        <v>6786844</v>
+        <v>6786558</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13868,7 +13869,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49064-2025 artfynd.xlsx
+++ b/artfynd/A 49064-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129082641</v>
+        <v>129082546</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436537</v>
+        <v>436092</v>
       </c>
       <c r="R2" t="n">
-        <v>6786684</v>
+        <v>6786744</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129082637</v>
+        <v>129082544</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436410</v>
+        <v>436044</v>
       </c>
       <c r="R3" t="n">
-        <v>6786560</v>
+        <v>6786741</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129082546</v>
+        <v>129082637</v>
       </c>
       <c r="B5" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436092</v>
+        <v>436410</v>
       </c>
       <c r="R5" t="n">
-        <v>6786744</v>
+        <v>6786560</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129082544</v>
+        <v>129082641</v>
       </c>
       <c r="B6" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436044</v>
+        <v>436537</v>
       </c>
       <c r="R6" t="n">
-        <v>6786741</v>
+        <v>6786684</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1267,54 +1267,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129082575</v>
+        <v>129082651</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436432</v>
+        <v>436254</v>
       </c>
       <c r="R8" t="n">
-        <v>6786759</v>
+        <v>6786925</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,7 +1346,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1374,54 +1364,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129082574</v>
+        <v>129082638</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436455</v>
+        <v>436456</v>
       </c>
       <c r="R9" t="n">
-        <v>6786732</v>
+        <v>6786598</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1462,7 +1443,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1481,45 +1461,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129082638</v>
+        <v>129082575</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436456</v>
+        <v>436432</v>
       </c>
       <c r="R10" t="n">
-        <v>6786598</v>
+        <v>6786759</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,6 +1549,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1578,45 +1568,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129082651</v>
+        <v>129082574</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436254</v>
+        <v>436455</v>
       </c>
       <c r="R11" t="n">
-        <v>6786925</v>
+        <v>6786732</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,6 +1656,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129082510</v>
+        <v>129082508</v>
       </c>
       <c r="B12" t="n">
         <v>79660</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436506</v>
+        <v>436338</v>
       </c>
       <c r="R12" t="n">
-        <v>6786715</v>
+        <v>6786741</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129082508</v>
+        <v>129082510</v>
       </c>
       <c r="B13" t="n">
         <v>79660</v>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436338</v>
+        <v>436506</v>
       </c>
       <c r="R13" t="n">
-        <v>6786741</v>
+        <v>6786715</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129082622</v>
+        <v>129082652</v>
       </c>
       <c r="B15" t="n">
         <v>79041</v>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436101</v>
+        <v>436190</v>
       </c>
       <c r="R15" t="n">
-        <v>6786774</v>
+        <v>6786911</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2073,45 +2073,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129082629</v>
+        <v>129082566</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436335</v>
+        <v>436258</v>
       </c>
       <c r="R16" t="n">
-        <v>6786743</v>
+        <v>6786851</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2152,6 +2161,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2170,45 +2180,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129082630</v>
+        <v>129082568</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436320</v>
+        <v>436409</v>
       </c>
       <c r="R17" t="n">
-        <v>6786718</v>
+        <v>6786563</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2249,6 +2268,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2267,7 +2287,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129082652</v>
+        <v>129082622</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2302,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436190</v>
+        <v>436101</v>
       </c>
       <c r="R18" t="n">
-        <v>6786911</v>
+        <v>6786774</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2364,54 +2384,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129082568</v>
+        <v>129082630</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436409</v>
+        <v>436320</v>
       </c>
       <c r="R19" t="n">
-        <v>6786563</v>
+        <v>6786718</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2452,7 +2463,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2471,54 +2481,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129082566</v>
+        <v>129082629</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436258</v>
+        <v>436335</v>
       </c>
       <c r="R20" t="n">
-        <v>6786851</v>
+        <v>6786743</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2559,7 +2560,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129082640</v>
+        <v>129082537</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2694,34 +2694,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436530</v>
+        <v>436399</v>
       </c>
       <c r="R22" t="n">
-        <v>6786657</v>
+        <v>6786867</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,10 +2885,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129082537</v>
+        <v>129082640</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2888,42 +2896,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436399</v>
+        <v>436530</v>
       </c>
       <c r="R24" t="n">
-        <v>6786867</v>
+        <v>6786657</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3079,7 +3079,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129082512</v>
+        <v>129082504</v>
       </c>
       <c r="B26" t="n">
         <v>79660</v>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436428</v>
+        <v>436031</v>
       </c>
       <c r="R26" t="n">
-        <v>6786809</v>
+        <v>6786744</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3176,7 +3176,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129082653</v>
+        <v>129082636</v>
       </c>
       <c r="B27" t="n">
         <v>79041</v>
@@ -3205,19 +3205,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436092</v>
+        <v>436431</v>
       </c>
       <c r="R27" t="n">
-        <v>6786889</v>
+        <v>6786583</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3258,7 +3255,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3374,10 +3370,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129082589</v>
+        <v>129082653</v>
       </c>
       <c r="B29" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3385,34 +3381,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436033</v>
+        <v>436092</v>
       </c>
       <c r="R29" t="n">
-        <v>6786758</v>
+        <v>6786889</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3453,6 +3452,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3471,10 +3471,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129082636</v>
+        <v>129082512</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3482,21 +3482,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436431</v>
+        <v>436428</v>
       </c>
       <c r="R30" t="n">
-        <v>6786583</v>
+        <v>6786809</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3568,10 +3568,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129082504</v>
+        <v>129082589</v>
       </c>
       <c r="B31" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3579,21 +3579,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3603,10 +3603,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436031</v>
+        <v>436033</v>
       </c>
       <c r="R31" t="n">
-        <v>6786744</v>
+        <v>6786758</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3877,27 +3877,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129082538</v>
+        <v>129082588</v>
       </c>
       <c r="B34" t="n">
-        <v>57724</v>
+        <v>58097</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3910,7 +3910,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436141</v>
+        <v>435979</v>
       </c>
       <c r="R34" t="n">
-        <v>6786882</v>
+        <v>6786531</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3982,40 +3982,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129082533</v>
+        <v>129082573</v>
       </c>
       <c r="B35" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4025,10 +4026,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436445</v>
+        <v>436525</v>
       </c>
       <c r="R35" t="n">
-        <v>6786610</v>
+        <v>6786729</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4069,6 +4070,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4087,53 +4089,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129082588</v>
+        <v>129082662</v>
       </c>
       <c r="B36" t="n">
-        <v>58097</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435979</v>
+        <v>435932</v>
       </c>
       <c r="R36" t="n">
-        <v>6786531</v>
+        <v>6786581</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4289,7 +4283,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129082662</v>
+        <v>129082646</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4324,10 +4318,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435932</v>
+        <v>436400</v>
       </c>
       <c r="R38" t="n">
-        <v>6786581</v>
+        <v>6786855</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4386,10 +4380,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129082646</v>
+        <v>129082538</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4397,34 +4391,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436400</v>
+        <v>436141</v>
       </c>
       <c r="R39" t="n">
-        <v>6786855</v>
+        <v>6786882</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4483,10 +4485,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129082543</v>
+        <v>129082533</v>
       </c>
       <c r="B40" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4494,34 +4496,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436027</v>
+        <v>436445</v>
       </c>
       <c r="R40" t="n">
-        <v>6786747</v>
+        <v>6786610</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4580,7 +4590,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129082551</v>
+        <v>129082543</v>
       </c>
       <c r="B41" t="n">
         <v>78799</v>
@@ -4615,10 +4625,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436436</v>
+        <v>436027</v>
       </c>
       <c r="R41" t="n">
-        <v>6786563</v>
+        <v>6786747</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4677,54 +4687,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129082573</v>
+        <v>129082551</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436525</v>
+        <v>436436</v>
       </c>
       <c r="R42" t="n">
-        <v>6786729</v>
+        <v>6786563</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4765,7 +4766,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4784,10 +4784,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129082663</v>
+        <v>129082590</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4795,21 +4795,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435984</v>
+        <v>436051</v>
       </c>
       <c r="R43" t="n">
-        <v>6786452</v>
+        <v>6786730</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4978,10 +4978,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129082590</v>
+        <v>129082663</v>
       </c>
       <c r="B45" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4989,21 +4989,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436051</v>
+        <v>435984</v>
       </c>
       <c r="R45" t="n">
-        <v>6786730</v>
+        <v>6786452</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5279,43 +5279,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129082585</v>
+        <v>129082648</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5323,10 +5317,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435948</v>
+        <v>436353</v>
       </c>
       <c r="R48" t="n">
-        <v>6786565</v>
+        <v>6786940</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5386,7 +5380,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129082648</v>
+        <v>129082611</v>
       </c>
       <c r="B49" t="n">
         <v>79041</v>
@@ -5415,19 +5409,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436353</v>
+        <v>435898</v>
       </c>
       <c r="R49" t="n">
-        <v>6786940</v>
+        <v>6786619</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5468,7 +5459,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5584,7 +5574,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129082611</v>
+        <v>129082655</v>
       </c>
       <c r="B51" t="n">
         <v>79041</v>
@@ -5619,10 +5609,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435898</v>
+        <v>436020</v>
       </c>
       <c r="R51" t="n">
-        <v>6786619</v>
+        <v>6786856</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5681,10 +5671,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129082655</v>
+        <v>129082529</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5692,34 +5682,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436020</v>
+        <v>436057</v>
       </c>
       <c r="R52" t="n">
-        <v>6786856</v>
+        <v>6786761</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5778,40 +5776,41 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129082529</v>
+        <v>129082567</v>
       </c>
       <c r="B53" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5821,10 +5820,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436057</v>
+        <v>436312</v>
       </c>
       <c r="R53" t="n">
-        <v>6786761</v>
+        <v>6786810</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5865,6 +5864,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5883,7 +5883,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129082567</v>
+        <v>129082585</v>
       </c>
       <c r="B54" t="n">
         <v>8450</v>
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>436312</v>
+        <v>435948</v>
       </c>
       <c r="R54" t="n">
-        <v>6786810</v>
+        <v>6786565</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6499,10 +6499,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129082644</v>
+        <v>129082506</v>
       </c>
       <c r="B60" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6510,34 +6510,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>436432</v>
+        <v>436172</v>
       </c>
       <c r="R60" t="n">
-        <v>6786765</v>
+        <v>6786831</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6578,6 +6581,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6596,10 +6600,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129082597</v>
+        <v>129082644</v>
       </c>
       <c r="B61" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6607,21 +6611,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6631,10 +6635,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436469</v>
+        <v>436432</v>
       </c>
       <c r="R61" t="n">
-        <v>6786748</v>
+        <v>6786765</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6693,10 +6697,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129082666</v>
+        <v>129082597</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6704,21 +6708,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6728,10 +6732,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>436618</v>
+        <v>436469</v>
       </c>
       <c r="R62" t="n">
-        <v>6786620</v>
+        <v>6786748</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6790,10 +6794,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129082506</v>
+        <v>129082666</v>
       </c>
       <c r="B63" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6801,37 +6805,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>436172</v>
+        <v>436618</v>
       </c>
       <c r="R63" t="n">
-        <v>6786831</v>
+        <v>6786620</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6872,7 +6873,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7590,54 +7590,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129082572</v>
+        <v>129082552</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436553</v>
+        <v>436206</v>
       </c>
       <c r="R71" t="n">
-        <v>6786640</v>
+        <v>6786892</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7678,7 +7669,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7697,7 +7687,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129082552</v>
+        <v>129082550</v>
       </c>
       <c r="B72" t="n">
         <v>78799</v>
@@ -7732,10 +7722,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436206</v>
+        <v>436361</v>
       </c>
       <c r="R72" t="n">
-        <v>6786892</v>
+        <v>6786687</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7794,45 +7784,54 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129082550</v>
+        <v>129082572</v>
       </c>
       <c r="B73" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436361</v>
+        <v>436553</v>
       </c>
       <c r="R73" t="n">
-        <v>6786687</v>
+        <v>6786640</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7873,6 +7872,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7891,10 +7891,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129082639</v>
+        <v>129082534</v>
       </c>
       <c r="B74" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7902,34 +7902,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436568</v>
+        <v>436565</v>
       </c>
       <c r="R74" t="n">
-        <v>6786650</v>
+        <v>6786624</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7988,10 +7996,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129082634</v>
+        <v>129082539</v>
       </c>
       <c r="B75" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7999,34 +8007,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436338</v>
+        <v>436069</v>
       </c>
       <c r="R75" t="n">
-        <v>6786664</v>
+        <v>6786886</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8085,10 +8101,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129082503</v>
+        <v>129082540</v>
       </c>
       <c r="B76" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8096,34 +8112,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436052</v>
+        <v>436188</v>
       </c>
       <c r="R76" t="n">
-        <v>6786720</v>
+        <v>6786921</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8182,54 +8206,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129082579</v>
+        <v>129082639</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436306</v>
+        <v>436568</v>
       </c>
       <c r="R77" t="n">
-        <v>6786960</v>
+        <v>6786650</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8270,7 +8285,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8289,10 +8303,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129082534</v>
+        <v>129082503</v>
       </c>
       <c r="B78" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8300,42 +8314,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436565</v>
+        <v>436052</v>
       </c>
       <c r="R78" t="n">
-        <v>6786624</v>
+        <v>6786720</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8394,10 +8400,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129082539</v>
+        <v>129082634</v>
       </c>
       <c r="B79" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8405,42 +8411,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436069</v>
+        <v>436338</v>
       </c>
       <c r="R79" t="n">
-        <v>6786886</v>
+        <v>6786664</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8499,40 +8497,41 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129082540</v>
+        <v>129082579</v>
       </c>
       <c r="B80" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8542,10 +8541,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436188</v>
+        <v>436306</v>
       </c>
       <c r="R80" t="n">
-        <v>6786921</v>
+        <v>6786960</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8586,6 +8585,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8604,53 +8604,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129082521</v>
+        <v>129082620</v>
       </c>
       <c r="B81" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>436093</v>
+        <v>436035</v>
       </c>
       <c r="R81" t="n">
-        <v>6786769</v>
+        <v>6786730</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8709,10 +8701,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129082617</v>
+        <v>129082513</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8720,21 +8712,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8744,10 +8736,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>436010</v>
+        <v>436205</v>
       </c>
       <c r="R82" t="n">
-        <v>6786752</v>
+        <v>6786914</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8903,7 +8895,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129082667</v>
+        <v>129082649</v>
       </c>
       <c r="B84" t="n">
         <v>79041</v>
@@ -8938,10 +8930,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>435965</v>
+        <v>436277</v>
       </c>
       <c r="R84" t="n">
-        <v>6786476</v>
+        <v>6786944</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9000,7 +8992,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129082620</v>
+        <v>129082617</v>
       </c>
       <c r="B85" t="n">
         <v>79041</v>
@@ -9035,10 +9027,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>436035</v>
+        <v>436010</v>
       </c>
       <c r="R85" t="n">
-        <v>6786730</v>
+        <v>6786752</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9097,10 +9089,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129082513</v>
+        <v>129082667</v>
       </c>
       <c r="B86" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9108,21 +9100,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9132,10 +9124,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>436205</v>
+        <v>435965</v>
       </c>
       <c r="R86" t="n">
-        <v>6786914</v>
+        <v>6786476</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9194,45 +9186,53 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129082649</v>
+        <v>129082521</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>436277</v>
+        <v>436093</v>
       </c>
       <c r="R87" t="n">
-        <v>6786944</v>
+        <v>6786769</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9291,37 +9291,42 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129082671</v>
+        <v>129082525</v>
       </c>
       <c r="B88" t="n">
-        <v>92835</v>
+        <v>57887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9329,10 +9334,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>436349</v>
+        <v>435948</v>
       </c>
       <c r="R88" t="n">
-        <v>6786689</v>
+        <v>6786586</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9373,7 +9378,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9392,45 +9396,54 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129082616</v>
+        <v>129082582</v>
       </c>
       <c r="B89" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>436012</v>
+        <v>436138</v>
       </c>
       <c r="R89" t="n">
-        <v>6786734</v>
+        <v>6786894</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9471,6 +9484,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9489,10 +9503,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129082625</v>
+        <v>129082514</v>
       </c>
       <c r="B90" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9500,21 +9514,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9524,10 +9538,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436202</v>
+        <v>436044</v>
       </c>
       <c r="R90" t="n">
-        <v>6786849</v>
+        <v>6786741</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9586,10 +9600,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129082619</v>
+        <v>129082556</v>
       </c>
       <c r="B91" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9597,21 +9611,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9621,10 +9635,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>436034</v>
+        <v>436010</v>
       </c>
       <c r="R91" t="n">
-        <v>6786743</v>
+        <v>6786852</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9683,45 +9697,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129082606</v>
+        <v>129082671</v>
       </c>
       <c r="B92" t="n">
-        <v>79041</v>
+        <v>92835</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>435970</v>
+        <v>436349</v>
       </c>
       <c r="R92" t="n">
-        <v>6786458</v>
+        <v>6786689</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9762,6 +9779,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9780,10 +9798,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129082594</v>
+        <v>129082654</v>
       </c>
       <c r="B93" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9791,21 +9809,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9815,10 +9833,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436339</v>
+        <v>436054</v>
       </c>
       <c r="R93" t="n">
-        <v>6786747</v>
+        <v>6786881</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9877,7 +9895,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129082665</v>
+        <v>129082625</v>
       </c>
       <c r="B94" t="n">
         <v>79041</v>
@@ -9912,10 +9930,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436330</v>
+        <v>436202</v>
       </c>
       <c r="R94" t="n">
-        <v>6786736</v>
+        <v>6786849</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9974,10 +9992,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129082595</v>
+        <v>129082665</v>
       </c>
       <c r="B95" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9985,21 +10003,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10009,10 +10027,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436361</v>
+        <v>436330</v>
       </c>
       <c r="R95" t="n">
-        <v>6786688</v>
+        <v>6786736</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10071,7 +10089,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129082654</v>
+        <v>129082606</v>
       </c>
       <c r="B96" t="n">
         <v>79041</v>
@@ -10106,10 +10124,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436054</v>
+        <v>435970</v>
       </c>
       <c r="R96" t="n">
-        <v>6786881</v>
+        <v>6786458</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10168,10 +10186,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129082525</v>
+        <v>129082619</v>
       </c>
       <c r="B97" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10179,42 +10197,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>435948</v>
+        <v>436034</v>
       </c>
       <c r="R97" t="n">
-        <v>6786586</v>
+        <v>6786743</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10273,54 +10283,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129082582</v>
+        <v>129082616</v>
       </c>
       <c r="B98" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436138</v>
+        <v>436012</v>
       </c>
       <c r="R98" t="n">
-        <v>6786894</v>
+        <v>6786734</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10361,7 +10362,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10380,10 +10380,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129082536</v>
+        <v>129082595</v>
       </c>
       <c r="B99" t="n">
-        <v>57724</v>
+        <v>78798</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10391,42 +10391,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436544</v>
+        <v>436361</v>
       </c>
       <c r="R99" t="n">
-        <v>6786666</v>
+        <v>6786688</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10485,10 +10477,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129082514</v>
+        <v>129082594</v>
       </c>
       <c r="B100" t="n">
-        <v>79631</v>
+        <v>78798</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10496,21 +10488,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10520,10 +10512,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436044</v>
+        <v>436339</v>
       </c>
       <c r="R100" t="n">
-        <v>6786741</v>
+        <v>6786747</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10582,10 +10574,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129082556</v>
+        <v>129082536</v>
       </c>
       <c r="B101" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10593,34 +10585,42 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>436010</v>
+        <v>436544</v>
       </c>
       <c r="R101" t="n">
-        <v>6786852</v>
+        <v>6786666</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10679,10 +10679,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129082532</v>
+        <v>129082621</v>
       </c>
       <c r="B102" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10690,42 +10690,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>436295</v>
+        <v>436086</v>
       </c>
       <c r="R102" t="n">
-        <v>6786848</v>
+        <v>6786788</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10784,10 +10776,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129082531</v>
+        <v>129082642</v>
       </c>
       <c r="B103" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10795,42 +10787,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>436246</v>
+        <v>436506</v>
       </c>
       <c r="R103" t="n">
-        <v>6786863</v>
+        <v>6786683</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10889,54 +10873,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129082578</v>
+        <v>129082591</v>
       </c>
       <c r="B104" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>436368</v>
+        <v>436044</v>
       </c>
       <c r="R104" t="n">
-        <v>6786971</v>
+        <v>6786741</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10977,7 +10952,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11093,10 +11067,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129082621</v>
+        <v>129082532</v>
       </c>
       <c r="B106" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11104,34 +11078,42 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>436086</v>
+        <v>436295</v>
       </c>
       <c r="R106" t="n">
-        <v>6786788</v>
+        <v>6786848</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11190,10 +11172,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129082642</v>
+        <v>129082531</v>
       </c>
       <c r="B107" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11201,34 +11183,42 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436506</v>
+        <v>436246</v>
       </c>
       <c r="R107" t="n">
-        <v>6786683</v>
+        <v>6786863</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11287,45 +11277,54 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129082591</v>
+        <v>129082578</v>
       </c>
       <c r="B108" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>436044</v>
+        <v>436368</v>
       </c>
       <c r="R108" t="n">
-        <v>6786741</v>
+        <v>6786971</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11366,6 +11365,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11578,7 +11578,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129082609</v>
+        <v>129082632</v>
       </c>
       <c r="B111" t="n">
         <v>79041</v>
@@ -11613,10 +11613,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>435914</v>
+        <v>436334</v>
       </c>
       <c r="R111" t="n">
-        <v>6786598</v>
+        <v>6786685</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11675,7 +11675,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129082627</v>
+        <v>129082609</v>
       </c>
       <c r="B112" t="n">
         <v>79041</v>
@@ -11710,10 +11710,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>436246</v>
+        <v>435914</v>
       </c>
       <c r="R112" t="n">
-        <v>6786881</v>
+        <v>6786598</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11772,10 +11772,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129082668</v>
+        <v>129082592</v>
       </c>
       <c r="B113" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11783,21 +11783,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11807,10 +11807,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>435933</v>
+        <v>436095</v>
       </c>
       <c r="R113" t="n">
-        <v>6786585</v>
+        <v>6786744</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11869,7 +11869,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129082632</v>
+        <v>129082627</v>
       </c>
       <c r="B114" t="n">
         <v>79041</v>
@@ -11904,10 +11904,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>436334</v>
+        <v>436246</v>
       </c>
       <c r="R114" t="n">
-        <v>6786685</v>
+        <v>6786881</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11966,10 +11966,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129082592</v>
+        <v>129082668</v>
       </c>
       <c r="B115" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11977,21 +11977,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12001,10 +12001,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>436095</v>
+        <v>435933</v>
       </c>
       <c r="R115" t="n">
-        <v>6786744</v>
+        <v>6786585</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12063,54 +12063,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129082560</v>
+        <v>129082645</v>
       </c>
       <c r="B116" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>435897</v>
+        <v>436405</v>
       </c>
       <c r="R116" t="n">
-        <v>6786676</v>
+        <v>6786825</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12151,7 +12142,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12170,54 +12160,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129082576</v>
+        <v>129082554</v>
       </c>
       <c r="B117" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>436417</v>
+        <v>436096</v>
       </c>
       <c r="R117" t="n">
-        <v>6786827</v>
+        <v>6786876</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12258,7 +12239,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12384,7 +12364,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129082580</v>
+        <v>129082576</v>
       </c>
       <c r="B119" t="n">
         <v>8450</v>
@@ -12428,10 +12408,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>436280</v>
+        <v>436417</v>
       </c>
       <c r="R119" t="n">
-        <v>6786936</v>
+        <v>6786827</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12491,45 +12471,54 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129082554</v>
+        <v>129082580</v>
       </c>
       <c r="B120" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>436096</v>
+        <v>436280</v>
       </c>
       <c r="R120" t="n">
-        <v>6786876</v>
+        <v>6786936</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12570,6 +12559,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12588,45 +12578,54 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129082645</v>
+        <v>129082560</v>
       </c>
       <c r="B121" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>436405</v>
+        <v>435897</v>
       </c>
       <c r="R121" t="n">
-        <v>6786825</v>
+        <v>6786676</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12667,6 +12666,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12879,10 +12879,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129082598</v>
+        <v>129082618</v>
       </c>
       <c r="B124" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12890,21 +12890,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12914,10 +12914,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>436107</v>
+        <v>436027</v>
       </c>
       <c r="R124" t="n">
-        <v>6786875</v>
+        <v>6786735</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12976,10 +12976,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129082618</v>
+        <v>129082598</v>
       </c>
       <c r="B125" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12987,21 +12987,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13011,10 +13011,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>436027</v>
+        <v>436107</v>
       </c>
       <c r="R125" t="n">
-        <v>6786735</v>
+        <v>6786875</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13073,7 +13073,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129082563</v>
+        <v>129082565</v>
       </c>
       <c r="B126" t="n">
         <v>8450</v>
@@ -13117,10 +13117,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436055</v>
+        <v>436230</v>
       </c>
       <c r="R126" t="n">
-        <v>6786776</v>
+        <v>6786855</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13180,7 +13180,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129082565</v>
+        <v>129082563</v>
       </c>
       <c r="B127" t="n">
         <v>8450</v>
@@ -13224,10 +13224,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>436230</v>
+        <v>436055</v>
       </c>
       <c r="R127" t="n">
-        <v>6786855</v>
+        <v>6786776</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13287,10 +13287,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129082535</v>
+        <v>129082596</v>
       </c>
       <c r="B128" t="n">
-        <v>57724</v>
+        <v>78798</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13298,42 +13298,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>436575</v>
+        <v>436432</v>
       </c>
       <c r="R128" t="n">
-        <v>6786632</v>
+        <v>6786558</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13392,54 +13384,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129082583</v>
+        <v>129082626</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>436011</v>
+        <v>436240</v>
       </c>
       <c r="R129" t="n">
-        <v>6786844</v>
+        <v>6786833</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13480,7 +13463,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13499,10 +13481,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129082547</v>
+        <v>129082664</v>
       </c>
       <c r="B130" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13510,21 +13492,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13534,10 +13516,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436172</v>
+        <v>436029</v>
       </c>
       <c r="R130" t="n">
-        <v>6786825</v>
+        <v>6786750</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13596,10 +13578,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129082664</v>
+        <v>129082535</v>
       </c>
       <c r="B131" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13607,34 +13589,42 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>436029</v>
+        <v>436575</v>
       </c>
       <c r="R131" t="n">
-        <v>6786750</v>
+        <v>6786632</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13693,45 +13683,54 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129082626</v>
+        <v>129082583</v>
       </c>
       <c r="B132" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>436240</v>
+        <v>436011</v>
       </c>
       <c r="R132" t="n">
-        <v>6786833</v>
+        <v>6786844</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13772,6 +13771,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13790,45 +13790,54 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129082596</v>
+        <v>129082558</v>
       </c>
       <c r="B133" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>436432</v>
+        <v>435909</v>
       </c>
       <c r="R133" t="n">
-        <v>6786558</v>
+        <v>6786616</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13869,6 +13878,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -13887,54 +13897,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129082558</v>
+        <v>129082547</v>
       </c>
       <c r="B134" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>435909</v>
+        <v>436172</v>
       </c>
       <c r="R134" t="n">
-        <v>6786616</v>
+        <v>6786825</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13975,7 +13976,6 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49064-2025 artfynd.xlsx
+++ b/artfynd/A 49064-2025 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129082546</v>
+        <v>129082570</v>
       </c>
       <c r="B2" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436092</v>
+        <v>436428</v>
       </c>
       <c r="R2" t="n">
-        <v>6786744</v>
+        <v>6786577</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129082544</v>
+        <v>129082546</v>
       </c>
       <c r="B3" t="n">
         <v>78799</v>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436044</v>
+        <v>436092</v>
       </c>
       <c r="R3" t="n">
-        <v>6786741</v>
+        <v>6786744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129082659</v>
+        <v>129082544</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435974</v>
+        <v>436044</v>
       </c>
       <c r="R4" t="n">
-        <v>6786534</v>
+        <v>6786741</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129082637</v>
+        <v>129082641</v>
       </c>
       <c r="B5" t="n">
         <v>79041</v>
@@ -1001,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436410</v>
+        <v>436537</v>
       </c>
       <c r="R5" t="n">
-        <v>6786560</v>
+        <v>6786684</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129082641</v>
+        <v>129082659</v>
       </c>
       <c r="B6" t="n">
         <v>79041</v>
@@ -1098,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436537</v>
+        <v>435974</v>
       </c>
       <c r="R6" t="n">
-        <v>6786684</v>
+        <v>6786534</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,54 +1170,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129082570</v>
+        <v>129082637</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436428</v>
+        <v>436410</v>
       </c>
       <c r="R7" t="n">
-        <v>6786577</v>
+        <v>6786560</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,7 +1249,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -2073,54 +2073,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129082566</v>
+        <v>129082622</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436258</v>
+        <v>436101</v>
       </c>
       <c r="R16" t="n">
-        <v>6786851</v>
+        <v>6786774</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2161,7 +2152,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2180,54 +2170,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129082568</v>
+        <v>129082629</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436409</v>
+        <v>436335</v>
       </c>
       <c r="R17" t="n">
-        <v>6786563</v>
+        <v>6786743</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2268,7 +2249,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2287,7 +2267,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129082622</v>
+        <v>129082630</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2322,10 +2302,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436101</v>
+        <v>436320</v>
       </c>
       <c r="R18" t="n">
-        <v>6786774</v>
+        <v>6786718</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2384,45 +2364,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129082630</v>
+        <v>129082522</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436320</v>
+        <v>436195</v>
       </c>
       <c r="R19" t="n">
-        <v>6786718</v>
+        <v>6786902</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2481,45 +2469,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129082629</v>
+        <v>129082566</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436335</v>
+        <v>436258</v>
       </c>
       <c r="R20" t="n">
-        <v>6786743</v>
+        <v>6786851</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2560,6 +2557,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2578,10 +2576,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129082522</v>
+        <v>129082568</v>
       </c>
       <c r="B21" t="n">
-        <v>56917</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,29 +2587,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2621,10 +2620,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436195</v>
+        <v>436409</v>
       </c>
       <c r="R21" t="n">
-        <v>6786902</v>
+        <v>6786563</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2665,6 +2664,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129082504</v>
+        <v>129082524</v>
       </c>
       <c r="B26" t="n">
-        <v>79660</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3090,34 +3090,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436031</v>
+        <v>436189</v>
       </c>
       <c r="R26" t="n">
-        <v>6786744</v>
+        <v>6786920</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3176,45 +3184,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129082636</v>
+        <v>129082562</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436431</v>
+        <v>436015</v>
       </c>
       <c r="R27" t="n">
-        <v>6786583</v>
+        <v>6786713</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3255,6 +3272,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3273,7 +3291,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129082505</v>
+        <v>129082504</v>
       </c>
       <c r="B28" t="n">
         <v>79660</v>
@@ -3308,10 +3326,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436095</v>
+        <v>436031</v>
       </c>
       <c r="R28" t="n">
-        <v>6786747</v>
+        <v>6786744</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3370,7 +3388,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129082653</v>
+        <v>129082636</v>
       </c>
       <c r="B29" t="n">
         <v>79041</v>
@@ -3399,19 +3417,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436092</v>
+        <v>436431</v>
       </c>
       <c r="R29" t="n">
-        <v>6786889</v>
+        <v>6786583</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3452,7 +3467,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3471,7 +3485,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129082512</v>
+        <v>129082505</v>
       </c>
       <c r="B30" t="n">
         <v>79660</v>
@@ -3506,10 +3520,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436428</v>
+        <v>436095</v>
       </c>
       <c r="R30" t="n">
-        <v>6786809</v>
+        <v>6786747</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3568,10 +3582,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129082589</v>
+        <v>129082653</v>
       </c>
       <c r="B31" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3579,34 +3593,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436033</v>
+        <v>436092</v>
       </c>
       <c r="R31" t="n">
-        <v>6786758</v>
+        <v>6786889</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3647,6 +3664,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3665,10 +3683,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129082524</v>
+        <v>129082512</v>
       </c>
       <c r="B32" t="n">
-        <v>57887</v>
+        <v>79660</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3676,42 +3694,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436189</v>
+        <v>436428</v>
       </c>
       <c r="R32" t="n">
-        <v>6786920</v>
+        <v>6786809</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3770,54 +3780,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129082562</v>
+        <v>129082589</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436015</v>
+        <v>436033</v>
       </c>
       <c r="R33" t="n">
-        <v>6786713</v>
+        <v>6786758</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3858,7 +3859,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3877,53 +3877,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129082588</v>
+        <v>129082543</v>
       </c>
       <c r="B34" t="n">
-        <v>58097</v>
+        <v>78799</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435979</v>
+        <v>436027</v>
       </c>
       <c r="R34" t="n">
-        <v>6786531</v>
+        <v>6786747</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3982,54 +3974,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129082573</v>
+        <v>129082551</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436525</v>
+        <v>436436</v>
       </c>
       <c r="R35" t="n">
-        <v>6786729</v>
+        <v>6786563</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4070,7 +4053,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4089,10 +4071,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129082662</v>
+        <v>129082538</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4100,34 +4082,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435932</v>
+        <v>436141</v>
       </c>
       <c r="R36" t="n">
-        <v>6786581</v>
+        <v>6786882</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4186,10 +4176,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129082612</v>
+        <v>129082533</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4197,34 +4187,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435883</v>
+        <v>436445</v>
       </c>
       <c r="R37" t="n">
-        <v>6786641</v>
+        <v>6786610</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4283,45 +4281,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129082646</v>
+        <v>129082588</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>58097</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436400</v>
+        <v>435979</v>
       </c>
       <c r="R38" t="n">
-        <v>6786855</v>
+        <v>6786531</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4380,40 +4386,41 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129082538</v>
+        <v>129082573</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4423,10 +4430,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436141</v>
+        <v>436525</v>
       </c>
       <c r="R39" t="n">
-        <v>6786882</v>
+        <v>6786729</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4467,6 +4474,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4485,10 +4493,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129082533</v>
+        <v>129082662</v>
       </c>
       <c r="B40" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4496,42 +4504,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436445</v>
+        <v>435932</v>
       </c>
       <c r="R40" t="n">
-        <v>6786610</v>
+        <v>6786581</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4590,10 +4590,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129082543</v>
+        <v>129082612</v>
       </c>
       <c r="B41" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4601,21 +4601,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4625,10 +4625,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436027</v>
+        <v>435883</v>
       </c>
       <c r="R41" t="n">
-        <v>6786747</v>
+        <v>6786641</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4687,10 +4687,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129082551</v>
+        <v>129082646</v>
       </c>
       <c r="B42" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4698,21 +4698,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4722,10 +4722,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436436</v>
+        <v>436400</v>
       </c>
       <c r="R42" t="n">
-        <v>6786563</v>
+        <v>6786855</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6499,10 +6499,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129082506</v>
+        <v>129082548</v>
       </c>
       <c r="B60" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6510,37 +6510,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>436172</v>
+        <v>436268</v>
       </c>
       <c r="R60" t="n">
-        <v>6786831</v>
+        <v>6786874</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6581,7 +6578,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6600,10 +6596,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129082644</v>
+        <v>129082516</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6611,34 +6607,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436432</v>
+        <v>436470</v>
       </c>
       <c r="R61" t="n">
-        <v>6786765</v>
+        <v>6786714</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6679,6 +6678,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6697,10 +6697,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129082597</v>
+        <v>129082545</v>
       </c>
       <c r="B62" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6708,34 +6708,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>436469</v>
+        <v>436085</v>
       </c>
       <c r="R62" t="n">
-        <v>6786748</v>
+        <v>6786778</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6776,6 +6779,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6794,10 +6798,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129082666</v>
+        <v>129082515</v>
       </c>
       <c r="B63" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6805,34 +6809,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>436618</v>
+        <v>436075</v>
       </c>
       <c r="R63" t="n">
-        <v>6786620</v>
+        <v>6786747</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6873,6 +6880,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6891,10 +6899,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129082548</v>
+        <v>129082644</v>
       </c>
       <c r="B64" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6902,21 +6910,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6926,10 +6934,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>436268</v>
+        <v>436432</v>
       </c>
       <c r="R64" t="n">
-        <v>6786874</v>
+        <v>6786765</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6988,10 +6996,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129082516</v>
+        <v>129082597</v>
       </c>
       <c r="B65" t="n">
-        <v>79631</v>
+        <v>78798</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6999,37 +7007,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>436470</v>
+        <v>436469</v>
       </c>
       <c r="R65" t="n">
-        <v>6786714</v>
+        <v>6786748</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7070,7 +7075,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7089,10 +7093,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129082545</v>
+        <v>129082666</v>
       </c>
       <c r="B66" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7100,37 +7104,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436085</v>
+        <v>436618</v>
       </c>
       <c r="R66" t="n">
-        <v>6786778</v>
+        <v>6786620</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7171,7 +7172,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7190,10 +7190,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129082515</v>
+        <v>129082506</v>
       </c>
       <c r="B67" t="n">
-        <v>79631</v>
+        <v>79660</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7201,21 +7201,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7228,10 +7228,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436075</v>
+        <v>436172</v>
       </c>
       <c r="R67" t="n">
-        <v>6786747</v>
+        <v>6786831</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7291,45 +7291,54 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129082507</v>
+        <v>129082572</v>
       </c>
       <c r="B68" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436265</v>
+        <v>436553</v>
       </c>
       <c r="R68" t="n">
-        <v>6786874</v>
+        <v>6786640</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7370,6 +7379,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7388,10 +7398,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129082610</v>
+        <v>129082552</v>
       </c>
       <c r="B69" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7399,21 +7409,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7423,10 +7433,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435906</v>
+        <v>436206</v>
       </c>
       <c r="R69" t="n">
-        <v>6786603</v>
+        <v>6786892</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7485,10 +7495,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129082528</v>
+        <v>129082550</v>
       </c>
       <c r="B70" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7496,42 +7506,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436042</v>
+        <v>436361</v>
       </c>
       <c r="R70" t="n">
-        <v>6786785</v>
+        <v>6786687</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7590,10 +7592,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129082552</v>
+        <v>129082507</v>
       </c>
       <c r="B71" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7601,21 +7603,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7625,10 +7627,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436206</v>
+        <v>436265</v>
       </c>
       <c r="R71" t="n">
-        <v>6786892</v>
+        <v>6786874</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7687,10 +7689,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129082550</v>
+        <v>129082610</v>
       </c>
       <c r="B72" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7698,21 +7700,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7722,10 +7724,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436361</v>
+        <v>435906</v>
       </c>
       <c r="R72" t="n">
-        <v>6786687</v>
+        <v>6786603</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7784,41 +7786,40 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129082572</v>
+        <v>129082528</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -7828,10 +7829,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436553</v>
+        <v>436042</v>
       </c>
       <c r="R73" t="n">
-        <v>6786640</v>
+        <v>6786785</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7872,7 +7873,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7891,40 +7891,41 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129082534</v>
+        <v>129082579</v>
       </c>
       <c r="B74" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -7934,10 +7935,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436565</v>
+        <v>436306</v>
       </c>
       <c r="R74" t="n">
-        <v>6786624</v>
+        <v>6786960</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7978,6 +7979,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7996,7 +7998,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129082539</v>
+        <v>129082534</v>
       </c>
       <c r="B75" t="n">
         <v>57724</v>
@@ -8029,7 +8031,7 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -8039,10 +8041,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436069</v>
+        <v>436565</v>
       </c>
       <c r="R75" t="n">
-        <v>6786886</v>
+        <v>6786624</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8101,7 +8103,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129082540</v>
+        <v>129082539</v>
       </c>
       <c r="B76" t="n">
         <v>57724</v>
@@ -8134,7 +8136,7 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -8144,10 +8146,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436188</v>
+        <v>436069</v>
       </c>
       <c r="R76" t="n">
-        <v>6786921</v>
+        <v>6786886</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8206,10 +8208,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129082639</v>
+        <v>129082540</v>
       </c>
       <c r="B77" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8217,34 +8219,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436568</v>
+        <v>436188</v>
       </c>
       <c r="R77" t="n">
-        <v>6786650</v>
+        <v>6786921</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8303,10 +8313,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129082503</v>
+        <v>129082639</v>
       </c>
       <c r="B78" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8314,21 +8324,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8338,10 +8348,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436052</v>
+        <v>436568</v>
       </c>
       <c r="R78" t="n">
-        <v>6786720</v>
+        <v>6786650</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8400,10 +8410,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129082634</v>
+        <v>129082503</v>
       </c>
       <c r="B79" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8411,21 +8421,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8435,10 +8445,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436338</v>
+        <v>436052</v>
       </c>
       <c r="R79" t="n">
-        <v>6786664</v>
+        <v>6786720</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8497,54 +8507,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129082579</v>
+        <v>129082634</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436306</v>
+        <v>436338</v>
       </c>
       <c r="R80" t="n">
-        <v>6786960</v>
+        <v>6786664</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8585,7 +8586,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9291,42 +9291,37 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129082525</v>
+        <v>129082671</v>
       </c>
       <c r="B88" t="n">
-        <v>57887</v>
+        <v>92835</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9334,10 +9329,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>435948</v>
+        <v>436349</v>
       </c>
       <c r="R88" t="n">
-        <v>6786586</v>
+        <v>6786689</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9378,6 +9373,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9396,54 +9392,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129082582</v>
+        <v>129082654</v>
       </c>
       <c r="B89" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>436138</v>
+        <v>436054</v>
       </c>
       <c r="R89" t="n">
-        <v>6786894</v>
+        <v>6786881</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9484,7 +9471,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9503,10 +9489,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129082514</v>
+        <v>129082625</v>
       </c>
       <c r="B90" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9514,21 +9500,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9538,10 +9524,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436044</v>
+        <v>436202</v>
       </c>
       <c r="R90" t="n">
-        <v>6786741</v>
+        <v>6786849</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9600,10 +9586,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129082556</v>
+        <v>129082665</v>
       </c>
       <c r="B91" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9611,21 +9597,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9635,10 +9621,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>436010</v>
+        <v>436330</v>
       </c>
       <c r="R91" t="n">
-        <v>6786852</v>
+        <v>6786736</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9697,48 +9683,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129082671</v>
+        <v>129082606</v>
       </c>
       <c r="B92" t="n">
-        <v>92835</v>
+        <v>79041</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>436349</v>
+        <v>435970</v>
       </c>
       <c r="R92" t="n">
-        <v>6786689</v>
+        <v>6786458</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9779,7 +9762,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9798,7 +9780,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129082654</v>
+        <v>129082619</v>
       </c>
       <c r="B93" t="n">
         <v>79041</v>
@@ -9833,10 +9815,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436054</v>
+        <v>436034</v>
       </c>
       <c r="R93" t="n">
-        <v>6786881</v>
+        <v>6786743</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9895,7 +9877,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129082625</v>
+        <v>129082616</v>
       </c>
       <c r="B94" t="n">
         <v>79041</v>
@@ -9930,10 +9912,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436202</v>
+        <v>436012</v>
       </c>
       <c r="R94" t="n">
-        <v>6786849</v>
+        <v>6786734</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9992,10 +9974,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129082665</v>
+        <v>129082595</v>
       </c>
       <c r="B95" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10003,21 +9985,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10027,10 +10009,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436330</v>
+        <v>436361</v>
       </c>
       <c r="R95" t="n">
-        <v>6786736</v>
+        <v>6786688</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10089,10 +10071,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129082606</v>
+        <v>129082594</v>
       </c>
       <c r="B96" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10100,21 +10082,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10124,10 +10106,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>435970</v>
+        <v>436339</v>
       </c>
       <c r="R96" t="n">
-        <v>6786458</v>
+        <v>6786747</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10186,10 +10168,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129082619</v>
+        <v>129082536</v>
       </c>
       <c r="B97" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10197,34 +10179,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436034</v>
+        <v>436544</v>
       </c>
       <c r="R97" t="n">
-        <v>6786743</v>
+        <v>6786666</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10283,10 +10273,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129082616</v>
+        <v>129082525</v>
       </c>
       <c r="B98" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10294,34 +10284,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436012</v>
+        <v>435948</v>
       </c>
       <c r="R98" t="n">
-        <v>6786734</v>
+        <v>6786586</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10380,45 +10378,54 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129082595</v>
+        <v>129082582</v>
       </c>
       <c r="B99" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436361</v>
+        <v>436138</v>
       </c>
       <c r="R99" t="n">
-        <v>6786688</v>
+        <v>6786894</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10459,6 +10466,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10477,10 +10485,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129082594</v>
+        <v>129082514</v>
       </c>
       <c r="B100" t="n">
-        <v>78798</v>
+        <v>79631</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10488,21 +10496,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10512,10 +10520,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436339</v>
+        <v>436044</v>
       </c>
       <c r="R100" t="n">
-        <v>6786747</v>
+        <v>6786741</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10574,10 +10582,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129082536</v>
+        <v>129082556</v>
       </c>
       <c r="B101" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10585,42 +10593,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>436544</v>
+        <v>436010</v>
       </c>
       <c r="R101" t="n">
-        <v>6786666</v>
+        <v>6786852</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10679,45 +10679,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129082621</v>
+        <v>129082578</v>
       </c>
       <c r="B102" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>436086</v>
+        <v>436368</v>
       </c>
       <c r="R102" t="n">
-        <v>6786788</v>
+        <v>6786971</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10758,6 +10767,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10776,10 +10786,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129082642</v>
+        <v>129082591</v>
       </c>
       <c r="B103" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10787,21 +10797,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10811,10 +10821,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>436506</v>
+        <v>436044</v>
       </c>
       <c r="R103" t="n">
-        <v>6786683</v>
+        <v>6786741</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10873,10 +10883,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129082591</v>
+        <v>129082621</v>
       </c>
       <c r="B104" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10884,21 +10894,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10908,10 +10918,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>436044</v>
+        <v>436086</v>
       </c>
       <c r="R104" t="n">
-        <v>6786741</v>
+        <v>6786788</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10970,7 +10980,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129082650</v>
+        <v>129082642</v>
       </c>
       <c r="B105" t="n">
         <v>79041</v>
@@ -11005,10 +11015,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>436235</v>
+        <v>436506</v>
       </c>
       <c r="R105" t="n">
-        <v>6786944</v>
+        <v>6786683</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11067,10 +11077,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129082532</v>
+        <v>129082650</v>
       </c>
       <c r="B106" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11078,42 +11088,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>436295</v>
+        <v>436235</v>
       </c>
       <c r="R106" t="n">
-        <v>6786848</v>
+        <v>6786944</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11172,7 +11174,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129082531</v>
+        <v>129082532</v>
       </c>
       <c r="B107" t="n">
         <v>57724</v>
@@ -11215,10 +11217,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436246</v>
+        <v>436295</v>
       </c>
       <c r="R107" t="n">
-        <v>6786863</v>
+        <v>6786848</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11277,41 +11279,40 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129082578</v>
+        <v>129082531</v>
       </c>
       <c r="B108" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
@@ -11321,10 +11322,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>436368</v>
+        <v>436246</v>
       </c>
       <c r="R108" t="n">
-        <v>6786971</v>
+        <v>6786863</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11365,7 +11366,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -12782,10 +12782,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129082613</v>
+        <v>129082598</v>
       </c>
       <c r="B123" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12793,21 +12793,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12817,10 +12817,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>435886</v>
+        <v>436107</v>
       </c>
       <c r="R123" t="n">
-        <v>6786666</v>
+        <v>6786875</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12879,45 +12879,54 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129082618</v>
+        <v>129082565</v>
       </c>
       <c r="B124" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>436027</v>
+        <v>436230</v>
       </c>
       <c r="R124" t="n">
-        <v>6786735</v>
+        <v>6786855</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12958,6 +12967,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -12976,45 +12986,54 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129082598</v>
+        <v>129082563</v>
       </c>
       <c r="B125" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>436107</v>
+        <v>436055</v>
       </c>
       <c r="R125" t="n">
-        <v>6786875</v>
+        <v>6786776</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13055,6 +13074,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13073,54 +13093,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129082565</v>
+        <v>129082618</v>
       </c>
       <c r="B126" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436230</v>
+        <v>436027</v>
       </c>
       <c r="R126" t="n">
-        <v>6786855</v>
+        <v>6786735</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13161,7 +13172,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13180,54 +13190,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129082563</v>
+        <v>129082613</v>
       </c>
       <c r="B127" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>436055</v>
+        <v>435886</v>
       </c>
       <c r="R127" t="n">
-        <v>6786776</v>
+        <v>6786666</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13268,7 +13269,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13287,45 +13287,54 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129082596</v>
+        <v>129082583</v>
       </c>
       <c r="B128" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>436432</v>
+        <v>436011</v>
       </c>
       <c r="R128" t="n">
-        <v>6786558</v>
+        <v>6786844</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13366,6 +13375,7 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13384,45 +13394,54 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129082626</v>
+        <v>129082558</v>
       </c>
       <c r="B129" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>436240</v>
+        <v>435909</v>
       </c>
       <c r="R129" t="n">
-        <v>6786833</v>
+        <v>6786616</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13463,6 +13482,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13481,10 +13501,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129082664</v>
+        <v>129082547</v>
       </c>
       <c r="B130" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13492,21 +13512,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13516,10 +13536,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436029</v>
+        <v>436172</v>
       </c>
       <c r="R130" t="n">
-        <v>6786750</v>
+        <v>6786825</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13578,10 +13598,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129082535</v>
+        <v>129082596</v>
       </c>
       <c r="B131" t="n">
-        <v>57724</v>
+        <v>78798</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13589,42 +13609,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>436575</v>
+        <v>436432</v>
       </c>
       <c r="R131" t="n">
-        <v>6786632</v>
+        <v>6786558</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13683,54 +13695,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129082583</v>
+        <v>129082626</v>
       </c>
       <c r="B132" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>436011</v>
+        <v>436240</v>
       </c>
       <c r="R132" t="n">
-        <v>6786844</v>
+        <v>6786833</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13771,7 +13774,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13790,54 +13792,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129082558</v>
+        <v>129082664</v>
       </c>
       <c r="B133" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>435909</v>
+        <v>436029</v>
       </c>
       <c r="R133" t="n">
-        <v>6786616</v>
+        <v>6786750</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13878,7 +13871,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -13897,10 +13889,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129082547</v>
+        <v>129082535</v>
       </c>
       <c r="B134" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13908,34 +13900,42 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>436172</v>
+        <v>436575</v>
       </c>
       <c r="R134" t="n">
-        <v>6786825</v>
+        <v>6786632</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>

--- a/artfynd/A 49064-2025 artfynd.xlsx
+++ b/artfynd/A 49064-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129082570</v>
+        <v>129082641</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436428</v>
+        <v>436537</v>
       </c>
       <c r="R2" t="n">
-        <v>6786577</v>
+        <v>6786684</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129082546</v>
+        <v>129082659</v>
       </c>
       <c r="B3" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436092</v>
+        <v>435974</v>
       </c>
       <c r="R3" t="n">
-        <v>6786744</v>
+        <v>6786534</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129082544</v>
+        <v>129082637</v>
       </c>
       <c r="B4" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436044</v>
+        <v>436410</v>
       </c>
       <c r="R4" t="n">
-        <v>6786741</v>
+        <v>6786560</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,45 +966,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129082641</v>
+        <v>129082570</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436537</v>
+        <v>436428</v>
       </c>
       <c r="R5" t="n">
-        <v>6786684</v>
+        <v>6786577</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1055,6 +1054,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129082659</v>
+        <v>129082546</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435974</v>
+        <v>436092</v>
       </c>
       <c r="R6" t="n">
-        <v>6786534</v>
+        <v>6786744</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129082637</v>
+        <v>129082544</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436410</v>
+        <v>436044</v>
       </c>
       <c r="R7" t="n">
-        <v>6786560</v>
+        <v>6786741</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1675,45 +1675,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129082508</v>
+        <v>129082559</v>
       </c>
       <c r="B12" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436338</v>
+        <v>435893</v>
       </c>
       <c r="R12" t="n">
-        <v>6786741</v>
+        <v>6786660</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1754,6 +1763,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1772,7 +1782,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129082510</v>
+        <v>129082508</v>
       </c>
       <c r="B13" t="n">
         <v>79660</v>
@@ -1807,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436506</v>
+        <v>436338</v>
       </c>
       <c r="R13" t="n">
-        <v>6786715</v>
+        <v>6786741</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1869,54 +1879,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129082559</v>
+        <v>129082510</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435893</v>
+        <v>436506</v>
       </c>
       <c r="R14" t="n">
-        <v>6786660</v>
+        <v>6786715</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1957,7 +1958,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1976,45 +1976,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129082652</v>
+        <v>129082568</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436190</v>
+        <v>436409</v>
       </c>
       <c r="R15" t="n">
-        <v>6786911</v>
+        <v>6786563</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2055,6 +2064,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2073,45 +2083,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129082622</v>
+        <v>129082566</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436101</v>
+        <v>436258</v>
       </c>
       <c r="R16" t="n">
-        <v>6786774</v>
+        <v>6786851</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2152,6 +2171,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2170,7 +2190,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129082629</v>
+        <v>129082652</v>
       </c>
       <c r="B17" t="n">
         <v>79041</v>
@@ -2205,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436335</v>
+        <v>436190</v>
       </c>
       <c r="R17" t="n">
-        <v>6786743</v>
+        <v>6786911</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2267,7 +2287,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129082630</v>
+        <v>129082622</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2302,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436320</v>
+        <v>436101</v>
       </c>
       <c r="R18" t="n">
-        <v>6786718</v>
+        <v>6786774</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2364,53 +2384,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129082522</v>
+        <v>129082629</v>
       </c>
       <c r="B19" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436195</v>
+        <v>436335</v>
       </c>
       <c r="R19" t="n">
-        <v>6786902</v>
+        <v>6786743</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2469,54 +2481,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129082566</v>
+        <v>129082630</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436258</v>
+        <v>436320</v>
       </c>
       <c r="R20" t="n">
-        <v>6786851</v>
+        <v>6786718</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2557,7 +2560,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2576,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129082568</v>
+        <v>129082522</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>56917</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2587,30 +2589,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2620,10 +2621,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436409</v>
+        <v>436195</v>
       </c>
       <c r="R21" t="n">
-        <v>6786563</v>
+        <v>6786902</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,7 +2665,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129082524</v>
+        <v>129082504</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>79660</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3090,42 +3090,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436189</v>
+        <v>436031</v>
       </c>
       <c r="R26" t="n">
-        <v>6786920</v>
+        <v>6786744</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3184,54 +3176,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129082562</v>
+        <v>129082636</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436015</v>
+        <v>436431</v>
       </c>
       <c r="R27" t="n">
-        <v>6786713</v>
+        <v>6786583</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3272,7 +3255,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3291,7 +3273,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129082504</v>
+        <v>129082505</v>
       </c>
       <c r="B28" t="n">
         <v>79660</v>
@@ -3326,10 +3308,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436031</v>
+        <v>436095</v>
       </c>
       <c r="R28" t="n">
-        <v>6786744</v>
+        <v>6786747</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3388,7 +3370,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129082636</v>
+        <v>129082653</v>
       </c>
       <c r="B29" t="n">
         <v>79041</v>
@@ -3417,16 +3399,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436431</v>
+        <v>436092</v>
       </c>
       <c r="R29" t="n">
-        <v>6786583</v>
+        <v>6786889</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3467,6 +3452,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3485,7 +3471,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129082505</v>
+        <v>129082512</v>
       </c>
       <c r="B30" t="n">
         <v>79660</v>
@@ -3520,10 +3506,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436095</v>
+        <v>436428</v>
       </c>
       <c r="R30" t="n">
-        <v>6786747</v>
+        <v>6786809</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3582,10 +3568,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129082653</v>
+        <v>129082589</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3593,37 +3579,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436092</v>
+        <v>436033</v>
       </c>
       <c r="R31" t="n">
-        <v>6786889</v>
+        <v>6786758</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3664,7 +3647,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3683,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129082512</v>
+        <v>129082524</v>
       </c>
       <c r="B32" t="n">
-        <v>79660</v>
+        <v>57887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3694,34 +3676,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436428</v>
+        <v>436189</v>
       </c>
       <c r="R32" t="n">
-        <v>6786809</v>
+        <v>6786920</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3780,45 +3770,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129082589</v>
+        <v>129082562</v>
       </c>
       <c r="B33" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436033</v>
+        <v>436015</v>
       </c>
       <c r="R33" t="n">
-        <v>6786758</v>
+        <v>6786713</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3859,6 +3858,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3877,10 +3877,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129082543</v>
+        <v>129082662</v>
       </c>
       <c r="B34" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3888,21 +3888,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436027</v>
+        <v>435932</v>
       </c>
       <c r="R34" t="n">
-        <v>6786747</v>
+        <v>6786581</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3974,10 +3974,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129082551</v>
+        <v>129082612</v>
       </c>
       <c r="B35" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3985,21 +3985,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436436</v>
+        <v>435883</v>
       </c>
       <c r="R35" t="n">
-        <v>6786563</v>
+        <v>6786641</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4071,10 +4071,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129082538</v>
+        <v>129082646</v>
       </c>
       <c r="B36" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4082,42 +4082,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436141</v>
+        <v>436400</v>
       </c>
       <c r="R36" t="n">
-        <v>6786882</v>
+        <v>6786855</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4176,27 +4168,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129082533</v>
+        <v>129082588</v>
       </c>
       <c r="B37" t="n">
-        <v>57724</v>
+        <v>58097</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4209,7 +4201,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4219,10 +4211,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436445</v>
+        <v>435979</v>
       </c>
       <c r="R37" t="n">
-        <v>6786610</v>
+        <v>6786531</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4281,27 +4273,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129082588</v>
+        <v>129082538</v>
       </c>
       <c r="B38" t="n">
-        <v>58097</v>
+        <v>57724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4314,7 +4306,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4324,10 +4316,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435979</v>
+        <v>436141</v>
       </c>
       <c r="R38" t="n">
-        <v>6786531</v>
+        <v>6786882</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4386,41 +4378,40 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129082573</v>
+        <v>129082533</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4430,10 +4421,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436525</v>
+        <v>436445</v>
       </c>
       <c r="R39" t="n">
-        <v>6786729</v>
+        <v>6786610</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4474,7 +4465,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4493,10 +4483,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129082662</v>
+        <v>129082543</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4504,21 +4494,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4528,10 +4518,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435932</v>
+        <v>436027</v>
       </c>
       <c r="R40" t="n">
-        <v>6786581</v>
+        <v>6786747</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4590,45 +4580,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129082612</v>
+        <v>129082573</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435883</v>
+        <v>436525</v>
       </c>
       <c r="R41" t="n">
-        <v>6786641</v>
+        <v>6786729</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4669,6 +4668,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4687,10 +4687,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129082646</v>
+        <v>129082551</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4698,21 +4698,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4722,10 +4722,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436400</v>
+        <v>436436</v>
       </c>
       <c r="R42" t="n">
-        <v>6786855</v>
+        <v>6786563</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5279,37 +5279,43 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129082648</v>
+        <v>129082567</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5317,10 +5323,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436353</v>
+        <v>436312</v>
       </c>
       <c r="R48" t="n">
-        <v>6786940</v>
+        <v>6786810</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5380,45 +5386,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129082611</v>
+        <v>129082585</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435898</v>
+        <v>435948</v>
       </c>
       <c r="R49" t="n">
-        <v>6786619</v>
+        <v>6786565</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5459,6 +5474,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5477,7 +5493,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129082624</v>
+        <v>129082648</v>
       </c>
       <c r="B50" t="n">
         <v>79041</v>
@@ -5506,16 +5522,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436138</v>
+        <v>436353</v>
       </c>
       <c r="R50" t="n">
-        <v>6786811</v>
+        <v>6786940</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5556,6 +5575,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5574,7 +5594,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129082655</v>
+        <v>129082611</v>
       </c>
       <c r="B51" t="n">
         <v>79041</v>
@@ -5609,10 +5629,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436020</v>
+        <v>435898</v>
       </c>
       <c r="R51" t="n">
-        <v>6786856</v>
+        <v>6786619</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5671,10 +5691,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129082529</v>
+        <v>129082624</v>
       </c>
       <c r="B52" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5682,42 +5702,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436057</v>
+        <v>436138</v>
       </c>
       <c r="R52" t="n">
-        <v>6786761</v>
+        <v>6786811</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5776,54 +5788,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129082567</v>
+        <v>129082655</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436312</v>
+        <v>436020</v>
       </c>
       <c r="R53" t="n">
-        <v>6786810</v>
+        <v>6786856</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5864,7 +5867,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5883,41 +5885,40 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129082585</v>
+        <v>129082529</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -5927,10 +5928,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435948</v>
+        <v>436057</v>
       </c>
       <c r="R54" t="n">
-        <v>6786565</v>
+        <v>6786761</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5971,7 +5972,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5990,7 +5990,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129082656</v>
+        <v>129082647</v>
       </c>
       <c r="B55" t="n">
         <v>79041</v>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435996</v>
+        <v>436372</v>
       </c>
       <c r="R55" t="n">
-        <v>6786755</v>
+        <v>6786946</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6087,7 +6087,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129082647</v>
+        <v>129082656</v>
       </c>
       <c r="B56" t="n">
         <v>79041</v>
@@ -6122,10 +6122,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>436372</v>
+        <v>435996</v>
       </c>
       <c r="R56" t="n">
-        <v>6786946</v>
+        <v>6786755</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6184,37 +6184,43 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129082555</v>
+        <v>129082577</v>
       </c>
       <c r="B57" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6222,10 +6228,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>436072</v>
+        <v>436381</v>
       </c>
       <c r="R57" t="n">
-        <v>6786886</v>
+        <v>6786936</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6285,7 +6291,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129082577</v>
+        <v>129082564</v>
       </c>
       <c r="B58" t="n">
         <v>8450</v>
@@ -6319,7 +6325,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6329,10 +6335,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>436381</v>
+        <v>436166</v>
       </c>
       <c r="R58" t="n">
-        <v>6786936</v>
+        <v>6786846</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6392,43 +6398,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129082564</v>
+        <v>129082555</v>
       </c>
       <c r="B59" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>436166</v>
+        <v>436072</v>
       </c>
       <c r="R59" t="n">
-        <v>6786846</v>
+        <v>6786886</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7291,54 +7291,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129082572</v>
+        <v>129082507</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436553</v>
+        <v>436265</v>
       </c>
       <c r="R68" t="n">
-        <v>6786640</v>
+        <v>6786874</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7379,7 +7370,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7398,10 +7388,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129082552</v>
+        <v>129082610</v>
       </c>
       <c r="B69" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7409,21 +7399,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7433,10 +7423,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>436206</v>
+        <v>435906</v>
       </c>
       <c r="R69" t="n">
-        <v>6786892</v>
+        <v>6786603</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7495,45 +7485,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129082550</v>
+        <v>129082572</v>
       </c>
       <c r="B70" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436361</v>
+        <v>436553</v>
       </c>
       <c r="R70" t="n">
-        <v>6786687</v>
+        <v>6786640</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7574,6 +7573,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7592,10 +7592,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129082507</v>
+        <v>129082550</v>
       </c>
       <c r="B71" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7603,21 +7603,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7627,10 +7627,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436265</v>
+        <v>436361</v>
       </c>
       <c r="R71" t="n">
-        <v>6786874</v>
+        <v>6786687</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7689,10 +7689,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129082610</v>
+        <v>129082552</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7700,21 +7700,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7724,10 +7724,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435906</v>
+        <v>436206</v>
       </c>
       <c r="R72" t="n">
-        <v>6786603</v>
+        <v>6786892</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7891,54 +7891,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129082579</v>
+        <v>129082639</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436306</v>
+        <v>436568</v>
       </c>
       <c r="R74" t="n">
-        <v>6786960</v>
+        <v>6786650</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7979,7 +7970,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7998,10 +7988,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129082534</v>
+        <v>129082503</v>
       </c>
       <c r="B75" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8009,42 +7999,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436565</v>
+        <v>436052</v>
       </c>
       <c r="R75" t="n">
-        <v>6786624</v>
+        <v>6786720</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8103,10 +8085,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129082539</v>
+        <v>129082634</v>
       </c>
       <c r="B76" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8114,42 +8096,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436069</v>
+        <v>436338</v>
       </c>
       <c r="R76" t="n">
-        <v>6786886</v>
+        <v>6786664</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8208,7 +8182,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129082540</v>
+        <v>129082534</v>
       </c>
       <c r="B77" t="n">
         <v>57724</v>
@@ -8251,10 +8225,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436188</v>
+        <v>436565</v>
       </c>
       <c r="R77" t="n">
-        <v>6786921</v>
+        <v>6786624</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8313,10 +8287,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129082639</v>
+        <v>129082539</v>
       </c>
       <c r="B78" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8324,34 +8298,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436568</v>
+        <v>436069</v>
       </c>
       <c r="R78" t="n">
-        <v>6786650</v>
+        <v>6786886</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8410,10 +8392,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129082503</v>
+        <v>129082540</v>
       </c>
       <c r="B79" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8421,34 +8403,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436052</v>
+        <v>436188</v>
       </c>
       <c r="R79" t="n">
-        <v>6786720</v>
+        <v>6786921</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8507,45 +8497,54 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129082634</v>
+        <v>129082579</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436338</v>
+        <v>436306</v>
       </c>
       <c r="R80" t="n">
-        <v>6786664</v>
+        <v>6786960</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8586,6 +8585,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9294,7 +9294,7 @@
         <v>129082671</v>
       </c>
       <c r="B88" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9392,10 +9392,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129082654</v>
+        <v>129082525</v>
       </c>
       <c r="B89" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9403,34 +9403,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>436054</v>
+        <v>435948</v>
       </c>
       <c r="R89" t="n">
-        <v>6786881</v>
+        <v>6786586</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9489,10 +9497,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129082625</v>
+        <v>129082514</v>
       </c>
       <c r="B90" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9500,21 +9508,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9524,10 +9532,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436202</v>
+        <v>436044</v>
       </c>
       <c r="R90" t="n">
-        <v>6786849</v>
+        <v>6786741</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9586,10 +9594,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129082665</v>
+        <v>129082556</v>
       </c>
       <c r="B91" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9597,21 +9605,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9621,10 +9629,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>436330</v>
+        <v>436010</v>
       </c>
       <c r="R91" t="n">
-        <v>6786736</v>
+        <v>6786852</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9683,7 +9691,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129082606</v>
+        <v>129082654</v>
       </c>
       <c r="B92" t="n">
         <v>79041</v>
@@ -9718,10 +9726,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>435970</v>
+        <v>436054</v>
       </c>
       <c r="R92" t="n">
-        <v>6786458</v>
+        <v>6786881</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9780,7 +9788,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129082619</v>
+        <v>129082625</v>
       </c>
       <c r="B93" t="n">
         <v>79041</v>
@@ -9815,10 +9823,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436034</v>
+        <v>436202</v>
       </c>
       <c r="R93" t="n">
-        <v>6786743</v>
+        <v>6786849</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9877,7 +9885,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129082616</v>
+        <v>129082665</v>
       </c>
       <c r="B94" t="n">
         <v>79041</v>
@@ -9912,10 +9920,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436012</v>
+        <v>436330</v>
       </c>
       <c r="R94" t="n">
-        <v>6786734</v>
+        <v>6786736</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9974,10 +9982,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129082595</v>
+        <v>129082606</v>
       </c>
       <c r="B95" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9985,21 +9993,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10009,10 +10017,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436361</v>
+        <v>435970</v>
       </c>
       <c r="R95" t="n">
-        <v>6786688</v>
+        <v>6786458</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10071,10 +10079,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129082594</v>
+        <v>129082619</v>
       </c>
       <c r="B96" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10082,21 +10090,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10106,10 +10114,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436339</v>
+        <v>436034</v>
       </c>
       <c r="R96" t="n">
-        <v>6786747</v>
+        <v>6786743</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10168,10 +10176,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129082536</v>
+        <v>129082616</v>
       </c>
       <c r="B97" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10179,42 +10187,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436544</v>
+        <v>436012</v>
       </c>
       <c r="R97" t="n">
-        <v>6786666</v>
+        <v>6786734</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10273,10 +10273,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129082525</v>
+        <v>129082595</v>
       </c>
       <c r="B98" t="n">
-        <v>57887</v>
+        <v>78798</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10284,42 +10284,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>435948</v>
+        <v>436361</v>
       </c>
       <c r="R98" t="n">
-        <v>6786586</v>
+        <v>6786688</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10378,54 +10370,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129082582</v>
+        <v>129082594</v>
       </c>
       <c r="B99" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436138</v>
+        <v>436339</v>
       </c>
       <c r="R99" t="n">
-        <v>6786894</v>
+        <v>6786747</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10466,7 +10449,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10485,10 +10467,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129082514</v>
+        <v>129082536</v>
       </c>
       <c r="B100" t="n">
-        <v>79631</v>
+        <v>57724</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10496,34 +10478,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436044</v>
+        <v>436544</v>
       </c>
       <c r="R100" t="n">
-        <v>6786741</v>
+        <v>6786666</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10582,45 +10572,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129082556</v>
+        <v>129082582</v>
       </c>
       <c r="B101" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>436010</v>
+        <v>436138</v>
       </c>
       <c r="R101" t="n">
-        <v>6786852</v>
+        <v>6786894</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10661,6 +10660,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -10679,41 +10679,40 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129082578</v>
+        <v>129082532</v>
       </c>
       <c r="B102" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -10723,10 +10722,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>436368</v>
+        <v>436295</v>
       </c>
       <c r="R102" t="n">
-        <v>6786971</v>
+        <v>6786848</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10767,7 +10766,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10786,10 +10784,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129082591</v>
+        <v>129082531</v>
       </c>
       <c r="B103" t="n">
-        <v>78798</v>
+        <v>57724</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10797,34 +10795,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>436044</v>
+        <v>436246</v>
       </c>
       <c r="R103" t="n">
-        <v>6786741</v>
+        <v>6786863</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10883,45 +10889,54 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129082621</v>
+        <v>129082578</v>
       </c>
       <c r="B104" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>436086</v>
+        <v>436368</v>
       </c>
       <c r="R104" t="n">
-        <v>6786788</v>
+        <v>6786971</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10962,6 +10977,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -10980,7 +10996,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129082642</v>
+        <v>129082621</v>
       </c>
       <c r="B105" t="n">
         <v>79041</v>
@@ -11015,10 +11031,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>436506</v>
+        <v>436086</v>
       </c>
       <c r="R105" t="n">
-        <v>6786683</v>
+        <v>6786788</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11077,7 +11093,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129082650</v>
+        <v>129082642</v>
       </c>
       <c r="B106" t="n">
         <v>79041</v>
@@ -11112,10 +11128,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>436235</v>
+        <v>436506</v>
       </c>
       <c r="R106" t="n">
-        <v>6786944</v>
+        <v>6786683</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11174,10 +11190,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129082532</v>
+        <v>129082591</v>
       </c>
       <c r="B107" t="n">
-        <v>57724</v>
+        <v>78798</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11185,42 +11201,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436295</v>
+        <v>436044</v>
       </c>
       <c r="R107" t="n">
-        <v>6786848</v>
+        <v>6786741</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11279,10 +11287,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129082531</v>
+        <v>129082650</v>
       </c>
       <c r="B108" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11290,42 +11298,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>436246</v>
+        <v>436235</v>
       </c>
       <c r="R108" t="n">
-        <v>6786863</v>
+        <v>6786944</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12063,45 +12063,54 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129082645</v>
+        <v>129082560</v>
       </c>
       <c r="B116" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>436405</v>
+        <v>435897</v>
       </c>
       <c r="R116" t="n">
-        <v>6786825</v>
+        <v>6786676</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12142,6 +12151,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12160,45 +12170,54 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129082554</v>
+        <v>129082576</v>
       </c>
       <c r="B117" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>436096</v>
+        <v>436417</v>
       </c>
       <c r="R117" t="n">
-        <v>6786876</v>
+        <v>6786827</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12239,6 +12258,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12364,7 +12384,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129082576</v>
+        <v>129082580</v>
       </c>
       <c r="B119" t="n">
         <v>8450</v>
@@ -12408,10 +12428,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>436417</v>
+        <v>436280</v>
       </c>
       <c r="R119" t="n">
-        <v>6786827</v>
+        <v>6786936</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12471,54 +12491,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129082580</v>
+        <v>129082645</v>
       </c>
       <c r="B120" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>436280</v>
+        <v>436405</v>
       </c>
       <c r="R120" t="n">
-        <v>6786936</v>
+        <v>6786825</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12559,7 +12570,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12578,54 +12588,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129082560</v>
+        <v>129082633</v>
       </c>
       <c r="B121" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>435897</v>
+        <v>436347</v>
       </c>
       <c r="R121" t="n">
-        <v>6786676</v>
+        <v>6786689</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12666,7 +12667,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12685,10 +12685,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129082633</v>
+        <v>129082554</v>
       </c>
       <c r="B122" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12696,21 +12696,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12720,10 +12720,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>436347</v>
+        <v>436096</v>
       </c>
       <c r="R122" t="n">
-        <v>6786689</v>
+        <v>6786876</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12782,10 +12782,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129082598</v>
+        <v>129082618</v>
       </c>
       <c r="B123" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12793,21 +12793,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12817,10 +12817,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>436107</v>
+        <v>436027</v>
       </c>
       <c r="R123" t="n">
-        <v>6786875</v>
+        <v>6786735</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12879,54 +12879,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129082565</v>
+        <v>129082598</v>
       </c>
       <c r="B124" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>436230</v>
+        <v>436107</v>
       </c>
       <c r="R124" t="n">
-        <v>6786855</v>
+        <v>6786875</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12967,7 +12958,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -12986,54 +12976,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129082563</v>
+        <v>129082613</v>
       </c>
       <c r="B125" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>436055</v>
+        <v>435886</v>
       </c>
       <c r="R125" t="n">
-        <v>6786776</v>
+        <v>6786666</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13074,7 +13055,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13093,45 +13073,54 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129082618</v>
+        <v>129082563</v>
       </c>
       <c r="B126" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436027</v>
+        <v>436055</v>
       </c>
       <c r="R126" t="n">
-        <v>6786735</v>
+        <v>6786776</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13172,6 +13161,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13190,45 +13180,54 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129082613</v>
+        <v>129082565</v>
       </c>
       <c r="B127" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>435886</v>
+        <v>436230</v>
       </c>
       <c r="R127" t="n">
-        <v>6786666</v>
+        <v>6786855</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13269,6 +13268,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13287,54 +13287,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129082583</v>
+        <v>129082596</v>
       </c>
       <c r="B128" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>436011</v>
+        <v>436432</v>
       </c>
       <c r="R128" t="n">
-        <v>6786844</v>
+        <v>6786558</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13375,7 +13366,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -13394,54 +13384,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129082558</v>
+        <v>129082626</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>435909</v>
+        <v>436240</v>
       </c>
       <c r="R129" t="n">
-        <v>6786616</v>
+        <v>6786833</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13482,7 +13463,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13501,10 +13481,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129082547</v>
+        <v>129082664</v>
       </c>
       <c r="B130" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13512,21 +13492,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13536,10 +13516,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436172</v>
+        <v>436029</v>
       </c>
       <c r="R130" t="n">
-        <v>6786825</v>
+        <v>6786750</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13598,10 +13578,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129082596</v>
+        <v>129082535</v>
       </c>
       <c r="B131" t="n">
-        <v>78798</v>
+        <v>57724</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13609,34 +13589,42 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>436432</v>
+        <v>436575</v>
       </c>
       <c r="R131" t="n">
-        <v>6786558</v>
+        <v>6786632</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13695,45 +13683,54 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129082626</v>
+        <v>129082558</v>
       </c>
       <c r="B132" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>436240</v>
+        <v>435909</v>
       </c>
       <c r="R132" t="n">
-        <v>6786833</v>
+        <v>6786616</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13774,6 +13771,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13792,45 +13790,54 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129082664</v>
+        <v>129082583</v>
       </c>
       <c r="B133" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>436029</v>
+        <v>436011</v>
       </c>
       <c r="R133" t="n">
-        <v>6786750</v>
+        <v>6786844</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13871,6 +13878,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -13889,10 +13897,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129082535</v>
+        <v>129082547</v>
       </c>
       <c r="B134" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13900,42 +13908,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>436575</v>
+        <v>436172</v>
       </c>
       <c r="R134" t="n">
-        <v>6786632</v>
+        <v>6786825</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>

--- a/artfynd/A 49064-2025 artfynd.xlsx
+++ b/artfynd/A 49064-2025 artfynd.xlsx
@@ -1073,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129082546</v>
+        <v>129082544</v>
       </c>
       <c r="B6" t="n">
         <v>78799</v>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436092</v>
+        <v>436044</v>
       </c>
       <c r="R6" t="n">
-        <v>6786744</v>
+        <v>6786741</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129082544</v>
+        <v>129082546</v>
       </c>
       <c r="B7" t="n">
         <v>78799</v>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436044</v>
+        <v>436092</v>
       </c>
       <c r="R7" t="n">
-        <v>6786741</v>
+        <v>6786744</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1675,54 +1675,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129082559</v>
+        <v>129082510</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435893</v>
+        <v>436506</v>
       </c>
       <c r="R12" t="n">
-        <v>6786660</v>
+        <v>6786715</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,7 +1754,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1879,45 +1869,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129082510</v>
+        <v>129082559</v>
       </c>
       <c r="B14" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436506</v>
+        <v>435893</v>
       </c>
       <c r="R14" t="n">
-        <v>6786715</v>
+        <v>6786660</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1958,6 +1957,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129082568</v>
+        <v>129082566</v>
       </c>
       <c r="B15" t="n">
         <v>8450</v>
@@ -2010,7 +2010,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436409</v>
+        <v>436258</v>
       </c>
       <c r="R15" t="n">
-        <v>6786563</v>
+        <v>6786851</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2083,7 +2083,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129082566</v>
+        <v>129082568</v>
       </c>
       <c r="B16" t="n">
         <v>8450</v>
@@ -2117,7 +2117,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436258</v>
+        <v>436409</v>
       </c>
       <c r="R16" t="n">
-        <v>6786851</v>
+        <v>6786563</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129082537</v>
+        <v>129082549</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2694,42 +2694,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436399</v>
+        <v>436322</v>
       </c>
       <c r="R22" t="n">
-        <v>6786867</v>
+        <v>6786798</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2982,10 +2974,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129082549</v>
+        <v>129082537</v>
       </c>
       <c r="B25" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2993,34 +2985,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436322</v>
+        <v>436399</v>
       </c>
       <c r="R25" t="n">
-        <v>6786798</v>
+        <v>6786867</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129082504</v>
+        <v>129082524</v>
       </c>
       <c r="B26" t="n">
-        <v>79660</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3090,34 +3090,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436031</v>
+        <v>436189</v>
       </c>
       <c r="R26" t="n">
-        <v>6786744</v>
+        <v>6786920</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3176,45 +3184,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129082636</v>
+        <v>129082562</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436431</v>
+        <v>436015</v>
       </c>
       <c r="R27" t="n">
-        <v>6786583</v>
+        <v>6786713</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3255,6 +3272,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3273,7 +3291,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129082505</v>
+        <v>129082504</v>
       </c>
       <c r="B28" t="n">
         <v>79660</v>
@@ -3308,10 +3326,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436095</v>
+        <v>436031</v>
       </c>
       <c r="R28" t="n">
-        <v>6786747</v>
+        <v>6786744</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3370,7 +3388,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129082653</v>
+        <v>129082636</v>
       </c>
       <c r="B29" t="n">
         <v>79041</v>
@@ -3399,19 +3417,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436092</v>
+        <v>436431</v>
       </c>
       <c r="R29" t="n">
-        <v>6786889</v>
+        <v>6786583</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3452,7 +3467,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3471,7 +3485,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129082512</v>
+        <v>129082505</v>
       </c>
       <c r="B30" t="n">
         <v>79660</v>
@@ -3506,10 +3520,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436428</v>
+        <v>436095</v>
       </c>
       <c r="R30" t="n">
-        <v>6786809</v>
+        <v>6786747</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3568,10 +3582,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129082589</v>
+        <v>129082653</v>
       </c>
       <c r="B31" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3579,34 +3593,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436033</v>
+        <v>436092</v>
       </c>
       <c r="R31" t="n">
-        <v>6786758</v>
+        <v>6786889</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3647,6 +3664,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3665,10 +3683,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129082524</v>
+        <v>129082512</v>
       </c>
       <c r="B32" t="n">
-        <v>57887</v>
+        <v>79660</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3676,42 +3694,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436189</v>
+        <v>436428</v>
       </c>
       <c r="R32" t="n">
-        <v>6786920</v>
+        <v>6786809</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3770,54 +3780,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129082562</v>
+        <v>129082589</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436015</v>
+        <v>436033</v>
       </c>
       <c r="R33" t="n">
-        <v>6786713</v>
+        <v>6786758</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3858,7 +3859,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3877,10 +3877,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129082662</v>
+        <v>129082543</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3888,21 +3888,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435932</v>
+        <v>436027</v>
       </c>
       <c r="R34" t="n">
-        <v>6786581</v>
+        <v>6786747</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3974,10 +3974,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129082612</v>
+        <v>129082551</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3985,21 +3985,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435883</v>
+        <v>436436</v>
       </c>
       <c r="R35" t="n">
-        <v>6786641</v>
+        <v>6786563</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4071,7 +4071,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129082646</v>
+        <v>129082662</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436400</v>
+        <v>435932</v>
       </c>
       <c r="R36" t="n">
-        <v>6786855</v>
+        <v>6786581</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4168,53 +4168,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129082588</v>
+        <v>129082612</v>
       </c>
       <c r="B37" t="n">
-        <v>58097</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435979</v>
+        <v>435883</v>
       </c>
       <c r="R37" t="n">
-        <v>6786531</v>
+        <v>6786641</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4273,10 +4265,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129082538</v>
+        <v>129082646</v>
       </c>
       <c r="B38" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4284,42 +4276,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436141</v>
+        <v>436400</v>
       </c>
       <c r="R38" t="n">
-        <v>6786882</v>
+        <v>6786855</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4378,7 +4362,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129082533</v>
+        <v>129082538</v>
       </c>
       <c r="B39" t="n">
         <v>57724</v>
@@ -4421,10 +4405,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436445</v>
+        <v>436141</v>
       </c>
       <c r="R39" t="n">
-        <v>6786610</v>
+        <v>6786882</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4483,10 +4467,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129082543</v>
+        <v>129082533</v>
       </c>
       <c r="B40" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4494,34 +4478,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436027</v>
+        <v>436445</v>
       </c>
       <c r="R40" t="n">
-        <v>6786747</v>
+        <v>6786610</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4580,10 +4572,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129082573</v>
+        <v>129082588</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>58097</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4591,30 +4583,29 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4624,10 +4615,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436525</v>
+        <v>435979</v>
       </c>
       <c r="R41" t="n">
-        <v>6786729</v>
+        <v>6786531</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4668,7 +4659,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4687,45 +4677,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129082551</v>
+        <v>129082573</v>
       </c>
       <c r="B42" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436436</v>
+        <v>436525</v>
       </c>
       <c r="R42" t="n">
-        <v>6786563</v>
+        <v>6786729</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4766,6 +4765,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4784,10 +4784,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129082590</v>
+        <v>129082553</v>
       </c>
       <c r="B43" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4795,21 +4795,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436051</v>
+        <v>436197</v>
       </c>
       <c r="R43" t="n">
-        <v>6786730</v>
+        <v>6786924</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4881,7 +4881,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129082593</v>
+        <v>129082590</v>
       </c>
       <c r="B44" t="n">
         <v>78798</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436271</v>
+        <v>436051</v>
       </c>
       <c r="R44" t="n">
-        <v>6786851</v>
+        <v>6786730</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4978,10 +4978,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129082663</v>
+        <v>129082593</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4989,21 +4989,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435984</v>
+        <v>436271</v>
       </c>
       <c r="R45" t="n">
-        <v>6786452</v>
+        <v>6786851</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5075,54 +5075,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129082581</v>
+        <v>129082663</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436252</v>
+        <v>435984</v>
       </c>
       <c r="R46" t="n">
-        <v>6786963</v>
+        <v>6786452</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5163,7 +5154,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5182,45 +5172,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129082553</v>
+        <v>129082581</v>
       </c>
       <c r="B47" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436197</v>
+        <v>436252</v>
       </c>
       <c r="R47" t="n">
-        <v>6786924</v>
+        <v>6786963</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5261,6 +5260,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5279,41 +5279,40 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129082567</v>
+        <v>129082529</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5323,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436312</v>
+        <v>436057</v>
       </c>
       <c r="R48" t="n">
-        <v>6786810</v>
+        <v>6786761</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5367,7 +5366,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5493,37 +5491,43 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129082648</v>
+        <v>129082567</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5531,10 +5535,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436353</v>
+        <v>436312</v>
       </c>
       <c r="R50" t="n">
-        <v>6786940</v>
+        <v>6786810</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5594,7 +5598,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129082611</v>
+        <v>129082648</v>
       </c>
       <c r="B51" t="n">
         <v>79041</v>
@@ -5623,16 +5627,19 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435898</v>
+        <v>436353</v>
       </c>
       <c r="R51" t="n">
-        <v>6786619</v>
+        <v>6786940</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5673,6 +5680,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5691,7 +5699,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129082624</v>
+        <v>129082611</v>
       </c>
       <c r="B52" t="n">
         <v>79041</v>
@@ -5726,10 +5734,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436138</v>
+        <v>435898</v>
       </c>
       <c r="R52" t="n">
-        <v>6786811</v>
+        <v>6786619</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5788,7 +5796,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129082655</v>
+        <v>129082624</v>
       </c>
       <c r="B53" t="n">
         <v>79041</v>
@@ -5823,10 +5831,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436020</v>
+        <v>436138</v>
       </c>
       <c r="R53" t="n">
-        <v>6786856</v>
+        <v>6786811</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5885,10 +5893,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129082529</v>
+        <v>129082655</v>
       </c>
       <c r="B54" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5896,42 +5904,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>436057</v>
+        <v>436020</v>
       </c>
       <c r="R54" t="n">
-        <v>6786761</v>
+        <v>6786856</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5990,45 +5990,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129082647</v>
+        <v>129082577</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436372</v>
+        <v>436381</v>
       </c>
       <c r="R55" t="n">
-        <v>6786946</v>
+        <v>6786936</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6069,6 +6078,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6087,45 +6097,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129082656</v>
+        <v>129082564</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435996</v>
+        <v>436166</v>
       </c>
       <c r="R56" t="n">
-        <v>6786755</v>
+        <v>6786846</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6166,6 +6185,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6184,54 +6204,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129082577</v>
+        <v>129082647</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>436381</v>
+        <v>436372</v>
       </c>
       <c r="R57" t="n">
-        <v>6786936</v>
+        <v>6786946</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6272,7 +6283,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6291,54 +6301,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129082564</v>
+        <v>129082656</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>436166</v>
+        <v>435996</v>
       </c>
       <c r="R58" t="n">
-        <v>6786846</v>
+        <v>6786755</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6379,7 +6380,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6499,10 +6499,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129082548</v>
+        <v>129082644</v>
       </c>
       <c r="B60" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6510,21 +6510,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>436268</v>
+        <v>436432</v>
       </c>
       <c r="R60" t="n">
-        <v>6786874</v>
+        <v>6786765</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6596,10 +6596,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129082516</v>
+        <v>129082597</v>
       </c>
       <c r="B61" t="n">
-        <v>79631</v>
+        <v>78798</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6607,37 +6607,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436470</v>
+        <v>436469</v>
       </c>
       <c r="R61" t="n">
-        <v>6786714</v>
+        <v>6786748</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6678,7 +6675,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6697,10 +6693,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129082545</v>
+        <v>129082666</v>
       </c>
       <c r="B62" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6708,37 +6704,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>436085</v>
+        <v>436618</v>
       </c>
       <c r="R62" t="n">
-        <v>6786778</v>
+        <v>6786620</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6779,7 +6772,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6798,10 +6790,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129082515</v>
+        <v>129082506</v>
       </c>
       <c r="B63" t="n">
-        <v>79631</v>
+        <v>79660</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6809,21 +6801,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6836,10 +6828,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>436075</v>
+        <v>436172</v>
       </c>
       <c r="R63" t="n">
-        <v>6786747</v>
+        <v>6786831</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6899,10 +6891,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129082644</v>
+        <v>129082515</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6910,34 +6902,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>436432</v>
+        <v>436075</v>
       </c>
       <c r="R64" t="n">
-        <v>6786765</v>
+        <v>6786747</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6978,6 +6973,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6996,10 +6992,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129082597</v>
+        <v>129082548</v>
       </c>
       <c r="B65" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7007,21 +7003,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7031,10 +7027,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>436469</v>
+        <v>436268</v>
       </c>
       <c r="R65" t="n">
-        <v>6786748</v>
+        <v>6786874</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7093,10 +7089,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129082666</v>
+        <v>129082516</v>
       </c>
       <c r="B66" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7104,34 +7100,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436618</v>
+        <v>436470</v>
       </c>
       <c r="R66" t="n">
-        <v>6786620</v>
+        <v>6786714</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7172,6 +7171,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7190,10 +7190,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129082506</v>
+        <v>129082545</v>
       </c>
       <c r="B67" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7201,21 +7201,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7228,10 +7228,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436172</v>
+        <v>436085</v>
       </c>
       <c r="R67" t="n">
-        <v>6786831</v>
+        <v>6786778</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7291,45 +7291,54 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129082507</v>
+        <v>129082572</v>
       </c>
       <c r="B68" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436265</v>
+        <v>436553</v>
       </c>
       <c r="R68" t="n">
-        <v>6786874</v>
+        <v>6786640</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7370,6 +7379,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7388,10 +7398,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129082610</v>
+        <v>129082550</v>
       </c>
       <c r="B69" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7399,21 +7409,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7423,10 +7433,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>435906</v>
+        <v>436361</v>
       </c>
       <c r="R69" t="n">
-        <v>6786603</v>
+        <v>6786687</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7485,54 +7495,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129082572</v>
+        <v>129082552</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436553</v>
+        <v>436206</v>
       </c>
       <c r="R70" t="n">
-        <v>6786640</v>
+        <v>6786892</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7573,7 +7574,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7592,10 +7592,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129082550</v>
+        <v>129082507</v>
       </c>
       <c r="B71" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7603,21 +7603,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7627,10 +7627,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436361</v>
+        <v>436265</v>
       </c>
       <c r="R71" t="n">
-        <v>6786687</v>
+        <v>6786874</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7689,10 +7689,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129082552</v>
+        <v>129082610</v>
       </c>
       <c r="B72" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7700,21 +7700,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7724,10 +7724,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436206</v>
+        <v>435906</v>
       </c>
       <c r="R72" t="n">
-        <v>6786892</v>
+        <v>6786603</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9291,48 +9291,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129082671</v>
+        <v>129082654</v>
       </c>
       <c r="B88" t="n">
-        <v>92821</v>
+        <v>79041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>436349</v>
+        <v>436054</v>
       </c>
       <c r="R88" t="n">
-        <v>6786689</v>
+        <v>6786881</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9373,7 +9370,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9392,10 +9388,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129082525</v>
+        <v>129082625</v>
       </c>
       <c r="B89" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9403,42 +9399,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>435948</v>
+        <v>436202</v>
       </c>
       <c r="R89" t="n">
-        <v>6786586</v>
+        <v>6786849</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9497,10 +9485,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129082514</v>
+        <v>129082665</v>
       </c>
       <c r="B90" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9508,21 +9496,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9532,10 +9520,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436044</v>
+        <v>436330</v>
       </c>
       <c r="R90" t="n">
-        <v>6786741</v>
+        <v>6786736</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9594,10 +9582,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129082556</v>
+        <v>129082606</v>
       </c>
       <c r="B91" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9605,21 +9593,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9629,10 +9617,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>436010</v>
+        <v>435970</v>
       </c>
       <c r="R91" t="n">
-        <v>6786852</v>
+        <v>6786458</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9691,7 +9679,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129082654</v>
+        <v>129082619</v>
       </c>
       <c r="B92" t="n">
         <v>79041</v>
@@ -9726,10 +9714,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>436054</v>
+        <v>436034</v>
       </c>
       <c r="R92" t="n">
-        <v>6786881</v>
+        <v>6786743</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9788,7 +9776,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129082625</v>
+        <v>129082616</v>
       </c>
       <c r="B93" t="n">
         <v>79041</v>
@@ -9823,10 +9811,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436202</v>
+        <v>436012</v>
       </c>
       <c r="R93" t="n">
-        <v>6786849</v>
+        <v>6786734</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9885,10 +9873,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129082665</v>
+        <v>129082595</v>
       </c>
       <c r="B94" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9896,21 +9884,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9920,10 +9908,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436330</v>
+        <v>436361</v>
       </c>
       <c r="R94" t="n">
-        <v>6786736</v>
+        <v>6786688</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9982,10 +9970,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129082606</v>
+        <v>129082594</v>
       </c>
       <c r="B95" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9993,21 +9981,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10017,10 +10005,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>435970</v>
+        <v>436339</v>
       </c>
       <c r="R95" t="n">
-        <v>6786458</v>
+        <v>6786747</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10079,45 +10067,54 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129082619</v>
+        <v>129082582</v>
       </c>
       <c r="B96" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436034</v>
+        <v>436138</v>
       </c>
       <c r="R96" t="n">
-        <v>6786743</v>
+        <v>6786894</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10158,6 +10155,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10176,45 +10174,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129082616</v>
+        <v>129082671</v>
       </c>
       <c r="B97" t="n">
-        <v>79041</v>
+        <v>92822</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436012</v>
+        <v>436349</v>
       </c>
       <c r="R97" t="n">
-        <v>6786734</v>
+        <v>6786689</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10255,6 +10256,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10273,10 +10275,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129082595</v>
+        <v>129082536</v>
       </c>
       <c r="B98" t="n">
-        <v>78798</v>
+        <v>57724</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10284,34 +10286,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436361</v>
+        <v>436544</v>
       </c>
       <c r="R98" t="n">
-        <v>6786688</v>
+        <v>6786666</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10370,10 +10380,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129082594</v>
+        <v>129082525</v>
       </c>
       <c r="B99" t="n">
-        <v>78798</v>
+        <v>57887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10381,34 +10391,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436339</v>
+        <v>435948</v>
       </c>
       <c r="R99" t="n">
-        <v>6786747</v>
+        <v>6786586</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10467,10 +10485,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129082536</v>
+        <v>129082556</v>
       </c>
       <c r="B100" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10478,42 +10496,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436544</v>
+        <v>436010</v>
       </c>
       <c r="R100" t="n">
-        <v>6786666</v>
+        <v>6786852</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10572,54 +10582,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129082582</v>
+        <v>129082514</v>
       </c>
       <c r="B101" t="n">
-        <v>8450</v>
+        <v>79631</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>436138</v>
+        <v>436044</v>
       </c>
       <c r="R101" t="n">
-        <v>6786894</v>
+        <v>6786741</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10660,7 +10661,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -10889,54 +10889,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129082578</v>
+        <v>129082621</v>
       </c>
       <c r="B104" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>436368</v>
+        <v>436086</v>
       </c>
       <c r="R104" t="n">
-        <v>6786971</v>
+        <v>6786788</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10977,7 +10968,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -10996,7 +10986,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129082621</v>
+        <v>129082642</v>
       </c>
       <c r="B105" t="n">
         <v>79041</v>
@@ -11031,10 +11021,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>436086</v>
+        <v>436506</v>
       </c>
       <c r="R105" t="n">
-        <v>6786788</v>
+        <v>6786683</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11093,10 +11083,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129082642</v>
+        <v>129082591</v>
       </c>
       <c r="B106" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11104,21 +11094,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11128,10 +11118,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>436506</v>
+        <v>436044</v>
       </c>
       <c r="R106" t="n">
-        <v>6786683</v>
+        <v>6786741</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11190,10 +11180,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129082591</v>
+        <v>129082650</v>
       </c>
       <c r="B107" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11201,21 +11191,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11225,10 +11215,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>436044</v>
+        <v>436235</v>
       </c>
       <c r="R107" t="n">
-        <v>6786741</v>
+        <v>6786944</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11287,45 +11277,54 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129082650</v>
+        <v>129082578</v>
       </c>
       <c r="B108" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>436235</v>
+        <v>436368</v>
       </c>
       <c r="R108" t="n">
-        <v>6786944</v>
+        <v>6786971</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11366,6 +11365,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -12063,7 +12063,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129082560</v>
+        <v>129082580</v>
       </c>
       <c r="B116" t="n">
         <v>8450</v>
@@ -12107,10 +12107,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>435897</v>
+        <v>436280</v>
       </c>
       <c r="R116" t="n">
-        <v>6786676</v>
+        <v>6786936</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12170,7 +12170,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129082576</v>
+        <v>129082586</v>
       </c>
       <c r="B117" t="n">
         <v>8450</v>
@@ -12214,10 +12214,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>436417</v>
+        <v>435931</v>
       </c>
       <c r="R117" t="n">
-        <v>6786827</v>
+        <v>6786572</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12277,7 +12277,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129082586</v>
+        <v>129082576</v>
       </c>
       <c r="B118" t="n">
         <v>8450</v>
@@ -12321,10 +12321,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>435931</v>
+        <v>436417</v>
       </c>
       <c r="R118" t="n">
-        <v>6786572</v>
+        <v>6786827</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12384,7 +12384,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129082580</v>
+        <v>129082560</v>
       </c>
       <c r="B119" t="n">
         <v>8450</v>
@@ -12428,10 +12428,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>436280</v>
+        <v>435897</v>
       </c>
       <c r="R119" t="n">
-        <v>6786936</v>
+        <v>6786676</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12491,10 +12491,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129082645</v>
+        <v>129082554</v>
       </c>
       <c r="B120" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12502,21 +12502,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12526,10 +12526,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>436405</v>
+        <v>436096</v>
       </c>
       <c r="R120" t="n">
-        <v>6786825</v>
+        <v>6786876</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12588,7 +12588,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129082633</v>
+        <v>129082645</v>
       </c>
       <c r="B121" t="n">
         <v>79041</v>
@@ -12623,10 +12623,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>436347</v>
+        <v>436405</v>
       </c>
       <c r="R121" t="n">
-        <v>6786689</v>
+        <v>6786825</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12685,10 +12685,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129082554</v>
+        <v>129082633</v>
       </c>
       <c r="B122" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12696,21 +12696,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12720,10 +12720,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>436096</v>
+        <v>436347</v>
       </c>
       <c r="R122" t="n">
-        <v>6786876</v>
+        <v>6786689</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13073,7 +13073,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129082563</v>
+        <v>129082565</v>
       </c>
       <c r="B126" t="n">
         <v>8450</v>
@@ -13117,10 +13117,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436055</v>
+        <v>436230</v>
       </c>
       <c r="R126" t="n">
-        <v>6786776</v>
+        <v>6786855</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13180,7 +13180,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129082565</v>
+        <v>129082563</v>
       </c>
       <c r="B127" t="n">
         <v>8450</v>
@@ -13224,10 +13224,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>436230</v>
+        <v>436055</v>
       </c>
       <c r="R127" t="n">
-        <v>6786855</v>
+        <v>6786776</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>

--- a/artfynd/A 49064-2025 artfynd.xlsx
+++ b/artfynd/A 49064-2025 artfynd.xlsx
@@ -1073,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129082544</v>
+        <v>129082546</v>
       </c>
       <c r="B6" t="n">
         <v>78799</v>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436044</v>
+        <v>436092</v>
       </c>
       <c r="R6" t="n">
-        <v>6786741</v>
+        <v>6786744</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129082546</v>
+        <v>129082544</v>
       </c>
       <c r="B7" t="n">
         <v>78799</v>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436092</v>
+        <v>436044</v>
       </c>
       <c r="R7" t="n">
-        <v>6786744</v>
+        <v>6786741</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129082510</v>
+        <v>129082508</v>
       </c>
       <c r="B12" t="n">
         <v>79660</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436506</v>
+        <v>436338</v>
       </c>
       <c r="R12" t="n">
-        <v>6786715</v>
+        <v>6786741</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129082508</v>
+        <v>129082510</v>
       </c>
       <c r="B13" t="n">
         <v>79660</v>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436338</v>
+        <v>436506</v>
       </c>
       <c r="R13" t="n">
-        <v>6786741</v>
+        <v>6786715</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129082566</v>
+        <v>129082568</v>
       </c>
       <c r="B15" t="n">
         <v>8450</v>
@@ -2010,7 +2010,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436258</v>
+        <v>436409</v>
       </c>
       <c r="R15" t="n">
-        <v>6786851</v>
+        <v>6786563</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2083,7 +2083,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129082568</v>
+        <v>129082566</v>
       </c>
       <c r="B16" t="n">
         <v>8450</v>
@@ -2117,7 +2117,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436409</v>
+        <v>436258</v>
       </c>
       <c r="R16" t="n">
-        <v>6786563</v>
+        <v>6786851</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2190,45 +2190,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129082652</v>
+        <v>129082522</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436190</v>
+        <v>436195</v>
       </c>
       <c r="R17" t="n">
-        <v>6786911</v>
+        <v>6786902</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2287,7 +2295,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129082622</v>
+        <v>129082652</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2322,10 +2330,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436101</v>
+        <v>436190</v>
       </c>
       <c r="R18" t="n">
-        <v>6786774</v>
+        <v>6786911</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2384,7 +2392,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129082629</v>
+        <v>129082622</v>
       </c>
       <c r="B19" t="n">
         <v>79041</v>
@@ -2419,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436335</v>
+        <v>436101</v>
       </c>
       <c r="R19" t="n">
-        <v>6786743</v>
+        <v>6786774</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2481,7 +2489,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129082630</v>
+        <v>129082629</v>
       </c>
       <c r="B20" t="n">
         <v>79041</v>
@@ -2516,10 +2524,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436320</v>
+        <v>436335</v>
       </c>
       <c r="R20" t="n">
-        <v>6786718</v>
+        <v>6786743</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2578,53 +2586,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129082522</v>
+        <v>129082630</v>
       </c>
       <c r="B21" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436195</v>
+        <v>436320</v>
       </c>
       <c r="R21" t="n">
-        <v>6786902</v>
+        <v>6786718</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129082549</v>
+        <v>129082614</v>
       </c>
       <c r="B22" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2694,21 +2694,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436322</v>
+        <v>435889</v>
       </c>
       <c r="R22" t="n">
-        <v>6786798</v>
+        <v>6786670</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2780,7 +2780,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129082614</v>
+        <v>129082640</v>
       </c>
       <c r="B23" t="n">
         <v>79041</v>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435889</v>
+        <v>436530</v>
       </c>
       <c r="R23" t="n">
-        <v>6786670</v>
+        <v>6786657</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129082640</v>
+        <v>129082549</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2888,21 +2888,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436530</v>
+        <v>436322</v>
       </c>
       <c r="R24" t="n">
-        <v>6786657</v>
+        <v>6786798</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3184,54 +3184,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129082562</v>
+        <v>129082504</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436015</v>
+        <v>436031</v>
       </c>
       <c r="R27" t="n">
-        <v>6786713</v>
+        <v>6786744</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3272,7 +3263,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3291,10 +3281,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129082504</v>
+        <v>129082636</v>
       </c>
       <c r="B28" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3302,21 +3292,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3326,10 +3316,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436031</v>
+        <v>436431</v>
       </c>
       <c r="R28" t="n">
-        <v>6786744</v>
+        <v>6786583</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3388,10 +3378,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129082636</v>
+        <v>129082505</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3399,21 +3389,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3423,10 +3413,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436431</v>
+        <v>436095</v>
       </c>
       <c r="R29" t="n">
-        <v>6786583</v>
+        <v>6786747</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3485,10 +3475,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129082505</v>
+        <v>129082653</v>
       </c>
       <c r="B30" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3496,34 +3486,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436095</v>
+        <v>436092</v>
       </c>
       <c r="R30" t="n">
-        <v>6786747</v>
+        <v>6786889</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3564,6 +3557,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3582,10 +3576,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129082653</v>
+        <v>129082512</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3593,37 +3587,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436092</v>
+        <v>436428</v>
       </c>
       <c r="R31" t="n">
-        <v>6786889</v>
+        <v>6786809</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3664,7 +3655,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3683,10 +3673,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129082512</v>
+        <v>129082589</v>
       </c>
       <c r="B32" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3694,21 +3684,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3718,10 +3708,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436428</v>
+        <v>436033</v>
       </c>
       <c r="R32" t="n">
-        <v>6786809</v>
+        <v>6786758</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3780,45 +3770,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129082589</v>
+        <v>129082562</v>
       </c>
       <c r="B33" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436033</v>
+        <v>436015</v>
       </c>
       <c r="R33" t="n">
-        <v>6786758</v>
+        <v>6786713</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3859,6 +3858,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3877,10 +3877,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129082543</v>
+        <v>129082662</v>
       </c>
       <c r="B34" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3888,21 +3888,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436027</v>
+        <v>435932</v>
       </c>
       <c r="R34" t="n">
-        <v>6786747</v>
+        <v>6786581</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3974,10 +3974,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129082551</v>
+        <v>129082612</v>
       </c>
       <c r="B35" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3985,21 +3985,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436436</v>
+        <v>435883</v>
       </c>
       <c r="R35" t="n">
-        <v>6786563</v>
+        <v>6786641</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4071,7 +4071,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129082662</v>
+        <v>129082646</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435932</v>
+        <v>436400</v>
       </c>
       <c r="R36" t="n">
-        <v>6786581</v>
+        <v>6786855</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4168,45 +4168,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129082612</v>
+        <v>129082573</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435883</v>
+        <v>436525</v>
       </c>
       <c r="R37" t="n">
-        <v>6786641</v>
+        <v>6786729</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4247,6 +4256,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4265,10 +4275,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129082646</v>
+        <v>129082543</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4276,21 +4286,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4300,10 +4310,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436400</v>
+        <v>436027</v>
       </c>
       <c r="R38" t="n">
-        <v>6786855</v>
+        <v>6786747</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4362,10 +4372,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129082538</v>
+        <v>129082551</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4373,42 +4383,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436141</v>
+        <v>436436</v>
       </c>
       <c r="R39" t="n">
-        <v>6786882</v>
+        <v>6786563</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4467,7 +4469,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129082533</v>
+        <v>129082538</v>
       </c>
       <c r="B40" t="n">
         <v>57724</v>
@@ -4510,10 +4512,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436445</v>
+        <v>436141</v>
       </c>
       <c r="R40" t="n">
-        <v>6786610</v>
+        <v>6786882</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4572,27 +4574,27 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129082588</v>
+        <v>129082533</v>
       </c>
       <c r="B41" t="n">
-        <v>58097</v>
+        <v>57724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4605,7 +4607,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4615,10 +4617,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435979</v>
+        <v>436445</v>
       </c>
       <c r="R41" t="n">
-        <v>6786531</v>
+        <v>6786610</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4677,10 +4679,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129082573</v>
+        <v>129082588</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>58097</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4688,30 +4690,29 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -4721,10 +4722,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436525</v>
+        <v>435979</v>
       </c>
       <c r="R42" t="n">
-        <v>6786729</v>
+        <v>6786531</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4765,7 +4766,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4784,10 +4784,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129082553</v>
+        <v>129082590</v>
       </c>
       <c r="B43" t="n">
-        <v>78799</v>
+        <v>78798</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4795,21 +4795,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436197</v>
+        <v>436051</v>
       </c>
       <c r="R43" t="n">
-        <v>6786924</v>
+        <v>6786730</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4881,7 +4881,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129082590</v>
+        <v>129082593</v>
       </c>
       <c r="B44" t="n">
         <v>78798</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436051</v>
+        <v>436271</v>
       </c>
       <c r="R44" t="n">
-        <v>6786730</v>
+        <v>6786851</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4978,10 +4978,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129082593</v>
+        <v>129082663</v>
       </c>
       <c r="B45" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4989,21 +4989,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436271</v>
+        <v>435984</v>
       </c>
       <c r="R45" t="n">
-        <v>6786851</v>
+        <v>6786452</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5075,45 +5075,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129082663</v>
+        <v>129082581</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435984</v>
+        <v>436252</v>
       </c>
       <c r="R46" t="n">
-        <v>6786452</v>
+        <v>6786963</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5154,6 +5163,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5172,54 +5182,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129082581</v>
+        <v>129082553</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436252</v>
+        <v>436197</v>
       </c>
       <c r="R47" t="n">
-        <v>6786963</v>
+        <v>6786924</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5260,7 +5261,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5279,10 +5279,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129082529</v>
+        <v>129082648</v>
       </c>
       <c r="B48" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5290,31 +5290,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5322,10 +5317,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436057</v>
+        <v>436353</v>
       </c>
       <c r="R48" t="n">
-        <v>6786761</v>
+        <v>6786940</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5366,6 +5361,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5384,54 +5380,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129082585</v>
+        <v>129082611</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435948</v>
+        <v>435898</v>
       </c>
       <c r="R49" t="n">
-        <v>6786565</v>
+        <v>6786619</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5472,7 +5459,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5491,54 +5477,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129082567</v>
+        <v>129082624</v>
       </c>
       <c r="B50" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436312</v>
+        <v>436138</v>
       </c>
       <c r="R50" t="n">
-        <v>6786810</v>
+        <v>6786811</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5579,7 +5556,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5598,7 +5574,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129082648</v>
+        <v>129082655</v>
       </c>
       <c r="B51" t="n">
         <v>79041</v>
@@ -5627,19 +5603,16 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436353</v>
+        <v>436020</v>
       </c>
       <c r="R51" t="n">
-        <v>6786940</v>
+        <v>6786856</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5680,7 +5653,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5699,45 +5671,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129082611</v>
+        <v>129082567</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435898</v>
+        <v>436312</v>
       </c>
       <c r="R52" t="n">
-        <v>6786619</v>
+        <v>6786810</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5778,6 +5759,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5796,45 +5778,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129082624</v>
+        <v>129082585</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436138</v>
+        <v>435948</v>
       </c>
       <c r="R53" t="n">
-        <v>6786811</v>
+        <v>6786565</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5875,6 +5866,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5893,10 +5885,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129082655</v>
+        <v>129082529</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5904,34 +5896,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>436020</v>
+        <v>436057</v>
       </c>
       <c r="R54" t="n">
-        <v>6786856</v>
+        <v>6786761</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5990,54 +5990,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129082577</v>
+        <v>129082647</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436381</v>
+        <v>436372</v>
       </c>
       <c r="R55" t="n">
-        <v>6786936</v>
+        <v>6786946</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6078,7 +6069,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6097,54 +6087,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129082564</v>
+        <v>129082656</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>436166</v>
+        <v>435996</v>
       </c>
       <c r="R56" t="n">
-        <v>6786846</v>
+        <v>6786755</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6185,7 +6166,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6204,45 +6184,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129082647</v>
+        <v>129082577</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>436372</v>
+        <v>436381</v>
       </c>
       <c r="R57" t="n">
-        <v>6786946</v>
+        <v>6786936</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6283,6 +6272,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6301,45 +6291,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129082656</v>
+        <v>129082564</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435996</v>
+        <v>436166</v>
       </c>
       <c r="R58" t="n">
-        <v>6786755</v>
+        <v>6786846</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6380,6 +6379,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6891,10 +6891,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129082515</v>
+        <v>129082548</v>
       </c>
       <c r="B64" t="n">
-        <v>79631</v>
+        <v>78799</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6902,37 +6902,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>436075</v>
+        <v>436268</v>
       </c>
       <c r="R64" t="n">
-        <v>6786747</v>
+        <v>6786874</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6973,7 +6970,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6992,10 +6988,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129082548</v>
+        <v>129082516</v>
       </c>
       <c r="B65" t="n">
-        <v>78799</v>
+        <v>79631</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7003,34 +6999,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>436268</v>
+        <v>436470</v>
       </c>
       <c r="R65" t="n">
-        <v>6786874</v>
+        <v>6786714</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7071,6 +7070,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7089,10 +7089,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129082516</v>
+        <v>129082545</v>
       </c>
       <c r="B66" t="n">
-        <v>79631</v>
+        <v>78799</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7100,21 +7100,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>436470</v>
+        <v>436085</v>
       </c>
       <c r="R66" t="n">
-        <v>6786714</v>
+        <v>6786778</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7190,10 +7190,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129082545</v>
+        <v>129082515</v>
       </c>
       <c r="B67" t="n">
-        <v>78799</v>
+        <v>79631</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7201,21 +7201,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7228,10 +7228,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>436085</v>
+        <v>436075</v>
       </c>
       <c r="R67" t="n">
-        <v>6786778</v>
+        <v>6786747</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7291,41 +7291,40 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129082572</v>
+        <v>129082528</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -7335,10 +7334,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436553</v>
+        <v>436042</v>
       </c>
       <c r="R68" t="n">
-        <v>6786640</v>
+        <v>6786785</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7379,7 +7378,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7398,10 +7396,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129082550</v>
+        <v>129082507</v>
       </c>
       <c r="B69" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7409,21 +7407,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7433,10 +7431,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>436361</v>
+        <v>436265</v>
       </c>
       <c r="R69" t="n">
-        <v>6786687</v>
+        <v>6786874</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7495,10 +7493,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129082552</v>
+        <v>129082610</v>
       </c>
       <c r="B70" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7506,21 +7504,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7530,10 +7528,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>436206</v>
+        <v>435906</v>
       </c>
       <c r="R70" t="n">
-        <v>6786892</v>
+        <v>6786603</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7592,45 +7590,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129082507</v>
+        <v>129082572</v>
       </c>
       <c r="B71" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436265</v>
+        <v>436553</v>
       </c>
       <c r="R71" t="n">
-        <v>6786874</v>
+        <v>6786640</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7671,6 +7678,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7689,10 +7697,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129082610</v>
+        <v>129082552</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7700,21 +7708,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7724,10 +7732,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>435906</v>
+        <v>436206</v>
       </c>
       <c r="R72" t="n">
-        <v>6786603</v>
+        <v>6786892</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7786,10 +7794,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129082528</v>
+        <v>129082550</v>
       </c>
       <c r="B73" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7797,42 +7805,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436042</v>
+        <v>436361</v>
       </c>
       <c r="R73" t="n">
-        <v>6786785</v>
+        <v>6786687</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7891,10 +7891,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129082639</v>
+        <v>129082534</v>
       </c>
       <c r="B74" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7902,34 +7902,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436568</v>
+        <v>436565</v>
       </c>
       <c r="R74" t="n">
-        <v>6786650</v>
+        <v>6786624</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7988,10 +7996,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129082503</v>
+        <v>129082539</v>
       </c>
       <c r="B75" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7999,34 +8007,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436052</v>
+        <v>436069</v>
       </c>
       <c r="R75" t="n">
-        <v>6786720</v>
+        <v>6786886</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8085,10 +8101,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129082634</v>
+        <v>129082540</v>
       </c>
       <c r="B76" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8096,34 +8112,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436338</v>
+        <v>436188</v>
       </c>
       <c r="R76" t="n">
-        <v>6786664</v>
+        <v>6786921</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8182,10 +8206,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129082534</v>
+        <v>129082639</v>
       </c>
       <c r="B77" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8193,42 +8217,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436565</v>
+        <v>436568</v>
       </c>
       <c r="R77" t="n">
-        <v>6786624</v>
+        <v>6786650</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8287,10 +8303,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129082539</v>
+        <v>129082503</v>
       </c>
       <c r="B78" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8298,42 +8314,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436069</v>
+        <v>436052</v>
       </c>
       <c r="R78" t="n">
-        <v>6786886</v>
+        <v>6786720</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8392,10 +8400,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129082540</v>
+        <v>129082634</v>
       </c>
       <c r="B79" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8403,42 +8411,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436188</v>
+        <v>436338</v>
       </c>
       <c r="R79" t="n">
-        <v>6786921</v>
+        <v>6786664</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8604,45 +8604,53 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129082620</v>
+        <v>129082521</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>436035</v>
+        <v>436093</v>
       </c>
       <c r="R81" t="n">
-        <v>6786730</v>
+        <v>6786769</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8701,10 +8709,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129082513</v>
+        <v>129082620</v>
       </c>
       <c r="B82" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8712,21 +8720,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8736,10 +8744,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>436205</v>
+        <v>436035</v>
       </c>
       <c r="R82" t="n">
-        <v>6786914</v>
+        <v>6786730</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8798,10 +8806,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129082635</v>
+        <v>129082513</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8809,21 +8817,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8833,10 +8841,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>436350</v>
+        <v>436205</v>
       </c>
       <c r="R83" t="n">
-        <v>6786631</v>
+        <v>6786914</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8895,7 +8903,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129082649</v>
+        <v>129082635</v>
       </c>
       <c r="B84" t="n">
         <v>79041</v>
@@ -8930,10 +8938,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>436277</v>
+        <v>436350</v>
       </c>
       <c r="R84" t="n">
-        <v>6786944</v>
+        <v>6786631</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8992,7 +9000,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129082617</v>
+        <v>129082649</v>
       </c>
       <c r="B85" t="n">
         <v>79041</v>
@@ -9027,10 +9035,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>436010</v>
+        <v>436277</v>
       </c>
       <c r="R85" t="n">
-        <v>6786752</v>
+        <v>6786944</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9089,7 +9097,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129082667</v>
+        <v>129082617</v>
       </c>
       <c r="B86" t="n">
         <v>79041</v>
@@ -9124,10 +9132,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>435965</v>
+        <v>436010</v>
       </c>
       <c r="R86" t="n">
-        <v>6786476</v>
+        <v>6786752</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9186,53 +9194,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129082521</v>
+        <v>129082667</v>
       </c>
       <c r="B87" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>436093</v>
+        <v>435965</v>
       </c>
       <c r="R87" t="n">
-        <v>6786769</v>
+        <v>6786476</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9291,45 +9291,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129082654</v>
+        <v>129082671</v>
       </c>
       <c r="B88" t="n">
-        <v>79041</v>
+        <v>92822</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>436054</v>
+        <v>436349</v>
       </c>
       <c r="R88" t="n">
-        <v>6786881</v>
+        <v>6786689</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9370,6 +9373,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9388,10 +9392,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129082625</v>
+        <v>129082536</v>
       </c>
       <c r="B89" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9399,34 +9403,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>436202</v>
+        <v>436544</v>
       </c>
       <c r="R89" t="n">
-        <v>6786849</v>
+        <v>6786666</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9485,7 +9497,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129082665</v>
+        <v>129082654</v>
       </c>
       <c r="B90" t="n">
         <v>79041</v>
@@ -9520,10 +9532,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436330</v>
+        <v>436054</v>
       </c>
       <c r="R90" t="n">
-        <v>6786736</v>
+        <v>6786881</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9582,7 +9594,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129082606</v>
+        <v>129082625</v>
       </c>
       <c r="B91" t="n">
         <v>79041</v>
@@ -9617,10 +9629,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>435970</v>
+        <v>436202</v>
       </c>
       <c r="R91" t="n">
-        <v>6786458</v>
+        <v>6786849</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9679,7 +9691,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129082619</v>
+        <v>129082665</v>
       </c>
       <c r="B92" t="n">
         <v>79041</v>
@@ -9714,10 +9726,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>436034</v>
+        <v>436330</v>
       </c>
       <c r="R92" t="n">
-        <v>6786743</v>
+        <v>6786736</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9776,7 +9788,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129082616</v>
+        <v>129082606</v>
       </c>
       <c r="B93" t="n">
         <v>79041</v>
@@ -9811,10 +9823,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436012</v>
+        <v>435970</v>
       </c>
       <c r="R93" t="n">
-        <v>6786734</v>
+        <v>6786458</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9873,10 +9885,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129082595</v>
+        <v>129082619</v>
       </c>
       <c r="B94" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9884,21 +9896,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9908,10 +9920,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436361</v>
+        <v>436034</v>
       </c>
       <c r="R94" t="n">
-        <v>6786688</v>
+        <v>6786743</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9970,10 +9982,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129082594</v>
+        <v>129082616</v>
       </c>
       <c r="B95" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9981,21 +9993,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10005,10 +10017,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436339</v>
+        <v>436012</v>
       </c>
       <c r="R95" t="n">
-        <v>6786747</v>
+        <v>6786734</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10067,54 +10079,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129082582</v>
+        <v>129082595</v>
       </c>
       <c r="B96" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436138</v>
+        <v>436361</v>
       </c>
       <c r="R96" t="n">
-        <v>6786894</v>
+        <v>6786688</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10155,7 +10158,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10174,48 +10176,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129082671</v>
+        <v>129082594</v>
       </c>
       <c r="B97" t="n">
-        <v>92822</v>
+        <v>78798</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436349</v>
+        <v>436339</v>
       </c>
       <c r="R97" t="n">
-        <v>6786689</v>
+        <v>6786747</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10256,7 +10255,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10275,10 +10273,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129082536</v>
+        <v>129082525</v>
       </c>
       <c r="B98" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10286,21 +10284,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10308,7 +10306,7 @@
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -10318,10 +10316,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436544</v>
+        <v>435948</v>
       </c>
       <c r="R98" t="n">
-        <v>6786666</v>
+        <v>6786586</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10380,40 +10378,41 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129082525</v>
+        <v>129082582</v>
       </c>
       <c r="B99" t="n">
-        <v>57887</v>
+        <v>8450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -10423,10 +10422,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>435948</v>
+        <v>436138</v>
       </c>
       <c r="R99" t="n">
-        <v>6786586</v>
+        <v>6786894</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10467,6 +10466,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10485,10 +10485,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129082556</v>
+        <v>129082514</v>
       </c>
       <c r="B100" t="n">
-        <v>78799</v>
+        <v>79631</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10496,21 +10496,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10520,10 +10520,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436010</v>
+        <v>436044</v>
       </c>
       <c r="R100" t="n">
-        <v>6786852</v>
+        <v>6786741</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10582,10 +10582,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129082514</v>
+        <v>129082556</v>
       </c>
       <c r="B101" t="n">
-        <v>79631</v>
+        <v>78799</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10593,21 +10593,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10617,10 +10617,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>436044</v>
+        <v>436010</v>
       </c>
       <c r="R101" t="n">
-        <v>6786741</v>
+        <v>6786852</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12063,54 +12063,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129082580</v>
+        <v>129082645</v>
       </c>
       <c r="B116" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>436280</v>
+        <v>436405</v>
       </c>
       <c r="R116" t="n">
-        <v>6786936</v>
+        <v>6786825</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12151,7 +12142,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12170,54 +12160,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129082586</v>
+        <v>129082633</v>
       </c>
       <c r="B117" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>435931</v>
+        <v>436347</v>
       </c>
       <c r="R117" t="n">
-        <v>6786572</v>
+        <v>6786689</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12258,7 +12239,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12277,7 +12257,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129082576</v>
+        <v>129082580</v>
       </c>
       <c r="B118" t="n">
         <v>8450</v>
@@ -12321,10 +12301,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>436417</v>
+        <v>436280</v>
       </c>
       <c r="R118" t="n">
-        <v>6786827</v>
+        <v>6786936</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12491,45 +12471,54 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129082554</v>
+        <v>129082576</v>
       </c>
       <c r="B120" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>436096</v>
+        <v>436417</v>
       </c>
       <c r="R120" t="n">
-        <v>6786876</v>
+        <v>6786827</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12570,6 +12559,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12588,45 +12578,54 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129082645</v>
+        <v>129082586</v>
       </c>
       <c r="B121" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>436405</v>
+        <v>435931</v>
       </c>
       <c r="R121" t="n">
-        <v>6786825</v>
+        <v>6786572</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12667,6 +12666,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12685,10 +12685,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129082633</v>
+        <v>129082554</v>
       </c>
       <c r="B122" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12696,21 +12696,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12720,10 +12720,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>436347</v>
+        <v>436096</v>
       </c>
       <c r="R122" t="n">
-        <v>6786689</v>
+        <v>6786876</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12782,45 +12782,54 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129082618</v>
+        <v>129082563</v>
       </c>
       <c r="B123" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>436027</v>
+        <v>436055</v>
       </c>
       <c r="R123" t="n">
-        <v>6786735</v>
+        <v>6786776</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12861,6 +12870,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12879,45 +12889,54 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129082598</v>
+        <v>129082565</v>
       </c>
       <c r="B124" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>436107</v>
+        <v>436230</v>
       </c>
       <c r="R124" t="n">
-        <v>6786875</v>
+        <v>6786855</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12958,6 +12977,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -12976,7 +12996,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129082613</v>
+        <v>129082618</v>
       </c>
       <c r="B125" t="n">
         <v>79041</v>
@@ -13011,10 +13031,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>435886</v>
+        <v>436027</v>
       </c>
       <c r="R125" t="n">
-        <v>6786666</v>
+        <v>6786735</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13073,54 +13093,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129082565</v>
+        <v>129082598</v>
       </c>
       <c r="B126" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436230</v>
+        <v>436107</v>
       </c>
       <c r="R126" t="n">
-        <v>6786855</v>
+        <v>6786875</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13161,7 +13172,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13180,54 +13190,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129082563</v>
+        <v>129082613</v>
       </c>
       <c r="B127" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>436055</v>
+        <v>435886</v>
       </c>
       <c r="R127" t="n">
-        <v>6786776</v>
+        <v>6786666</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13268,7 +13269,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13578,10 +13578,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129082535</v>
+        <v>129082547</v>
       </c>
       <c r="B131" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13589,42 +13589,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>436575</v>
+        <v>436172</v>
       </c>
       <c r="R131" t="n">
-        <v>6786632</v>
+        <v>6786825</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13683,41 +13675,40 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129082558</v>
+        <v>129082535</v>
       </c>
       <c r="B132" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -13727,10 +13718,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>435909</v>
+        <v>436575</v>
       </c>
       <c r="R132" t="n">
-        <v>6786616</v>
+        <v>6786632</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13771,7 +13762,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13790,7 +13780,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129082583</v>
+        <v>129082558</v>
       </c>
       <c r="B133" t="n">
         <v>8450</v>
@@ -13834,10 +13824,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>436011</v>
+        <v>435909</v>
       </c>
       <c r="R133" t="n">
-        <v>6786844</v>
+        <v>6786616</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13897,45 +13887,54 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129082547</v>
+        <v>129082583</v>
       </c>
       <c r="B134" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>436172</v>
+        <v>436011</v>
       </c>
       <c r="R134" t="n">
-        <v>6786825</v>
+        <v>6786844</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13976,6 +13975,7 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49064-2025 artfynd.xlsx
+++ b/artfynd/A 49064-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129082641</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129082659</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129082637</v>
+        <v>129082546</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>78801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436410</v>
+        <v>436092</v>
       </c>
       <c r="R4" t="n">
-        <v>6786560</v>
+        <v>6786744</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,54 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129082570</v>
+        <v>129082544</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>78801</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436428</v>
+        <v>436044</v>
       </c>
       <c r="R5" t="n">
-        <v>6786577</v>
+        <v>6786741</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,7 +1045,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1073,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129082546</v>
+        <v>129082637</v>
       </c>
       <c r="B6" t="n">
-        <v>78799</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436092</v>
+        <v>436410</v>
       </c>
       <c r="R6" t="n">
-        <v>6786744</v>
+        <v>6786560</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,45 +1160,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129082544</v>
+        <v>129082570</v>
       </c>
       <c r="B7" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436044</v>
+        <v>436428</v>
       </c>
       <c r="R7" t="n">
-        <v>6786741</v>
+        <v>6786577</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,6 +1248,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>129082651</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129082638</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>129082508</v>
       </c>
       <c r="B12" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>129082510</v>
       </c>
       <c r="B13" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2190,53 +2190,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129082522</v>
+        <v>129082652</v>
       </c>
       <c r="B17" t="n">
-        <v>56917</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436195</v>
+        <v>436190</v>
       </c>
       <c r="R17" t="n">
-        <v>6786902</v>
+        <v>6786911</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2295,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129082652</v>
+        <v>129082622</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2330,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436190</v>
+        <v>436101</v>
       </c>
       <c r="R18" t="n">
-        <v>6786911</v>
+        <v>6786774</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2392,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129082622</v>
+        <v>129082629</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2427,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436101</v>
+        <v>436335</v>
       </c>
       <c r="R19" t="n">
-        <v>6786774</v>
+        <v>6786743</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2489,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129082629</v>
+        <v>129082630</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2524,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436335</v>
+        <v>436320</v>
       </c>
       <c r="R20" t="n">
-        <v>6786743</v>
+        <v>6786718</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2586,45 +2578,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129082630</v>
+        <v>129082522</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436320</v>
+        <v>436195</v>
       </c>
       <c r="R21" t="n">
-        <v>6786718</v>
+        <v>6786902</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2686,7 +2686,7 @@
         <v>129082614</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>129082640</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129082549</v>
+        <v>129082537</v>
       </c>
       <c r="B24" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2888,34 +2888,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436322</v>
+        <v>436399</v>
       </c>
       <c r="R24" t="n">
-        <v>6786798</v>
+        <v>6786867</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2974,10 +2982,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129082537</v>
+        <v>129082549</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>78801</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2985,42 +2993,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436399</v>
+        <v>436322</v>
       </c>
       <c r="R25" t="n">
-        <v>6786867</v>
+        <v>6786798</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129082524</v>
+        <v>129082504</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>79662</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3090,42 +3090,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436189</v>
+        <v>436031</v>
       </c>
       <c r="R26" t="n">
-        <v>6786920</v>
+        <v>6786744</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3184,10 +3176,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129082504</v>
+        <v>129082636</v>
       </c>
       <c r="B27" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3195,21 +3187,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3219,10 +3211,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436031</v>
+        <v>436431</v>
       </c>
       <c r="R27" t="n">
-        <v>6786744</v>
+        <v>6786583</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3281,10 +3273,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129082636</v>
+        <v>129082505</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3292,21 +3284,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3316,10 +3308,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436431</v>
+        <v>436095</v>
       </c>
       <c r="R28" t="n">
-        <v>6786583</v>
+        <v>6786747</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3378,10 +3370,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129082505</v>
+        <v>129082653</v>
       </c>
       <c r="B29" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3389,34 +3381,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436095</v>
+        <v>436092</v>
       </c>
       <c r="R29" t="n">
-        <v>6786747</v>
+        <v>6786889</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3457,6 +3452,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3475,10 +3471,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129082653</v>
+        <v>129082512</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3486,37 +3482,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436092</v>
+        <v>436428</v>
       </c>
       <c r="R30" t="n">
-        <v>6786889</v>
+        <v>6786809</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3557,7 +3550,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3576,10 +3568,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129082512</v>
+        <v>129082589</v>
       </c>
       <c r="B31" t="n">
-        <v>79660</v>
+        <v>78800</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3587,21 +3579,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3611,10 +3603,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436428</v>
+        <v>436033</v>
       </c>
       <c r="R31" t="n">
-        <v>6786809</v>
+        <v>6786758</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3673,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129082589</v>
+        <v>129082524</v>
       </c>
       <c r="B32" t="n">
-        <v>78798</v>
+        <v>57887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3684,34 +3676,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436033</v>
+        <v>436189</v>
       </c>
       <c r="R32" t="n">
-        <v>6786758</v>
+        <v>6786920</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3877,45 +3877,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129082662</v>
+        <v>129082573</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435932</v>
+        <v>436525</v>
       </c>
       <c r="R34" t="n">
-        <v>6786581</v>
+        <v>6786729</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3956,6 +3965,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3974,10 +3984,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129082612</v>
+        <v>129082543</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>78801</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3985,21 +3995,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4009,10 +4019,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435883</v>
+        <v>436027</v>
       </c>
       <c r="R35" t="n">
-        <v>6786641</v>
+        <v>6786747</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4071,10 +4081,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129082646</v>
+        <v>129082551</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>78801</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4082,21 +4092,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4106,10 +4116,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436400</v>
+        <v>436436</v>
       </c>
       <c r="R36" t="n">
-        <v>6786855</v>
+        <v>6786563</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4168,54 +4178,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129082573</v>
+        <v>129082662</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436525</v>
+        <v>435932</v>
       </c>
       <c r="R37" t="n">
-        <v>6786729</v>
+        <v>6786581</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4256,7 +4257,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129082543</v>
+        <v>129082612</v>
       </c>
       <c r="B38" t="n">
-        <v>78799</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4286,21 +4286,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436027</v>
+        <v>435883</v>
       </c>
       <c r="R38" t="n">
-        <v>6786747</v>
+        <v>6786641</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4372,10 +4372,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129082551</v>
+        <v>129082646</v>
       </c>
       <c r="B39" t="n">
-        <v>78799</v>
+        <v>79043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4383,21 +4383,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436436</v>
+        <v>436400</v>
       </c>
       <c r="R39" t="n">
-        <v>6786563</v>
+        <v>6786855</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4469,7 +4469,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129082538</v>
+        <v>129082533</v>
       </c>
       <c r="B40" t="n">
         <v>57724</v>
@@ -4512,10 +4512,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436141</v>
+        <v>436445</v>
       </c>
       <c r="R40" t="n">
-        <v>6786882</v>
+        <v>6786610</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129082533</v>
+        <v>129082538</v>
       </c>
       <c r="B41" t="n">
         <v>57724</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436445</v>
+        <v>436141</v>
       </c>
       <c r="R41" t="n">
-        <v>6786610</v>
+        <v>6786882</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4784,10 +4784,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129082590</v>
+        <v>129082553</v>
       </c>
       <c r="B43" t="n">
-        <v>78798</v>
+        <v>78801</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4795,21 +4795,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436051</v>
+        <v>436197</v>
       </c>
       <c r="R43" t="n">
-        <v>6786730</v>
+        <v>6786924</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4881,10 +4881,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129082593</v>
+        <v>129082590</v>
       </c>
       <c r="B44" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436271</v>
+        <v>436051</v>
       </c>
       <c r="R44" t="n">
-        <v>6786851</v>
+        <v>6786730</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4978,10 +4978,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129082663</v>
+        <v>129082593</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4989,21 +4989,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435984</v>
+        <v>436271</v>
       </c>
       <c r="R45" t="n">
-        <v>6786452</v>
+        <v>6786851</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5075,54 +5075,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129082581</v>
+        <v>129082663</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436252</v>
+        <v>435984</v>
       </c>
       <c r="R46" t="n">
-        <v>6786963</v>
+        <v>6786452</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5163,7 +5154,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5182,45 +5172,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129082553</v>
+        <v>129082581</v>
       </c>
       <c r="B47" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436197</v>
+        <v>436252</v>
       </c>
       <c r="R47" t="n">
-        <v>6786924</v>
+        <v>6786963</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5261,6 +5260,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5282,7 +5282,7 @@
         <v>129082648</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>129082611</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>129082624</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>129082655</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5990,45 +5990,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129082647</v>
+        <v>129082577</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436372</v>
+        <v>436381</v>
       </c>
       <c r="R55" t="n">
-        <v>6786946</v>
+        <v>6786936</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6069,6 +6078,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6087,45 +6097,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129082656</v>
+        <v>129082564</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435996</v>
+        <v>436166</v>
       </c>
       <c r="R56" t="n">
-        <v>6786755</v>
+        <v>6786846</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6166,6 +6185,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6184,54 +6204,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129082577</v>
+        <v>129082647</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>436381</v>
+        <v>436372</v>
       </c>
       <c r="R57" t="n">
-        <v>6786936</v>
+        <v>6786946</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6272,7 +6283,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6291,54 +6301,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129082564</v>
+        <v>129082656</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>436166</v>
+        <v>435996</v>
       </c>
       <c r="R58" t="n">
-        <v>6786846</v>
+        <v>6786755</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6379,7 +6380,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6401,7 +6401,7 @@
         <v>129082555</v>
       </c>
       <c r="B59" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>129082644</v>
       </c>
       <c r="B60" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>129082597</v>
       </c>
       <c r="B61" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>129082666</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>129082506</v>
       </c>
       <c r="B63" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>129082548</v>
       </c>
       <c r="B64" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>129082516</v>
       </c>
       <c r="B65" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>129082545</v>
       </c>
       <c r="B66" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>129082515</v>
       </c>
       <c r="B67" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7291,10 +7291,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129082528</v>
+        <v>129082552</v>
       </c>
       <c r="B68" t="n">
-        <v>57724</v>
+        <v>78801</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7302,42 +7302,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>436042</v>
+        <v>436206</v>
       </c>
       <c r="R68" t="n">
-        <v>6786785</v>
+        <v>6786892</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7396,10 +7388,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129082507</v>
+        <v>129082550</v>
       </c>
       <c r="B69" t="n">
-        <v>79660</v>
+        <v>78801</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7407,21 +7399,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7431,10 +7423,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>436265</v>
+        <v>436361</v>
       </c>
       <c r="R69" t="n">
-        <v>6786874</v>
+        <v>6786687</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7493,45 +7485,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129082610</v>
+        <v>129082572</v>
       </c>
       <c r="B70" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>435906</v>
+        <v>436553</v>
       </c>
       <c r="R70" t="n">
-        <v>6786603</v>
+        <v>6786640</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7572,6 +7573,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7590,54 +7592,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129082572</v>
+        <v>129082507</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>79662</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>436553</v>
+        <v>436265</v>
       </c>
       <c r="R71" t="n">
-        <v>6786640</v>
+        <v>6786874</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7678,7 +7671,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7697,10 +7689,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129082552</v>
+        <v>129082610</v>
       </c>
       <c r="B72" t="n">
-        <v>78799</v>
+        <v>79043</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7708,21 +7700,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7732,10 +7724,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>436206</v>
+        <v>435906</v>
       </c>
       <c r="R72" t="n">
-        <v>6786892</v>
+        <v>6786603</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7794,10 +7786,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129082550</v>
+        <v>129082528</v>
       </c>
       <c r="B73" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7805,34 +7797,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>436361</v>
+        <v>436042</v>
       </c>
       <c r="R73" t="n">
-        <v>6786687</v>
+        <v>6786785</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7891,40 +7891,41 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129082534</v>
+        <v>129082579</v>
       </c>
       <c r="B74" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -7934,10 +7935,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436565</v>
+        <v>436306</v>
       </c>
       <c r="R74" t="n">
-        <v>6786624</v>
+        <v>6786960</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7978,6 +7979,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7996,10 +7998,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129082539</v>
+        <v>129082639</v>
       </c>
       <c r="B75" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8007,42 +8009,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436069</v>
+        <v>436568</v>
       </c>
       <c r="R75" t="n">
-        <v>6786886</v>
+        <v>6786650</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8101,10 +8095,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129082540</v>
+        <v>129082503</v>
       </c>
       <c r="B76" t="n">
-        <v>57724</v>
+        <v>79662</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8112,42 +8106,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436188</v>
+        <v>436052</v>
       </c>
       <c r="R76" t="n">
-        <v>6786921</v>
+        <v>6786720</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8206,10 +8192,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129082639</v>
+        <v>129082634</v>
       </c>
       <c r="B77" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8241,10 +8227,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>436568</v>
+        <v>436338</v>
       </c>
       <c r="R77" t="n">
-        <v>6786650</v>
+        <v>6786664</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8303,10 +8289,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129082503</v>
+        <v>129082540</v>
       </c>
       <c r="B78" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8314,34 +8300,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>436052</v>
+        <v>436188</v>
       </c>
       <c r="R78" t="n">
-        <v>6786720</v>
+        <v>6786921</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8400,10 +8394,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129082634</v>
+        <v>129082539</v>
       </c>
       <c r="B79" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8411,34 +8405,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436338</v>
+        <v>436069</v>
       </c>
       <c r="R79" t="n">
-        <v>6786664</v>
+        <v>6786886</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8497,41 +8499,40 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129082579</v>
+        <v>129082534</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8541,10 +8542,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436306</v>
+        <v>436565</v>
       </c>
       <c r="R80" t="n">
-        <v>6786960</v>
+        <v>6786624</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8585,7 +8586,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8604,53 +8604,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129082521</v>
+        <v>129082667</v>
       </c>
       <c r="B81" t="n">
-        <v>56917</v>
+        <v>79043</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>436093</v>
+        <v>435965</v>
       </c>
       <c r="R81" t="n">
-        <v>6786769</v>
+        <v>6786476</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8712,7 +8704,7 @@
         <v>129082620</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8809,7 +8801,7 @@
         <v>129082513</v>
       </c>
       <c r="B83" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8906,7 +8898,7 @@
         <v>129082635</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9003,7 +8995,7 @@
         <v>129082649</v>
       </c>
       <c r="B85" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9100,7 +9092,7 @@
         <v>129082617</v>
       </c>
       <c r="B86" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9194,45 +9186,53 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129082667</v>
+        <v>129082521</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>435965</v>
+        <v>436093</v>
       </c>
       <c r="R87" t="n">
-        <v>6786476</v>
+        <v>6786769</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9294,7 +9294,7 @@
         <v>129082671</v>
       </c>
       <c r="B88" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9392,10 +9392,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129082536</v>
+        <v>129082654</v>
       </c>
       <c r="B89" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9403,42 +9403,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>436544</v>
+        <v>436054</v>
       </c>
       <c r="R89" t="n">
-        <v>6786666</v>
+        <v>6786881</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9497,10 +9489,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129082654</v>
+        <v>129082625</v>
       </c>
       <c r="B90" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9532,10 +9524,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436054</v>
+        <v>436202</v>
       </c>
       <c r="R90" t="n">
-        <v>6786881</v>
+        <v>6786849</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9594,10 +9586,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129082625</v>
+        <v>129082665</v>
       </c>
       <c r="B91" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9629,10 +9621,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>436202</v>
+        <v>436330</v>
       </c>
       <c r="R91" t="n">
-        <v>6786849</v>
+        <v>6786736</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9691,10 +9683,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129082665</v>
+        <v>129082606</v>
       </c>
       <c r="B92" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9726,10 +9718,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>436330</v>
+        <v>435970</v>
       </c>
       <c r="R92" t="n">
-        <v>6786736</v>
+        <v>6786458</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9788,10 +9780,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129082606</v>
+        <v>129082619</v>
       </c>
       <c r="B93" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9823,10 +9815,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>435970</v>
+        <v>436034</v>
       </c>
       <c r="R93" t="n">
-        <v>6786458</v>
+        <v>6786743</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9885,10 +9877,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129082619</v>
+        <v>129082616</v>
       </c>
       <c r="B94" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9920,10 +9912,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436034</v>
+        <v>436012</v>
       </c>
       <c r="R94" t="n">
-        <v>6786743</v>
+        <v>6786734</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9982,10 +9974,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129082616</v>
+        <v>129082595</v>
       </c>
       <c r="B95" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9993,21 +9985,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10017,10 +10009,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436012</v>
+        <v>436361</v>
       </c>
       <c r="R95" t="n">
-        <v>6786734</v>
+        <v>6786688</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10079,10 +10071,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129082595</v>
+        <v>129082594</v>
       </c>
       <c r="B96" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10114,10 +10106,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436361</v>
+        <v>436339</v>
       </c>
       <c r="R96" t="n">
-        <v>6786688</v>
+        <v>6786747</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10176,10 +10168,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129082594</v>
+        <v>129082536</v>
       </c>
       <c r="B97" t="n">
-        <v>78798</v>
+        <v>57724</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10187,34 +10179,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436339</v>
+        <v>436544</v>
       </c>
       <c r="R97" t="n">
-        <v>6786747</v>
+        <v>6786666</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10378,54 +10378,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129082582</v>
+        <v>129082514</v>
       </c>
       <c r="B99" t="n">
-        <v>8450</v>
+        <v>79633</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>436138</v>
+        <v>436044</v>
       </c>
       <c r="R99" t="n">
-        <v>6786894</v>
+        <v>6786741</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10466,7 +10457,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10485,10 +10475,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129082514</v>
+        <v>129082556</v>
       </c>
       <c r="B100" t="n">
-        <v>79631</v>
+        <v>78801</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10496,21 +10486,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10520,10 +10510,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>436044</v>
+        <v>436010</v>
       </c>
       <c r="R100" t="n">
-        <v>6786741</v>
+        <v>6786852</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10582,45 +10572,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129082556</v>
+        <v>129082582</v>
       </c>
       <c r="B101" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>436010</v>
+        <v>436138</v>
       </c>
       <c r="R101" t="n">
-        <v>6786852</v>
+        <v>6786894</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10661,6 +10660,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -10679,7 +10679,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129082532</v>
+        <v>129082531</v>
       </c>
       <c r="B102" t="n">
         <v>57724</v>
@@ -10722,10 +10722,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>436295</v>
+        <v>436246</v>
       </c>
       <c r="R102" t="n">
-        <v>6786848</v>
+        <v>6786863</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10784,7 +10784,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129082531</v>
+        <v>129082532</v>
       </c>
       <c r="B103" t="n">
         <v>57724</v>
@@ -10827,10 +10827,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>436246</v>
+        <v>436295</v>
       </c>
       <c r="R103" t="n">
-        <v>6786863</v>
+        <v>6786848</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10892,7 +10892,7 @@
         <v>129082621</v>
       </c>
       <c r="B104" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>129082642</v>
       </c>
       <c r="B105" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>129082591</v>
       </c>
       <c r="B106" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>129082650</v>
       </c>
       <c r="B107" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>129082509</v>
       </c>
       <c r="B109" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>129082628</v>
       </c>
       <c r="B110" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
         <v>129082632</v>
       </c>
       <c r="B111" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>129082609</v>
       </c>
       <c r="B112" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>129082592</v>
       </c>
       <c r="B113" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         <v>129082627</v>
       </c>
       <c r="B114" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>129082668</v>
       </c>
       <c r="B115" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>129082645</v>
       </c>
       <c r="B116" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>129082633</v>
       </c>
       <c r="B117" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12257,54 +12257,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129082580</v>
+        <v>129082554</v>
       </c>
       <c r="B118" t="n">
-        <v>8450</v>
+        <v>78801</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>436280</v>
+        <v>436096</v>
       </c>
       <c r="R118" t="n">
-        <v>6786936</v>
+        <v>6786876</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12345,7 +12336,6 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12685,45 +12675,54 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129082554</v>
+        <v>129082580</v>
       </c>
       <c r="B122" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>436096</v>
+        <v>436280</v>
       </c>
       <c r="R122" t="n">
-        <v>6786876</v>
+        <v>6786936</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12764,6 +12763,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12782,54 +12782,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129082563</v>
+        <v>129082618</v>
       </c>
       <c r="B123" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>436055</v>
+        <v>436027</v>
       </c>
       <c r="R123" t="n">
-        <v>6786776</v>
+        <v>6786735</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12870,7 +12861,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12889,54 +12879,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129082565</v>
+        <v>129082598</v>
       </c>
       <c r="B124" t="n">
-        <v>8450</v>
+        <v>78800</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>436230</v>
+        <v>436107</v>
       </c>
       <c r="R124" t="n">
-        <v>6786855</v>
+        <v>6786875</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12977,7 +12958,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -12996,10 +12976,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129082618</v>
+        <v>129082613</v>
       </c>
       <c r="B125" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13031,10 +13011,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>436027</v>
+        <v>435886</v>
       </c>
       <c r="R125" t="n">
-        <v>6786735</v>
+        <v>6786666</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13093,45 +13073,54 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129082598</v>
+        <v>129082563</v>
       </c>
       <c r="B126" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>436107</v>
+        <v>436055</v>
       </c>
       <c r="R126" t="n">
-        <v>6786875</v>
+        <v>6786776</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13172,6 +13161,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13190,45 +13180,54 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129082613</v>
+        <v>129082565</v>
       </c>
       <c r="B127" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>435886</v>
+        <v>436230</v>
       </c>
       <c r="R127" t="n">
-        <v>6786666</v>
+        <v>6786855</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13269,6 +13268,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13287,10 +13287,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129082596</v>
+        <v>129082535</v>
       </c>
       <c r="B128" t="n">
-        <v>78798</v>
+        <v>57724</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13298,34 +13298,42 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>436432</v>
+        <v>436575</v>
       </c>
       <c r="R128" t="n">
-        <v>6786558</v>
+        <v>6786632</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13384,45 +13392,54 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129082626</v>
+        <v>129082558</v>
       </c>
       <c r="B129" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>436240</v>
+        <v>435909</v>
       </c>
       <c r="R129" t="n">
-        <v>6786833</v>
+        <v>6786616</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13463,6 +13480,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13481,45 +13499,54 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129082664</v>
+        <v>129082583</v>
       </c>
       <c r="B130" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>436029</v>
+        <v>436011</v>
       </c>
       <c r="R130" t="n">
-        <v>6786750</v>
+        <v>6786844</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13560,6 +13587,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -13581,7 +13609,7 @@
         <v>129082547</v>
       </c>
       <c r="B131" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13675,10 +13703,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129082535</v>
+        <v>129082596</v>
       </c>
       <c r="B132" t="n">
-        <v>57724</v>
+        <v>78800</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13686,42 +13714,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>436575</v>
+        <v>436432</v>
       </c>
       <c r="R132" t="n">
-        <v>6786632</v>
+        <v>6786558</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13780,54 +13800,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129082558</v>
+        <v>129082626</v>
       </c>
       <c r="B133" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>435909</v>
+        <v>436240</v>
       </c>
       <c r="R133" t="n">
-        <v>6786616</v>
+        <v>6786833</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13868,7 +13879,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -13887,54 +13897,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129082583</v>
+        <v>129082664</v>
       </c>
       <c r="B134" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rätjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>436011</v>
+        <v>436029</v>
       </c>
       <c r="R134" t="n">
-        <v>6786844</v>
+        <v>6786750</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13975,7 +13976,6 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49064-2025 artfynd.xlsx
+++ b/artfynd/A 49064-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY148"/>
+  <dimension ref="A1:AZ148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082605</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082606</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082608</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082609</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082610</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082611</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082612</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082613</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082614</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082615</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082616</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082617</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082618</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082619</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082620</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082621</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082622</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082624</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082625</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082626</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082627</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082649</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082650</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082651</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082652</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3198,6 +3328,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082653</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3295,6 +3430,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082654</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3392,6 +3532,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082655</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3489,6 +3634,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082656</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3586,6 +3736,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082657</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3683,6 +3838,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082658</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3780,6 +3940,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082659</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3877,6 +4042,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082660</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3974,6 +4144,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082661</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4071,6 +4246,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082662</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4168,6 +4348,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082663</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4265,6 +4450,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082664</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4362,6 +4552,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082667</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4459,6 +4654,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082668</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4556,6 +4756,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082589</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4653,6 +4858,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082590</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4750,6 +4960,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082591</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4847,6 +5062,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082592</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4944,6 +5164,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082593</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5041,6 +5266,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082598</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5138,6 +5368,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082599</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5235,6 +5470,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082503</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5332,6 +5572,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082504</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5429,6 +5674,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082505</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5530,6 +5780,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082506</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5627,6 +5882,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082507</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5724,6 +5984,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082513</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5829,6 +6094,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082527</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5934,6 +6204,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082528</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6039,6 +6314,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082529</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6144,6 +6424,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082531</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6249,6 +6534,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082532</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6354,6 +6644,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082538</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6459,6 +6754,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082539</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6564,6 +6864,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082540</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6669,6 +6974,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082521</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6774,6 +7084,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082522</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6879,6 +7194,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082588</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6984,6 +7304,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082604</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7089,6 +7414,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082524</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7194,6 +7524,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082525</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7301,6 +7636,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082558</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7408,6 +7748,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082559</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7515,6 +7860,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082560</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7622,6 +7972,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082561</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7729,6 +8084,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082562</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7836,6 +8196,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082563</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7943,6 +8308,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082564</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8050,6 +8420,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082565</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8157,6 +8532,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082566</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8264,6 +8644,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082579</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8371,6 +8756,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082580</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8478,6 +8868,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082581</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8585,6 +8980,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082582</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8692,6 +9092,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082583</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8799,6 +9204,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082584</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8906,6 +9316,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082585</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9013,6 +9428,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082586</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9110,6 +9530,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082543</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9207,6 +9632,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082544</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9308,6 +9738,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082545</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9405,6 +9840,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082546</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9502,6 +9942,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082547</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9599,6 +10044,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082548</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9696,6 +10146,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082552</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9793,6 +10248,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082553</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9890,6 +10350,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082554</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9991,6 +10456,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082555</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10088,6 +10558,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082556</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10185,6 +10660,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082557</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10282,6 +10762,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082514</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10383,6 +10868,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082515</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10484,6 +10974,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082671</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10581,6 +11076,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082628</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10678,6 +11178,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082629</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10775,6 +11280,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082630</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10872,6 +11382,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082632</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10969,6 +11484,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082633</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11066,6 +11586,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082634</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11163,6 +11688,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082635</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11260,6 +11790,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082636</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11357,6 +11892,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082637</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11454,6 +11994,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082638</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11551,6 +12096,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082639</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11648,6 +12198,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082640</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11745,6 +12300,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082641</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11842,6 +12402,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082642</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11939,6 +12504,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082644</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12036,6 +12606,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082645</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12133,6 +12708,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082646</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12230,6 +12810,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082647</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12331,6 +12916,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082648</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12428,6 +13018,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082665</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12525,6 +13120,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082666</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12622,6 +13222,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082594</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12719,6 +13324,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082595</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12816,6 +13426,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082596</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12913,6 +13528,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082597</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13010,6 +13630,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082508</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13107,6 +13732,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082509</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13204,6 +13834,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082510</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13301,6 +13936,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082512</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13406,6 +14046,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082533</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13511,6 +14156,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082534</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13616,6 +14266,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082535</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13721,6 +14376,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082536</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13826,6 +14486,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082537</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13933,6 +14598,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082567</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14040,6 +14710,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082568</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14147,6 +14822,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082570</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14254,6 +14934,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082571</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14361,6 +15046,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082572</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14468,6 +15158,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082573</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14575,6 +15270,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082574</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14682,6 +15382,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082575</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14789,6 +15494,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082576</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14896,6 +15606,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082577</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15003,6 +15718,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082578</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15100,6 +15820,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082549</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15197,6 +15922,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082550</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15294,6 +16024,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082551</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15395,8 +16130,162 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129082516</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>